--- a/data/health_tracker_dataset.xlsx
+++ b/data/health_tracker_dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\PycharmProjects\ComponentOne\DSGP\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\PycharmProjects\DSGP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3B1376-2777-491F-A06B-6BC6AE00B979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9F2CF-D5F3-40F9-A1B1-AA7C256AED86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{27FCE13B-2E77-4A27-A5F0-881C18068B7E}"/>
   </bookViews>
@@ -109,7 +109,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,7 +449,7 @@
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.5546875" bestFit="1" customWidth="1"/>
@@ -463,7 +463,7 @@
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
@@ -487,7 +487,7 @@
         <v>1450.71</v>
       </c>
       <c r="C2" s="1">
-        <v>676.03</v>
+        <v>675.42</v>
       </c>
       <c r="D2">
         <v>310.05</v>
@@ -510,7 +510,7 @@
         <v>1469.91</v>
       </c>
       <c r="C3" s="1">
-        <v>758.8</v>
+        <v>758.91</v>
       </c>
       <c r="D3">
         <v>446.38</v>
@@ -533,7 +533,7 @@
         <v>1111.6500000000001</v>
       </c>
       <c r="C4" s="1">
-        <v>115.09</v>
+        <v>115.13</v>
       </c>
       <c r="D4">
         <v>52.09</v>
@@ -556,7 +556,7 @@
         <v>882.46</v>
       </c>
       <c r="C5" s="1">
-        <v>522.08000000000004</v>
+        <v>522.17999999999995</v>
       </c>
       <c r="D5">
         <v>175.45</v>
@@ -579,7 +579,7 @@
         <v>565.04999999999995</v>
       </c>
       <c r="C6" s="1">
-        <v>324.58999999999997</v>
+        <v>324.61</v>
       </c>
       <c r="D6">
         <v>215.4</v>
@@ -602,7 +602,7 @@
         <v>622.04</v>
       </c>
       <c r="C7" s="1">
-        <v>216.21</v>
+        <v>216.05</v>
       </c>
       <c r="D7">
         <v>114.22</v>
@@ -625,7 +625,7 @@
         <v>811.71</v>
       </c>
       <c r="C8" s="1">
-        <v>292.24</v>
+        <v>292.12</v>
       </c>
       <c r="D8">
         <v>58.81</v>
@@ -648,7 +648,7 @@
         <v>545.23</v>
       </c>
       <c r="C9" s="1">
-        <v>143.21</v>
+        <v>143.27000000000001</v>
       </c>
       <c r="D9">
         <v>32.14</v>
@@ -671,7 +671,7 @@
         <v>1465.26</v>
       </c>
       <c r="C10" s="1">
-        <v>591.26</v>
+        <v>591.41999999999996</v>
       </c>
       <c r="D10">
         <v>316.95</v>
@@ -694,7 +694,7 @@
         <v>698.72</v>
       </c>
       <c r="C11" s="1">
-        <v>71.8</v>
+        <v>71.739999999999995</v>
       </c>
       <c r="D11">
         <v>37.49</v>
@@ -717,7 +717,7 @@
         <v>1105.96</v>
       </c>
       <c r="C12" s="1">
-        <v>622.82000000000005</v>
+        <v>623.35</v>
       </c>
       <c r="D12">
         <v>189.84</v>
@@ -740,7 +740,7 @@
         <v>1229.6099999999999</v>
       </c>
       <c r="C13" s="1">
-        <v>514.92999999999995</v>
+        <v>514.83000000000004</v>
       </c>
       <c r="D13">
         <v>235.72</v>
@@ -763,7 +763,7 @@
         <v>1260.79</v>
       </c>
       <c r="C14" s="1">
-        <v>479.9</v>
+        <v>479.63</v>
       </c>
       <c r="D14">
         <v>293.14</v>
@@ -786,7 +786,7 @@
         <v>701.72</v>
       </c>
       <c r="C15" s="1">
-        <v>384.46</v>
+        <v>384.49</v>
       </c>
       <c r="D15">
         <v>163.33000000000001</v>
@@ -809,7 +809,7 @@
         <v>749.29</v>
       </c>
       <c r="C16" s="1">
-        <v>228.68</v>
+        <v>228.81</v>
       </c>
       <c r="D16">
         <v>116.54</v>
@@ -832,7 +832,7 @@
         <v>1124.3499999999999</v>
       </c>
       <c r="C17" s="1">
-        <v>278.63</v>
+        <v>278.41000000000003</v>
       </c>
       <c r="D17">
         <v>149.82</v>
@@ -855,7 +855,7 @@
         <v>1392.56</v>
       </c>
       <c r="C18" s="1">
-        <v>514.79</v>
+        <v>515.04999999999995</v>
       </c>
       <c r="D18">
         <v>250</v>
@@ -878,7 +878,7 @@
         <v>1318.01</v>
       </c>
       <c r="C19" s="1">
-        <v>699.03</v>
+        <v>699.14</v>
       </c>
       <c r="D19">
         <v>315.56</v>
@@ -901,7 +901,7 @@
         <v>1192.44</v>
       </c>
       <c r="C20" s="1">
-        <v>279.87</v>
+        <v>279.77</v>
       </c>
       <c r="D20">
         <v>200.69</v>
@@ -924,7 +924,7 @@
         <v>753.92</v>
       </c>
       <c r="C21" s="1">
-        <v>168.45</v>
+        <v>168.35</v>
       </c>
       <c r="D21">
         <v>80.45</v>
@@ -947,7 +947,7 @@
         <v>766.78</v>
       </c>
       <c r="C22" s="1">
-        <v>451.1</v>
+        <v>451.14</v>
       </c>
       <c r="D22">
         <v>176.06</v>
@@ -970,7 +970,7 @@
         <v>989.45</v>
       </c>
       <c r="C23" s="1">
-        <v>586.57000000000005</v>
+        <v>587.17999999999995</v>
       </c>
       <c r="D23">
         <v>200.64</v>
@@ -993,7 +993,7 @@
         <v>742.16</v>
       </c>
       <c r="C24" s="1">
-        <v>372.25</v>
+        <v>372.12</v>
       </c>
       <c r="D24">
         <v>154.43</v>
@@ -1016,7 +1016,7 @@
         <v>820.78</v>
       </c>
       <c r="C25" s="1">
-        <v>158.62</v>
+        <v>158.55000000000001</v>
       </c>
       <c r="D25">
         <v>47.87</v>
@@ -1039,7 +1039,7 @@
         <v>1211.1500000000001</v>
       </c>
       <c r="C26" s="1">
-        <v>611.33000000000004</v>
+        <v>611.67999999999995</v>
       </c>
       <c r="D26">
         <v>123.73</v>
@@ -1062,7 +1062,7 @@
         <v>1175.69</v>
       </c>
       <c r="C27" s="1">
-        <v>549.76</v>
+        <v>550.01</v>
       </c>
       <c r="D27">
         <v>244.74</v>
@@ -1085,7 +1085,7 @@
         <v>674.95</v>
       </c>
       <c r="C28" s="1">
-        <v>398.96</v>
+        <v>398.63</v>
       </c>
       <c r="D28">
         <v>79.14</v>
@@ -1108,7 +1108,7 @@
         <v>688.71</v>
       </c>
       <c r="C29" s="1">
-        <v>164.9</v>
+        <v>164.75</v>
       </c>
       <c r="D29">
         <v>38.32</v>
@@ -1131,7 +1131,7 @@
         <v>1142.03</v>
       </c>
       <c r="C30" s="1">
-        <v>162.25</v>
+        <v>162.13</v>
       </c>
       <c r="D30">
         <v>56.57</v>
@@ -1154,7 +1154,7 @@
         <v>1151.96</v>
       </c>
       <c r="C31" s="1">
-        <v>244.37</v>
+        <v>244.38</v>
       </c>
       <c r="D31">
         <v>129.68</v>
@@ -1177,7 +1177,7 @@
         <v>866.47</v>
       </c>
       <c r="C32" s="1">
-        <v>409.05</v>
+        <v>408.79</v>
       </c>
       <c r="D32">
         <v>110.16</v>
@@ -1200,7 +1200,7 @@
         <v>986.74</v>
       </c>
       <c r="C33" s="1">
-        <v>545.72</v>
+        <v>545.51</v>
       </c>
       <c r="D33">
         <v>237.17</v>
@@ -1223,7 +1223,7 @@
         <v>695.24</v>
       </c>
       <c r="C34" s="1">
-        <v>320.66000000000003</v>
+        <v>320.73</v>
       </c>
       <c r="D34">
         <v>111.6</v>
@@ -1246,7 +1246,7 @@
         <v>1072.29</v>
       </c>
       <c r="C35" s="1">
-        <v>632.83000000000004</v>
+        <v>632.58000000000004</v>
       </c>
       <c r="D35">
         <v>371.23</v>
@@ -1269,7 +1269,7 @@
         <v>816.92</v>
       </c>
       <c r="C36" s="1">
-        <v>150.91999999999999</v>
+        <v>151.01</v>
       </c>
       <c r="D36">
         <v>55.2</v>
@@ -1292,7 +1292,7 @@
         <v>754.16</v>
       </c>
       <c r="C37" s="1">
-        <v>186.77</v>
+        <v>186.66</v>
       </c>
       <c r="D37">
         <v>100.42</v>
@@ -1315,7 +1315,7 @@
         <v>796.51</v>
       </c>
       <c r="C38" s="1">
-        <v>246.83</v>
+        <v>246.94</v>
       </c>
       <c r="D38">
         <v>171.59</v>
@@ -1338,7 +1338,7 @@
         <v>838</v>
       </c>
       <c r="C39" s="1">
-        <v>241.17</v>
+        <v>241.28</v>
       </c>
       <c r="D39">
         <v>142.77000000000001</v>
@@ -1361,7 +1361,7 @@
         <v>655.04</v>
       </c>
       <c r="C40" s="1">
-        <v>387.08</v>
+        <v>386.91</v>
       </c>
       <c r="D40">
         <v>309.45999999999998</v>
@@ -1384,7 +1384,7 @@
         <v>771.54</v>
       </c>
       <c r="C41" s="1">
-        <v>449.52</v>
+        <v>449.42</v>
       </c>
       <c r="D41">
         <v>270.14</v>
@@ -1407,7 +1407,7 @@
         <v>1137.43</v>
       </c>
       <c r="C42" s="1">
-        <v>526.67999999999995</v>
+        <v>527.05999999999995</v>
       </c>
       <c r="D42">
         <v>370.73</v>
@@ -1430,7 +1430,7 @@
         <v>1244.04</v>
       </c>
       <c r="C43" s="1">
-        <v>280.44</v>
+        <v>280.41000000000003</v>
       </c>
       <c r="D43">
         <v>108.27</v>
@@ -1453,7 +1453,7 @@
         <v>908.95</v>
       </c>
       <c r="C44" s="1">
-        <v>169.65</v>
+        <v>169.61</v>
       </c>
       <c r="D44">
         <v>56.5</v>
@@ -1476,7 +1476,7 @@
         <v>1138.27</v>
       </c>
       <c r="C45" s="1">
-        <v>407.9</v>
+        <v>407.92</v>
       </c>
       <c r="D45">
         <v>59.01</v>
@@ -1499,7 +1499,7 @@
         <v>747.73</v>
       </c>
       <c r="C46" s="1">
-        <v>207.86</v>
+        <v>207.71</v>
       </c>
       <c r="D46">
         <v>152.02000000000001</v>
@@ -1522,7 +1522,7 @@
         <v>517.16</v>
       </c>
       <c r="C47" s="1">
-        <v>249.11</v>
+        <v>249.44</v>
       </c>
       <c r="D47">
         <v>93.51</v>
@@ -1545,7 +1545,7 @@
         <v>898.5</v>
       </c>
       <c r="C48" s="1">
-        <v>366.52</v>
+        <v>366.57</v>
       </c>
       <c r="D48">
         <v>127.27</v>
@@ -1568,7 +1568,7 @@
         <v>1039.3800000000001</v>
       </c>
       <c r="C49" s="1">
-        <v>459.39</v>
+        <v>456.87</v>
       </c>
       <c r="D49">
         <v>48.19</v>
@@ -1591,7 +1591,7 @@
         <v>1085.78</v>
       </c>
       <c r="C50" s="1">
-        <v>619.02</v>
+        <v>620.14</v>
       </c>
       <c r="D50">
         <v>146.11000000000001</v>
@@ -1614,7 +1614,7 @@
         <v>1125.94</v>
       </c>
       <c r="C51" s="1">
-        <v>574.47</v>
+        <v>574.36</v>
       </c>
       <c r="D51">
         <v>280.35000000000002</v>
@@ -1637,7 +1637,7 @@
         <v>600.78</v>
       </c>
       <c r="C52" s="1">
-        <v>65.55</v>
+        <v>65.510000000000005</v>
       </c>
       <c r="D52">
         <v>34.56</v>
@@ -1660,7 +1660,7 @@
         <v>840.62</v>
       </c>
       <c r="C53" s="1">
-        <v>193.64</v>
+        <v>193.62</v>
       </c>
       <c r="D53">
         <v>93.7</v>
@@ -1683,7 +1683,7 @@
         <v>1377.47</v>
       </c>
       <c r="C54" s="1">
-        <v>644.02</v>
+        <v>644.12</v>
       </c>
       <c r="D54">
         <v>445.44</v>
@@ -1706,7 +1706,7 @@
         <v>1231.6500000000001</v>
       </c>
       <c r="C55" s="1">
-        <v>201.8</v>
+        <v>201.62</v>
       </c>
       <c r="D55">
         <v>44.93</v>
@@ -1729,7 +1729,7 @@
         <v>738.6</v>
       </c>
       <c r="C56" s="1">
-        <v>324.93</v>
+        <v>324.95</v>
       </c>
       <c r="D56">
         <v>118.67</v>
@@ -1752,7 +1752,7 @@
         <v>820.05</v>
       </c>
       <c r="C57" s="1">
-        <v>449.19</v>
+        <v>451.18</v>
       </c>
       <c r="D57">
         <v>33.76</v>
@@ -1775,7 +1775,7 @@
         <v>854.91</v>
       </c>
       <c r="C58" s="1">
-        <v>494.48</v>
+        <v>494.01</v>
       </c>
       <c r="D58">
         <v>171.39</v>
@@ -1798,7 +1798,7 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="C59" s="1">
-        <v>620.91</v>
+        <v>620.42999999999995</v>
       </c>
       <c r="D59">
         <v>121.12</v>
@@ -1821,7 +1821,7 @@
         <v>941.53</v>
       </c>
       <c r="C60" s="1">
-        <v>512.04999999999995</v>
+        <v>511.63</v>
       </c>
       <c r="D60">
         <v>262.23</v>
@@ -1844,7 +1844,7 @@
         <v>1338.48</v>
       </c>
       <c r="C61" s="1">
-        <v>419.01</v>
+        <v>419.16</v>
       </c>
       <c r="D61">
         <v>115.37</v>
@@ -1866,7 +1866,7 @@
       <c r="B62">
         <v>581.35</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="1">
         <v>82.8</v>
       </c>
       <c r="D62">
@@ -1889,7 +1889,7 @@
       <c r="B63">
         <v>877.99</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>397.33</v>
       </c>
       <c r="D63">
@@ -1912,7 +1912,7 @@
       <c r="B64">
         <v>511.35</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>170.96</v>
       </c>
       <c r="D64">
@@ -1935,7 +1935,7 @@
       <c r="B65">
         <v>737.51</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>221.33</v>
       </c>
       <c r="D65">
@@ -1958,7 +1958,7 @@
       <c r="B66">
         <v>1463.22</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="1">
         <v>155.21</v>
       </c>
       <c r="D66">
@@ -1981,7 +1981,7 @@
       <c r="B67">
         <v>752.99</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>337.12</v>
       </c>
       <c r="D67">
@@ -2004,7 +2004,7 @@
       <c r="B68">
         <v>1127.56</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="1">
         <v>442.18</v>
       </c>
       <c r="D68">
@@ -2027,7 +2027,7 @@
       <c r="B69">
         <v>688.12</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="1">
         <v>228.35</v>
       </c>
       <c r="D69">
@@ -2050,7 +2050,7 @@
       <c r="B70">
         <v>759.95</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
         <v>248.22</v>
       </c>
       <c r="D70">
@@ -2073,7 +2073,7 @@
       <c r="B71">
         <v>1410.93</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
         <v>721.36</v>
       </c>
       <c r="D71">
@@ -2096,7 +2096,7 @@
       <c r="B72">
         <v>582.75</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="1">
         <v>313.70999999999998</v>
       </c>
       <c r="D72">
@@ -2119,7 +2119,7 @@
       <c r="B73">
         <v>876.74</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
         <v>416.27</v>
       </c>
       <c r="D73">
@@ -2142,7 +2142,7 @@
       <c r="B74">
         <v>968.69</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
         <v>297.79000000000002</v>
       </c>
       <c r="D74">
@@ -2165,7 +2165,7 @@
       <c r="B75">
         <v>1226.1199999999999</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>586.75</v>
       </c>
       <c r="D75">
@@ -2188,7 +2188,7 @@
       <c r="B76">
         <v>1454.05</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>586.11</v>
       </c>
       <c r="D76">
@@ -2211,7 +2211,7 @@
       <c r="B77">
         <v>998.17</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
         <v>337.48</v>
       </c>
       <c r="D77">
@@ -2234,7 +2234,7 @@
       <c r="B78">
         <v>1060.94</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>571.13</v>
       </c>
       <c r="D78">
@@ -2257,7 +2257,7 @@
       <c r="B79">
         <v>1305.04</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="1">
         <v>719.83</v>
       </c>
       <c r="D79">
@@ -2280,7 +2280,7 @@
       <c r="B80">
         <v>892.24</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>284.39</v>
       </c>
       <c r="D80">
@@ -2303,7 +2303,7 @@
       <c r="B81">
         <v>1362.36</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
         <v>783.03</v>
       </c>
       <c r="D81">
@@ -2326,7 +2326,7 @@
       <c r="B82">
         <v>566.24</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>69.61</v>
       </c>
       <c r="D82">
@@ -2349,7 +2349,7 @@
       <c r="B83">
         <v>960.12</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
         <v>376.73</v>
       </c>
       <c r="D83">
@@ -2372,7 +2372,7 @@
       <c r="B84">
         <v>845.67</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>463.76</v>
       </c>
       <c r="D84">
@@ -2395,7 +2395,7 @@
       <c r="B85">
         <v>531.79999999999995</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>199.09</v>
       </c>
       <c r="D85">
@@ -2418,7 +2418,7 @@
       <c r="B86">
         <v>1003.42</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>446.72</v>
       </c>
       <c r="D86">
@@ -2441,7 +2441,7 @@
       <c r="B87">
         <v>1097.28</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="1">
         <v>650.83000000000004</v>
       </c>
       <c r="D87">
@@ -2464,7 +2464,7 @@
       <c r="B88">
         <v>868.91</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="1">
         <v>287.83999999999997</v>
       </c>
       <c r="D88">
@@ -2487,7 +2487,7 @@
       <c r="B89">
         <v>1032.1099999999999</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>158.52000000000001</v>
       </c>
       <c r="D89">
@@ -2510,7 +2510,7 @@
       <c r="B90">
         <v>1237.4100000000001</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>236.52</v>
       </c>
       <c r="D90">
@@ -2533,7 +2533,7 @@
       <c r="B91">
         <v>1093.5899999999999</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="1">
         <v>480.69</v>
       </c>
       <c r="D91">
@@ -2556,7 +2556,7 @@
       <c r="B92">
         <v>1057.74</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>415.98</v>
       </c>
       <c r="D92">
@@ -2579,7 +2579,7 @@
       <c r="B93">
         <v>856.1</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="1">
         <v>507.89</v>
       </c>
       <c r="D93">
@@ -2602,7 +2602,7 @@
       <c r="B94">
         <v>1350.82</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="1">
         <v>194.44</v>
       </c>
       <c r="D94">
@@ -2625,7 +2625,7 @@
       <c r="B95">
         <v>1365.51</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>694.41</v>
       </c>
       <c r="D95">
@@ -2648,7 +2648,7 @@
       <c r="B96">
         <v>1218.46</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>447.81</v>
       </c>
       <c r="D96">
@@ -2671,7 +2671,7 @@
       <c r="B97">
         <v>614.84</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="1">
         <v>249.2</v>
       </c>
       <c r="D97">
@@ -2694,7 +2694,7 @@
       <c r="B98">
         <v>820.64</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="1">
         <v>325.75</v>
       </c>
       <c r="D98">
@@ -2717,7 +2717,7 @@
       <c r="B99">
         <v>587.87</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="1">
         <v>99.59</v>
       </c>
       <c r="D99">
@@ -2740,7 +2740,7 @@
       <c r="B100">
         <v>848.87</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>479.41</v>
       </c>
       <c r="D100">
@@ -2763,7 +2763,7 @@
       <c r="B101">
         <v>879.23</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>495.2</v>
       </c>
       <c r="D101">
@@ -2786,7 +2786,7 @@
       <c r="B102">
         <v>1295.27</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>260.11</v>
       </c>
       <c r="D102">
@@ -2809,7 +2809,7 @@
       <c r="B103">
         <v>816.2</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
         <v>321.70999999999998</v>
       </c>
       <c r="D103">
@@ -2832,7 +2832,7 @@
       <c r="B104">
         <v>1124.0999999999999</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="1">
         <v>415.79</v>
       </c>
       <c r="D104">
@@ -2855,7 +2855,7 @@
       <c r="B105">
         <v>1406.47</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="1">
         <v>579.63</v>
       </c>
       <c r="D105">
@@ -2878,7 +2878,7 @@
       <c r="B106">
         <v>639.27</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="1">
         <v>317.73</v>
       </c>
       <c r="D106">
@@ -2901,7 +2901,7 @@
       <c r="B107">
         <v>1206.98</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="1">
         <v>590.55999999999995</v>
       </c>
       <c r="D107">
@@ -2924,7 +2924,7 @@
       <c r="B108">
         <v>1376.77</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="1">
         <v>373.16</v>
       </c>
       <c r="D108">
@@ -2947,7 +2947,7 @@
       <c r="B109">
         <v>1039.8599999999999</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="1">
         <v>356.86</v>
       </c>
       <c r="D109">
@@ -2970,7 +2970,7 @@
       <c r="B110">
         <v>1193.95</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="1">
         <v>443.39</v>
       </c>
       <c r="D110">
@@ -2993,7 +2993,7 @@
       <c r="B111">
         <v>1447.28</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
         <v>255.7</v>
       </c>
       <c r="D111">
@@ -3016,7 +3016,7 @@
       <c r="B112">
         <v>1092.96</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="1">
         <v>165.15</v>
       </c>
       <c r="D112">
@@ -3039,7 +3039,7 @@
       <c r="B113">
         <v>568.91999999999996</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="1">
         <v>78.89</v>
       </c>
       <c r="D113">
@@ -3062,7 +3062,7 @@
       <c r="B114">
         <v>613.24</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="1">
         <v>363.29</v>
       </c>
       <c r="D114">
@@ -3085,7 +3085,7 @@
       <c r="B115">
         <v>879.31</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="1">
         <v>415.14</v>
       </c>
       <c r="D115">
@@ -3108,7 +3108,7 @@
       <c r="B116">
         <v>898.17</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="1">
         <v>331.15</v>
       </c>
       <c r="D116">
@@ -3131,7 +3131,7 @@
       <c r="B117">
         <v>532.85</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="1">
         <v>296.45999999999998</v>
       </c>
       <c r="D117">
@@ -3154,7 +3154,7 @@
       <c r="B118">
         <v>1414.85</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="1">
         <v>397.85</v>
       </c>
       <c r="D118">
@@ -3177,7 +3177,7 @@
       <c r="B119">
         <v>958.99</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="1">
         <v>363.12</v>
       </c>
       <c r="D119">
@@ -3200,7 +3200,7 @@
       <c r="B120">
         <v>809.94</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="1">
         <v>241.89</v>
       </c>
       <c r="D120">
@@ -3223,7 +3223,7 @@
       <c r="B121">
         <v>972.07</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="1">
         <v>371.74</v>
       </c>
       <c r="D121">
@@ -3246,7 +3246,7 @@
       <c r="B122">
         <v>1034.46</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="1">
         <v>352.28</v>
       </c>
       <c r="D122">
@@ -3269,7 +3269,7 @@
       <c r="B123">
         <v>873.31</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="1">
         <v>205.55</v>
       </c>
       <c r="D123">
@@ -3292,7 +3292,7 @@
       <c r="B124">
         <v>1339.79</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="1">
         <v>714.77</v>
       </c>
       <c r="D124">
@@ -3315,7 +3315,7 @@
       <c r="B125">
         <v>1299.92</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="1">
         <v>246.04</v>
       </c>
       <c r="D125">
@@ -3338,7 +3338,7 @@
       <c r="B126">
         <v>1462.65</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="1">
         <v>836.94</v>
       </c>
       <c r="D126">
@@ -3361,7 +3361,7 @@
       <c r="B127">
         <v>707.89</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="1">
         <v>80.180000000000007</v>
       </c>
       <c r="D127">
@@ -3384,7 +3384,7 @@
       <c r="B128">
         <v>1410.62</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="1">
         <v>581.71</v>
       </c>
       <c r="D128">
@@ -3407,7 +3407,7 @@
       <c r="B129">
         <v>936.13</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="1">
         <v>231.44</v>
       </c>
       <c r="D129">
@@ -3430,7 +3430,7 @@
       <c r="B130">
         <v>1065.78</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="1">
         <v>631.66999999999996</v>
       </c>
       <c r="D130">
@@ -3453,7 +3453,7 @@
       <c r="B131">
         <v>1133.48</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="1">
         <v>259.5</v>
       </c>
       <c r="D131">
@@ -3476,7 +3476,7 @@
       <c r="B132">
         <v>1400.57</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="1">
         <v>624.11</v>
       </c>
       <c r="D132">
@@ -3499,7 +3499,7 @@
       <c r="B133">
         <v>1054.18</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="1">
         <v>448.77</v>
       </c>
       <c r="D133">
@@ -3522,7 +3522,7 @@
       <c r="B134">
         <v>763.68</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="1">
         <v>178.13</v>
       </c>
       <c r="D134">
@@ -3545,7 +3545,7 @@
       <c r="B135">
         <v>918.77</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="1">
         <v>267.89</v>
       </c>
       <c r="D135">
@@ -3568,7 +3568,7 @@
       <c r="B136">
         <v>684.37</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="1">
         <v>99.35</v>
       </c>
       <c r="D136">
@@ -3591,7 +3591,7 @@
       <c r="B137">
         <v>797.12</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="1">
         <v>305.45999999999998</v>
       </c>
       <c r="D137">
@@ -3614,7 +3614,7 @@
       <c r="B138">
         <v>983.75</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="1">
         <v>231.14</v>
       </c>
       <c r="D138">
@@ -3637,7 +3637,7 @@
       <c r="B139">
         <v>606.6</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="1">
         <v>83.45</v>
       </c>
       <c r="D139">
@@ -3660,7 +3660,7 @@
       <c r="B140">
         <v>959.68</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="1">
         <v>132.4</v>
       </c>
       <c r="D140">
@@ -3683,7 +3683,7 @@
       <c r="B141">
         <v>636.82000000000005</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="1">
         <v>366.25</v>
       </c>
       <c r="D141">
@@ -3706,7 +3706,7 @@
       <c r="B142">
         <v>1232.22</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="1">
         <v>620.15</v>
       </c>
       <c r="D142">
@@ -3729,7 +3729,7 @@
       <c r="B143">
         <v>1487.67</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="1">
         <v>850.99</v>
       </c>
       <c r="D143">
@@ -3752,7 +3752,7 @@
       <c r="B144">
         <v>1067.95</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="1">
         <v>595.64</v>
       </c>
       <c r="D144">
@@ -3775,7 +3775,7 @@
       <c r="B145">
         <v>1344.55</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="1">
         <v>348.98</v>
       </c>
       <c r="D145">
@@ -3798,7 +3798,7 @@
       <c r="B146">
         <v>1060.68</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="1">
         <v>361.19</v>
       </c>
       <c r="D146">
@@ -3821,7 +3821,7 @@
       <c r="B147">
         <v>1038.4000000000001</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="1">
         <v>447.37</v>
       </c>
       <c r="D147">
@@ -3844,7 +3844,7 @@
       <c r="B148">
         <v>732.96</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="1">
         <v>82.24</v>
       </c>
       <c r="D148">
@@ -3867,7 +3867,7 @@
       <c r="B149">
         <v>570.03</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="1">
         <v>59.71</v>
       </c>
       <c r="D149">
@@ -3890,7 +3890,7 @@
       <c r="B150">
         <v>1127.51</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="1">
         <v>605.29</v>
       </c>
       <c r="D150">
@@ -3913,7 +3913,7 @@
       <c r="B151">
         <v>610.47</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="1">
         <v>169.29</v>
       </c>
       <c r="D151">
@@ -3936,7 +3936,7 @@
       <c r="B152">
         <v>777.27</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="1">
         <v>431.51</v>
       </c>
       <c r="D152">
@@ -3959,7 +3959,7 @@
       <c r="B153">
         <v>917.58</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="1">
         <v>495.09</v>
       </c>
       <c r="D153">
@@ -3982,7 +3982,7 @@
       <c r="B154">
         <v>1243.3499999999999</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="1">
         <v>164.74</v>
       </c>
       <c r="D154">
@@ -4005,7 +4005,7 @@
       <c r="B155">
         <v>686.44</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="1">
         <v>336.21</v>
       </c>
       <c r="D155">
@@ -4028,7 +4028,7 @@
       <c r="B156">
         <v>1018.26</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="1">
         <v>405.92</v>
       </c>
       <c r="D156">
@@ -4051,7 +4051,7 @@
       <c r="B157">
         <v>1315.83</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="1">
         <v>279.25</v>
       </c>
       <c r="D157">
@@ -4074,7 +4074,7 @@
       <c r="B158">
         <v>591.49</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="1">
         <v>318.64999999999998</v>
       </c>
       <c r="D158">
@@ -4097,7 +4097,7 @@
       <c r="B159">
         <v>1235.21</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="1">
         <v>297.31</v>
       </c>
       <c r="D159">
@@ -4120,7 +4120,7 @@
       <c r="B160">
         <v>1032.5999999999999</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="1">
         <v>600.01</v>
       </c>
       <c r="D160">
@@ -4143,7 +4143,7 @@
       <c r="B161">
         <v>847.81</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="1">
         <v>372.2</v>
       </c>
       <c r="D161">
@@ -4166,7 +4166,7 @@
       <c r="B162">
         <v>1368.16</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="1">
         <v>304.61</v>
       </c>
       <c r="D162">
@@ -4189,7 +4189,7 @@
       <c r="B163">
         <v>658.61</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="1">
         <v>355.93</v>
       </c>
       <c r="D163">
@@ -4212,7 +4212,7 @@
       <c r="B164">
         <v>1319.95</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="1">
         <v>282.88</v>
       </c>
       <c r="D164">
@@ -4235,7 +4235,7 @@
       <c r="B165">
         <v>787.04</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="1">
         <v>321.48</v>
       </c>
       <c r="D165">
@@ -4258,7 +4258,7 @@
       <c r="B166">
         <v>509.07</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="1">
         <v>259.29000000000002</v>
       </c>
       <c r="D166">
@@ -4281,7 +4281,7 @@
       <c r="B167">
         <v>1132.6199999999999</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="1">
         <v>641.08000000000004</v>
       </c>
       <c r="D167">
@@ -4304,7 +4304,7 @@
       <c r="B168">
         <v>1447.3</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="1">
         <v>265.13</v>
       </c>
       <c r="D168">
@@ -4327,7 +4327,7 @@
       <c r="B169">
         <v>630.09</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="1">
         <v>301.89</v>
       </c>
       <c r="D169">
@@ -4350,7 +4350,7 @@
       <c r="B170">
         <v>752.51</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="1">
         <v>75.64</v>
       </c>
       <c r="D170">
@@ -4373,7 +4373,7 @@
       <c r="B171">
         <v>720.77</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="1">
         <v>101.77</v>
       </c>
       <c r="D171">
@@ -4396,7 +4396,7 @@
       <c r="B172">
         <v>1463.24</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="1">
         <v>169.23</v>
       </c>
       <c r="D172">
@@ -4419,7 +4419,7 @@
       <c r="B173">
         <v>1394.1</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="1">
         <v>299.7</v>
       </c>
       <c r="D173">
@@ -4442,7 +4442,7 @@
       <c r="B174">
         <v>1062.75</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="1">
         <v>356.84</v>
       </c>
       <c r="D174">
@@ -4465,7 +4465,7 @@
       <c r="B175">
         <v>1296.8</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="1">
         <v>320.42</v>
       </c>
       <c r="D175">
@@ -4488,7 +4488,7 @@
       <c r="B176">
         <v>501.23</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="1">
         <v>200.07</v>
       </c>
       <c r="D176">
@@ -4511,7 +4511,7 @@
       <c r="B177">
         <v>768.99</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="1">
         <v>383.56</v>
       </c>
       <c r="D177">
@@ -4534,7 +4534,7 @@
       <c r="B178">
         <v>1180.46</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="1">
         <v>351.51</v>
       </c>
       <c r="D178">
@@ -4557,7 +4557,7 @@
       <c r="B179">
         <v>604.92999999999995</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="1">
         <v>133.69999999999999</v>
       </c>
       <c r="D179">
@@ -4580,7 +4580,7 @@
       <c r="B180">
         <v>1202.46</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="1">
         <v>456.73</v>
       </c>
       <c r="D180">
@@ -4603,7 +4603,7 @@
       <c r="B181">
         <v>1324.51</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="1">
         <v>369.41</v>
       </c>
       <c r="D181">
@@ -4626,7 +4626,7 @@
       <c r="B182">
         <v>1300.5899999999999</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="1">
         <v>260.22000000000003</v>
       </c>
       <c r="D182">
@@ -4649,7 +4649,7 @@
       <c r="B183">
         <v>1125.3</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="1">
         <v>553.33000000000004</v>
       </c>
       <c r="D183">
@@ -4672,7 +4672,7 @@
       <c r="B184">
         <v>1097.48</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="1">
         <v>539.87</v>
       </c>
       <c r="D184">
@@ -4695,7 +4695,7 @@
       <c r="B185">
         <v>747.1</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="1">
         <v>134.31</v>
       </c>
       <c r="D185">
@@ -4718,7 +4718,7 @@
       <c r="B186">
         <v>1244.28</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="1">
         <v>666.83</v>
       </c>
       <c r="D186">
@@ -4741,7 +4741,7 @@
       <c r="B187">
         <v>1150.33</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="1">
         <v>229.8</v>
       </c>
       <c r="D187">
@@ -4764,7 +4764,7 @@
       <c r="B188">
         <v>1340.45</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="1">
         <v>250.79</v>
       </c>
       <c r="D188">
@@ -4787,7 +4787,7 @@
       <c r="B189">
         <v>1004.84</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="1">
         <v>373.45</v>
       </c>
       <c r="D189">
@@ -4810,7 +4810,7 @@
       <c r="B190">
         <v>986.67</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="1">
         <v>529.55999999999995</v>
       </c>
       <c r="D190">
@@ -4833,7 +4833,7 @@
       <c r="B191">
         <v>883.85</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="1">
         <v>294.24</v>
       </c>
       <c r="D191">
@@ -4856,7 +4856,7 @@
       <c r="B192">
         <v>1409.03</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="1">
         <v>267.49</v>
       </c>
       <c r="D192">
@@ -4879,7 +4879,7 @@
       <c r="B193">
         <v>905.02</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="1">
         <v>358.8</v>
       </c>
       <c r="D193">
@@ -4902,7 +4902,7 @@
       <c r="B194">
         <v>891.08</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="1">
         <v>521.02</v>
       </c>
       <c r="D194">
@@ -4925,7 +4925,7 @@
       <c r="B195">
         <v>737.03</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="1">
         <v>160.18</v>
       </c>
       <c r="D195">
@@ -4948,7 +4948,7 @@
       <c r="B196">
         <v>837</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="1">
         <v>430.59</v>
       </c>
       <c r="D196">
@@ -4971,7 +4971,7 @@
       <c r="B197">
         <v>879.36</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="1">
         <v>354.18</v>
       </c>
       <c r="D197">
@@ -4994,7 +4994,7 @@
       <c r="B198">
         <v>946.37</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="1">
         <v>503.57</v>
       </c>
       <c r="D198">
@@ -5017,7 +5017,7 @@
       <c r="B199">
         <v>1433.88</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="1">
         <v>370.05</v>
       </c>
       <c r="D199">
@@ -5040,7 +5040,7 @@
       <c r="B200">
         <v>979.9</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="1">
         <v>434.08</v>
       </c>
       <c r="D200">
@@ -5063,7 +5063,7 @@
       <c r="B201">
         <v>988.85</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="1">
         <v>428.6</v>
       </c>
       <c r="D201">
@@ -5086,7 +5086,7 @@
       <c r="B202">
         <v>701.85</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="1">
         <v>306.51</v>
       </c>
       <c r="D202">
@@ -5109,7 +5109,7 @@
       <c r="B203">
         <v>1161.6300000000001</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="1">
         <v>684.57</v>
       </c>
       <c r="D203">
@@ -5132,7 +5132,7 @@
       <c r="B204">
         <v>1368.9</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="1">
         <v>527.45000000000005</v>
       </c>
       <c r="D204">
@@ -5155,7 +5155,7 @@
       <c r="B205">
         <v>1166.97</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="1">
         <v>453.48</v>
       </c>
       <c r="D205">
@@ -5178,7 +5178,7 @@
       <c r="B206">
         <v>1366.44</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="1">
         <v>815.31</v>
       </c>
       <c r="D206">
@@ -5201,7 +5201,7 @@
       <c r="B207">
         <v>1167.5899999999999</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="1">
         <v>588.38</v>
       </c>
       <c r="D207">
@@ -5224,7 +5224,7 @@
       <c r="B208">
         <v>875.67</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="1">
         <v>217.55</v>
       </c>
       <c r="D208">
@@ -5247,7 +5247,7 @@
       <c r="B209">
         <v>888.56</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="1">
         <v>288.2</v>
       </c>
       <c r="D209">
@@ -5270,7 +5270,7 @@
       <c r="B210">
         <v>1087.06</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="1">
         <v>200.26</v>
       </c>
       <c r="D210">
@@ -5293,7 +5293,7 @@
       <c r="B211">
         <v>979.18</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="1">
         <v>110.47</v>
       </c>
       <c r="D211">
@@ -5316,7 +5316,7 @@
       <c r="B212">
         <v>746.07</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="1">
         <v>252.43</v>
       </c>
       <c r="D212">
@@ -5339,7 +5339,7 @@
       <c r="B213">
         <v>695.78</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="1">
         <v>72.209999999999994</v>
       </c>
       <c r="D213">
@@ -5362,7 +5362,7 @@
       <c r="B214">
         <v>880.07</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="1">
         <v>174.76</v>
       </c>
       <c r="D214">
@@ -5385,7 +5385,7 @@
       <c r="B215">
         <v>1429.61</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="1">
         <v>523.41999999999996</v>
       </c>
       <c r="D215">
@@ -5408,7 +5408,7 @@
       <c r="B216">
         <v>772.62</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="1">
         <v>237.02</v>
       </c>
       <c r="D216">
@@ -5431,7 +5431,7 @@
       <c r="B217">
         <v>1067.31</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="1">
         <v>243.65</v>
       </c>
       <c r="D217">
@@ -5454,7 +5454,7 @@
       <c r="B218">
         <v>873.51</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="1">
         <v>317.3</v>
       </c>
       <c r="D218">
@@ -5477,7 +5477,7 @@
       <c r="B219">
         <v>712.04</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="1">
         <v>288.73</v>
       </c>
       <c r="D219">
@@ -5500,7 +5500,7 @@
       <c r="B220">
         <v>736.87</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="1">
         <v>361.26</v>
       </c>
       <c r="D220">
@@ -5523,7 +5523,7 @@
       <c r="B221">
         <v>649.70000000000005</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="1">
         <v>202.69</v>
       </c>
       <c r="D221">
@@ -5546,7 +5546,7 @@
       <c r="B222">
         <v>716.74</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="1">
         <v>105.98</v>
       </c>
       <c r="D222">
@@ -5569,7 +5569,7 @@
       <c r="B223">
         <v>1094.48</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="1">
         <v>381.3</v>
       </c>
       <c r="D223">
@@ -5592,7 +5592,7 @@
       <c r="B224">
         <v>942.72</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="1">
         <v>304.39999999999998</v>
       </c>
       <c r="D224">
@@ -5615,7 +5615,7 @@
       <c r="B225">
         <v>1405.52</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="1">
         <v>683.52</v>
       </c>
       <c r="D225">
@@ -5638,7 +5638,7 @@
       <c r="B226">
         <v>823.37</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="1">
         <v>175.65</v>
       </c>
       <c r="D226">
@@ -5661,7 +5661,7 @@
       <c r="B227">
         <v>1180.1300000000001</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="1">
         <v>254.22</v>
       </c>
       <c r="D227">
@@ -5684,7 +5684,7 @@
       <c r="B228">
         <v>1161.8399999999999</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="1">
         <v>440.21</v>
       </c>
       <c r="D228">
@@ -5707,7 +5707,7 @@
       <c r="B229">
         <v>1134.96</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="1">
         <v>541.85</v>
       </c>
       <c r="D229">
@@ -5730,7 +5730,7 @@
       <c r="B230">
         <v>847.57</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="1">
         <v>366.54</v>
       </c>
       <c r="D230">
@@ -5753,7 +5753,7 @@
       <c r="B231">
         <v>1237.18</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="1">
         <v>599.16999999999996</v>
       </c>
       <c r="D231">
@@ -5776,7 +5776,7 @@
       <c r="B232">
         <v>1287.9000000000001</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="1">
         <v>685.61</v>
       </c>
       <c r="D232">
@@ -5799,7 +5799,7 @@
       <c r="B233">
         <v>587.64</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="1">
         <v>334.06</v>
       </c>
       <c r="D233">
@@ -5822,7 +5822,7 @@
       <c r="B234">
         <v>1100.5899999999999</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="1">
         <v>393.84</v>
       </c>
       <c r="D234">
@@ -5845,7 +5845,7 @@
       <c r="B235">
         <v>616.37</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="1">
         <v>313.56</v>
       </c>
       <c r="D235">
@@ -5868,7 +5868,7 @@
       <c r="B236">
         <v>1290.03</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="1">
         <v>325.52999999999997</v>
       </c>
       <c r="D236">
@@ -5891,7 +5891,7 @@
       <c r="B237">
         <v>1073.04</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="1">
         <v>607.73</v>
       </c>
       <c r="D237">
@@ -5914,7 +5914,7 @@
       <c r="B238">
         <v>1106.25</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="1">
         <v>533.66</v>
       </c>
       <c r="D238">
@@ -5937,7 +5937,7 @@
       <c r="B239">
         <v>525.80999999999995</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="1">
         <v>88.12</v>
       </c>
       <c r="D239">
@@ -5960,7 +5960,7 @@
       <c r="B240">
         <v>811.82</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="1">
         <v>286.63</v>
       </c>
       <c r="D240">
@@ -5983,7 +5983,7 @@
       <c r="B241">
         <v>864.8</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="1">
         <v>253.59</v>
       </c>
       <c r="D241">
@@ -6006,7 +6006,7 @@
       <c r="B242">
         <v>1254.25</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="1">
         <v>513.92999999999995</v>
       </c>
       <c r="D242">
@@ -6029,7 +6029,7 @@
       <c r="B243">
         <v>1118.05</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="1">
         <v>465.77</v>
       </c>
       <c r="D243">
@@ -6052,7 +6052,7 @@
       <c r="B244">
         <v>1123.9000000000001</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="1">
         <v>408.56</v>
       </c>
       <c r="D244">
@@ -6075,7 +6075,7 @@
       <c r="B245">
         <v>914.13</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="1">
         <v>469.65</v>
       </c>
       <c r="D245">
@@ -6098,7 +6098,7 @@
       <c r="B246">
         <v>633.79999999999995</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="1">
         <v>196.03</v>
       </c>
       <c r="D246">
@@ -6121,7 +6121,7 @@
       <c r="B247">
         <v>512.12</v>
       </c>
-      <c r="C247">
+      <c r="C247" s="1">
         <v>112.97</v>
       </c>
       <c r="D247">
@@ -6144,7 +6144,7 @@
       <c r="B248">
         <v>871.41</v>
       </c>
-      <c r="C248">
+      <c r="C248" s="1">
         <v>202.97</v>
       </c>
       <c r="D248">
@@ -6167,7 +6167,7 @@
       <c r="B249">
         <v>976.02</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="1">
         <v>281.04000000000002</v>
       </c>
       <c r="D249">
@@ -6190,7 +6190,7 @@
       <c r="B250">
         <v>633.15</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="1">
         <v>95.65</v>
       </c>
       <c r="D250">
@@ -6213,7 +6213,7 @@
       <c r="B251">
         <v>538.42999999999995</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="1">
         <v>296.61</v>
       </c>
       <c r="D251">
@@ -6236,7 +6236,7 @@
       <c r="B252">
         <v>950.12</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="1">
         <v>202.83</v>
       </c>
       <c r="D252">
@@ -6259,7 +6259,7 @@
       <c r="B253">
         <v>1246.21</v>
       </c>
-      <c r="C253">
+      <c r="C253" s="1">
         <v>535.27</v>
       </c>
       <c r="D253">
@@ -6282,7 +6282,7 @@
       <c r="B254">
         <v>1237.51</v>
       </c>
-      <c r="C254">
+      <c r="C254" s="1">
         <v>342.33</v>
       </c>
       <c r="D254">
@@ -6305,7 +6305,7 @@
       <c r="B255">
         <v>912.13</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="1">
         <v>341.87</v>
       </c>
       <c r="D255">
@@ -6328,7 +6328,7 @@
       <c r="B256">
         <v>1398.9</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="1">
         <v>687.2</v>
       </c>
       <c r="D256">
@@ -6351,7 +6351,7 @@
       <c r="B257">
         <v>1030.3</v>
       </c>
-      <c r="C257">
+      <c r="C257" s="1">
         <v>124.64</v>
       </c>
       <c r="D257">
@@ -6374,7 +6374,7 @@
       <c r="B258">
         <v>1101.8800000000001</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="1">
         <v>431.07</v>
       </c>
       <c r="D258">
@@ -6397,7 +6397,7 @@
       <c r="B259">
         <v>724.62</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="1">
         <v>207.3</v>
       </c>
       <c r="D259">
@@ -6420,7 +6420,7 @@
       <c r="B260">
         <v>740.69</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="1">
         <v>119.07</v>
       </c>
       <c r="D260">
@@ -6443,7 +6443,7 @@
       <c r="B261">
         <v>758.43</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="1">
         <v>282.14</v>
       </c>
       <c r="D261">
@@ -6466,7 +6466,7 @@
       <c r="B262">
         <v>553.86</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="1">
         <v>144.02000000000001</v>
       </c>
       <c r="D262">
@@ -6489,7 +6489,7 @@
       <c r="B263">
         <v>1225.98</v>
       </c>
-      <c r="C263">
+      <c r="C263" s="1">
         <v>623.89</v>
       </c>
       <c r="D263">
@@ -6512,7 +6512,7 @@
       <c r="B264">
         <v>913.42</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="1">
         <v>437.61</v>
       </c>
       <c r="D264">
@@ -6535,7 +6535,7 @@
       <c r="B265">
         <v>660.07</v>
       </c>
-      <c r="C265">
+      <c r="C265" s="1">
         <v>218.34</v>
       </c>
       <c r="D265">
@@ -6558,7 +6558,7 @@
       <c r="B266">
         <v>777.9</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="1">
         <v>153.22999999999999</v>
       </c>
       <c r="D266">
@@ -6581,7 +6581,7 @@
       <c r="B267">
         <v>688.02</v>
       </c>
-      <c r="C267">
+      <c r="C267" s="1">
         <v>191.06</v>
       </c>
       <c r="D267">
@@ -6604,7 +6604,7 @@
       <c r="B268">
         <v>1339.96</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="1">
         <v>691.88</v>
       </c>
       <c r="D268">
@@ -6627,7 +6627,7 @@
       <c r="B269">
         <v>1496.33</v>
       </c>
-      <c r="C269">
+      <c r="C269" s="1">
         <v>425.19</v>
       </c>
       <c r="D269">
@@ -6650,7 +6650,7 @@
       <c r="B270">
         <v>637.82000000000005</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="1">
         <v>275.23</v>
       </c>
       <c r="D270">
@@ -6673,7 +6673,7 @@
       <c r="B271">
         <v>592.99</v>
       </c>
-      <c r="C271">
+      <c r="C271" s="1">
         <v>233.7</v>
       </c>
       <c r="D271">
@@ -6696,7 +6696,7 @@
       <c r="B272">
         <v>1061.48</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="1">
         <v>403.71</v>
       </c>
       <c r="D272">
@@ -6719,7 +6719,7 @@
       <c r="B273">
         <v>1136.49</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="1">
         <v>198.32</v>
       </c>
       <c r="D273">
@@ -6742,7 +6742,7 @@
       <c r="B274">
         <v>1288.6099999999999</v>
       </c>
-      <c r="C274">
+      <c r="C274" s="1">
         <v>462.14</v>
       </c>
       <c r="D274">
@@ -6765,7 +6765,7 @@
       <c r="B275">
         <v>562.54</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="1">
         <v>281.66000000000003</v>
       </c>
       <c r="D275">
@@ -6788,7 +6788,7 @@
       <c r="B276">
         <v>921.25</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="1">
         <v>385.16</v>
       </c>
       <c r="D276">
@@ -6811,7 +6811,7 @@
       <c r="B277">
         <v>1450.31</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="1">
         <v>292.19</v>
       </c>
       <c r="D277">
@@ -6834,7 +6834,7 @@
       <c r="B278">
         <v>524.19000000000005</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="1">
         <v>270.39999999999998</v>
       </c>
       <c r="D278">
@@ -6857,7 +6857,7 @@
       <c r="B279">
         <v>961.73</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="1">
         <v>327.42</v>
       </c>
       <c r="D279">
@@ -6880,7 +6880,7 @@
       <c r="B280">
         <v>580.6</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="1">
         <v>269.38</v>
       </c>
       <c r="D280">
@@ -6903,7 +6903,7 @@
       <c r="B281">
         <v>631.35</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="1">
         <v>189.04</v>
       </c>
       <c r="D281">
@@ -6926,7 +6926,7 @@
       <c r="B282">
         <v>544.59</v>
       </c>
-      <c r="C282">
+      <c r="C282" s="1">
         <v>64.34</v>
       </c>
       <c r="D282">
@@ -6949,7 +6949,7 @@
       <c r="B283">
         <v>1344.79</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="1">
         <v>314.77</v>
       </c>
       <c r="D283">
@@ -6972,7 +6972,7 @@
       <c r="B284">
         <v>1406.44</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="1">
         <v>238.56</v>
       </c>
       <c r="D284">
@@ -6995,7 +6995,7 @@
       <c r="B285">
         <v>552.26</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="1">
         <v>170.87</v>
       </c>
       <c r="D285">
@@ -7018,7 +7018,7 @@
       <c r="B286">
         <v>644.97</v>
       </c>
-      <c r="C286">
+      <c r="C286" s="1">
         <v>298.35000000000002</v>
       </c>
       <c r="D286">
@@ -7041,7 +7041,7 @@
       <c r="B287">
         <v>1350.62</v>
       </c>
-      <c r="C287">
+      <c r="C287" s="1">
         <v>514.05999999999995</v>
       </c>
       <c r="D287">
@@ -7064,7 +7064,7 @@
       <c r="B288">
         <v>1042.55</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="1">
         <v>516.95000000000005</v>
       </c>
       <c r="D288">
@@ -7087,7 +7087,7 @@
       <c r="B289">
         <v>1445.7</v>
       </c>
-      <c r="C289">
+      <c r="C289" s="1">
         <v>758.97</v>
       </c>
       <c r="D289">
@@ -7110,7 +7110,7 @@
       <c r="B290">
         <v>1249.28</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="1">
         <v>306.44</v>
       </c>
       <c r="D290">
@@ -7133,7 +7133,7 @@
       <c r="B291">
         <v>664.71</v>
       </c>
-      <c r="C291">
+      <c r="C291" s="1">
         <v>176.22</v>
       </c>
       <c r="D291">
@@ -7156,7 +7156,7 @@
       <c r="B292">
         <v>1159.6300000000001</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="1">
         <v>209.67</v>
       </c>
       <c r="D292">
@@ -7179,7 +7179,7 @@
       <c r="B293">
         <v>565.20000000000005</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="1">
         <v>187.63</v>
       </c>
       <c r="D293">
@@ -7202,7 +7202,7 @@
       <c r="B294">
         <v>951.7</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="1">
         <v>284.26</v>
       </c>
       <c r="D294">
@@ -7225,7 +7225,7 @@
       <c r="B295">
         <v>1134.58</v>
       </c>
-      <c r="C295">
+      <c r="C295" s="1">
         <v>566.11</v>
       </c>
       <c r="D295">
@@ -7248,7 +7248,7 @@
       <c r="B296">
         <v>947.6</v>
       </c>
-      <c r="C296">
+      <c r="C296" s="1">
         <v>359.06</v>
       </c>
       <c r="D296">
@@ -7271,7 +7271,7 @@
       <c r="B297">
         <v>1232.6400000000001</v>
       </c>
-      <c r="C297">
+      <c r="C297" s="1">
         <v>628.88</v>
       </c>
       <c r="D297">
@@ -7294,7 +7294,7 @@
       <c r="B298">
         <v>1382.42</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="1">
         <v>693.7</v>
       </c>
       <c r="D298">
@@ -7317,7 +7317,7 @@
       <c r="B299">
         <v>927.49</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="1">
         <v>167.98</v>
       </c>
       <c r="D299">
@@ -7340,7 +7340,7 @@
       <c r="B300">
         <v>1322.96</v>
       </c>
-      <c r="C300">
+      <c r="C300" s="1">
         <v>271.04000000000002</v>
       </c>
       <c r="D300">
@@ -7363,7 +7363,7 @@
       <c r="B301">
         <v>1259.58</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="1">
         <v>748.23</v>
       </c>
       <c r="D301">
@@ -7386,7 +7386,7 @@
       <c r="B302">
         <v>1319.26</v>
       </c>
-      <c r="C302">
+      <c r="C302" s="1">
         <v>712.28</v>
       </c>
       <c r="D302">
@@ -7409,7 +7409,7 @@
       <c r="B303">
         <v>641.97</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="1">
         <v>175.88</v>
       </c>
       <c r="D303">
@@ -7432,7 +7432,7 @@
       <c r="B304">
         <v>1341.45</v>
       </c>
-      <c r="C304">
+      <c r="C304" s="1">
         <v>450.25</v>
       </c>
       <c r="D304">
@@ -7455,7 +7455,7 @@
       <c r="B305">
         <v>1181.67</v>
       </c>
-      <c r="C305">
+      <c r="C305" s="1">
         <v>216.91</v>
       </c>
       <c r="D305">
@@ -7478,7 +7478,7 @@
       <c r="B306">
         <v>1194.1500000000001</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="1">
         <v>425.51</v>
       </c>
       <c r="D306">
@@ -7501,7 +7501,7 @@
       <c r="B307">
         <v>1371.2</v>
       </c>
-      <c r="C307">
+      <c r="C307" s="1">
         <v>662.34</v>
       </c>
       <c r="D307">
@@ -7524,7 +7524,7 @@
       <c r="B308">
         <v>1374.23</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="1">
         <v>137.55000000000001</v>
       </c>
       <c r="D308">
@@ -7547,7 +7547,7 @@
       <c r="B309">
         <v>912.76</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="1">
         <v>457.46</v>
       </c>
       <c r="D309">
@@ -7570,7 +7570,7 @@
       <c r="B310">
         <v>1466.24</v>
       </c>
-      <c r="C310">
+      <c r="C310" s="1">
         <v>240.06</v>
       </c>
       <c r="D310">
@@ -7593,7 +7593,7 @@
       <c r="B311">
         <v>1462.81</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="1">
         <v>677.77</v>
       </c>
       <c r="D311">
@@ -7616,7 +7616,7 @@
       <c r="B312">
         <v>612.58000000000004</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="1">
         <v>276.79000000000002</v>
       </c>
       <c r="D312">
@@ -7639,7 +7639,7 @@
       <c r="B313">
         <v>1324.53</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="1">
         <v>181.62</v>
       </c>
       <c r="D313">
@@ -7662,7 +7662,7 @@
       <c r="B314">
         <v>1402.89</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="1">
         <v>738.11</v>
       </c>
       <c r="D314">
@@ -7685,7 +7685,7 @@
       <c r="B315">
         <v>1082.81</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="1">
         <v>647.21</v>
       </c>
       <c r="D315">
@@ -7708,7 +7708,7 @@
       <c r="B316">
         <v>720.23</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="1">
         <v>247.89</v>
       </c>
       <c r="D316">
@@ -7731,7 +7731,7 @@
       <c r="B317">
         <v>964.43</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="1">
         <v>162.76</v>
       </c>
       <c r="D317">
@@ -7754,7 +7754,7 @@
       <c r="B318">
         <v>1131.31</v>
       </c>
-      <c r="C318">
+      <c r="C318" s="1">
         <v>447.83</v>
       </c>
       <c r="D318">
@@ -7777,7 +7777,7 @@
       <c r="B319">
         <v>1470.77</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="1">
         <v>340.24</v>
       </c>
       <c r="D319">
@@ -7800,7 +7800,7 @@
       <c r="B320">
         <v>502.92</v>
       </c>
-      <c r="C320">
+      <c r="C320" s="1">
         <v>60.29</v>
       </c>
       <c r="D320">
@@ -7823,7 +7823,7 @@
       <c r="B321">
         <v>982.04</v>
       </c>
-      <c r="C321">
+      <c r="C321" s="1">
         <v>194.49</v>
       </c>
       <c r="D321">
@@ -7846,7 +7846,7 @@
       <c r="B322">
         <v>1037.01</v>
       </c>
-      <c r="C322">
+      <c r="C322" s="1">
         <v>546.57000000000005</v>
       </c>
       <c r="D322">
@@ -7869,7 +7869,7 @@
       <c r="B323">
         <v>1072.05</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="1">
         <v>382.01</v>
       </c>
       <c r="D323">
@@ -7892,7 +7892,7 @@
       <c r="B324">
         <v>784.56</v>
       </c>
-      <c r="C324">
+      <c r="C324" s="1">
         <v>399.42</v>
       </c>
       <c r="D324">
@@ -7915,7 +7915,7 @@
       <c r="B325">
         <v>894.58</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="1">
         <v>278.14</v>
       </c>
       <c r="D325">
@@ -7938,7 +7938,7 @@
       <c r="B326">
         <v>1174.6099999999999</v>
       </c>
-      <c r="C326">
+      <c r="C326" s="1">
         <v>291.73</v>
       </c>
       <c r="D326">
@@ -7961,7 +7961,7 @@
       <c r="B327">
         <v>1103.8</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="1">
         <v>489.31</v>
       </c>
       <c r="D327">
@@ -7984,7 +7984,7 @@
       <c r="B328">
         <v>592.28</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="1">
         <v>235.82</v>
       </c>
       <c r="D328">
@@ -8007,7 +8007,7 @@
       <c r="B329">
         <v>1168.57</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="1">
         <v>513.39</v>
       </c>
       <c r="D329">
@@ -8030,7 +8030,7 @@
       <c r="B330">
         <v>638.87</v>
       </c>
-      <c r="C330">
+      <c r="C330" s="1">
         <v>100.86</v>
       </c>
       <c r="D330">
@@ -8053,7 +8053,7 @@
       <c r="B331">
         <v>1033.97</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="1">
         <v>176.88</v>
       </c>
       <c r="D331">
@@ -8076,7 +8076,7 @@
       <c r="B332">
         <v>584.39</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="1">
         <v>175.13</v>
       </c>
       <c r="D332">
@@ -8099,7 +8099,7 @@
       <c r="B333">
         <v>887.39</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="1">
         <v>466.7</v>
       </c>
       <c r="D333">
@@ -8122,7 +8122,7 @@
       <c r="B334">
         <v>1090.29</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="1">
         <v>232.38</v>
       </c>
       <c r="D334">
@@ -8145,7 +8145,7 @@
       <c r="B335">
         <v>1082.2</v>
       </c>
-      <c r="C335">
+      <c r="C335" s="1">
         <v>309.06</v>
       </c>
       <c r="D335">
@@ -8168,7 +8168,7 @@
       <c r="B336">
         <v>666.86</v>
       </c>
-      <c r="C336">
+      <c r="C336" s="1">
         <v>210.24</v>
       </c>
       <c r="D336">
@@ -8191,7 +8191,7 @@
       <c r="B337">
         <v>885.87</v>
       </c>
-      <c r="C337">
+      <c r="C337" s="1">
         <v>439.27</v>
       </c>
       <c r="D337">
@@ -8214,7 +8214,7 @@
       <c r="B338">
         <v>1341.72</v>
       </c>
-      <c r="C338">
+      <c r="C338" s="1">
         <v>523.41999999999996</v>
       </c>
       <c r="D338">
@@ -8237,7 +8237,7 @@
       <c r="B339">
         <v>884.21</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="1">
         <v>105.66</v>
       </c>
       <c r="D339">
@@ -8260,7 +8260,7 @@
       <c r="B340">
         <v>813.21</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="1">
         <v>141.12</v>
       </c>
       <c r="D340">
@@ -8283,7 +8283,7 @@
       <c r="B341">
         <v>1388.4</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="1">
         <v>557.4</v>
       </c>
       <c r="D341">
@@ -8306,7 +8306,7 @@
       <c r="B342">
         <v>530.94000000000005</v>
       </c>
-      <c r="C342">
+      <c r="C342" s="1">
         <v>310.8</v>
       </c>
       <c r="D342">
@@ -8329,7 +8329,7 @@
       <c r="B343">
         <v>1333.65</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="1">
         <v>427.06</v>
       </c>
       <c r="D343">
@@ -8352,7 +8352,7 @@
       <c r="B344">
         <v>1007.45</v>
       </c>
-      <c r="C344">
+      <c r="C344" s="1">
         <v>441.96</v>
       </c>
       <c r="D344">
@@ -8375,7 +8375,7 @@
       <c r="B345">
         <v>944.04</v>
       </c>
-      <c r="C345">
+      <c r="C345" s="1">
         <v>390</v>
       </c>
       <c r="D345">
@@ -8398,7 +8398,7 @@
       <c r="B346">
         <v>800.49</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="1">
         <v>210.46</v>
       </c>
       <c r="D346">
@@ -8421,7 +8421,7 @@
       <c r="B347">
         <v>1043.02</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="1">
         <v>223.08</v>
       </c>
       <c r="D347">
@@ -8444,7 +8444,7 @@
       <c r="B348">
         <v>958.47</v>
       </c>
-      <c r="C348">
+      <c r="C348" s="1">
         <v>114.05</v>
       </c>
       <c r="D348">
@@ -8467,7 +8467,7 @@
       <c r="B349">
         <v>1444.04</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="1">
         <v>251.84</v>
       </c>
       <c r="D349">
@@ -8490,7 +8490,7 @@
       <c r="B350">
         <v>991.42</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="1">
         <v>358.12</v>
       </c>
       <c r="D350">
@@ -8513,7 +8513,7 @@
       <c r="B351">
         <v>1365.58</v>
       </c>
-      <c r="C351">
+      <c r="C351" s="1">
         <v>806.2</v>
       </c>
       <c r="D351">
@@ -8536,7 +8536,7 @@
       <c r="B352">
         <v>1306.5899999999999</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="1">
         <v>441.94</v>
       </c>
       <c r="D352">
@@ -8559,7 +8559,7 @@
       <c r="B353">
         <v>811.9</v>
       </c>
-      <c r="C353">
+      <c r="C353" s="1">
         <v>185.13</v>
       </c>
       <c r="D353">
@@ -8582,7 +8582,7 @@
       <c r="B354">
         <v>976.84</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="1">
         <v>433.58</v>
       </c>
       <c r="D354">
@@ -8605,7 +8605,7 @@
       <c r="B355">
         <v>833.41</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="1">
         <v>388.81</v>
       </c>
       <c r="D355">
@@ -8628,7 +8628,7 @@
       <c r="B356">
         <v>1176.82</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="1">
         <v>605.16</v>
       </c>
       <c r="D356">
@@ -8651,7 +8651,7 @@
       <c r="B357">
         <v>505.67</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="1">
         <v>287.49</v>
       </c>
       <c r="D357">
@@ -8674,7 +8674,7 @@
       <c r="B358">
         <v>1113.5999999999999</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="1">
         <v>160.69999999999999</v>
       </c>
       <c r="D358">
@@ -8697,7 +8697,7 @@
       <c r="B359">
         <v>1049.1300000000001</v>
       </c>
-      <c r="C359">
+      <c r="C359" s="1">
         <v>436.49</v>
       </c>
       <c r="D359">
@@ -8720,7 +8720,7 @@
       <c r="B360">
         <v>1022.58</v>
       </c>
-      <c r="C360">
+      <c r="C360" s="1">
         <v>255.42</v>
       </c>
       <c r="D360">
@@ -8743,7 +8743,7 @@
       <c r="B361">
         <v>1210.1099999999999</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="1">
         <v>524.49</v>
       </c>
       <c r="D361">
@@ -8766,7 +8766,7 @@
       <c r="B362">
         <v>522.03</v>
       </c>
-      <c r="C362">
+      <c r="C362" s="1">
         <v>204.44</v>
       </c>
       <c r="D362">
@@ -8789,7 +8789,7 @@
       <c r="B363">
         <v>1219.79</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="1">
         <v>650.72</v>
       </c>
       <c r="D363">
@@ -8812,7 +8812,7 @@
       <c r="B364">
         <v>1182.6199999999999</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="1">
         <v>261.32</v>
       </c>
       <c r="D364">
@@ -8835,7 +8835,7 @@
       <c r="B365">
         <v>1416.79</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="1">
         <v>652.19000000000005</v>
       </c>
       <c r="D365">
@@ -8858,7 +8858,7 @@
       <c r="B366">
         <v>1221.72</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="1">
         <v>288.05</v>
       </c>
       <c r="D366">
@@ -8881,7 +8881,7 @@
       <c r="B367">
         <v>562.69000000000005</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="1">
         <v>292.41000000000003</v>
       </c>
       <c r="D367">
@@ -8904,7 +8904,7 @@
       <c r="B368">
         <v>1430.89</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="1">
         <v>734.56</v>
       </c>
       <c r="D368">
@@ -8927,7 +8927,7 @@
       <c r="B369">
         <v>933.82</v>
       </c>
-      <c r="C369">
+      <c r="C369" s="1">
         <v>518.24</v>
       </c>
       <c r="D369">
@@ -8950,7 +8950,7 @@
       <c r="B370">
         <v>542.29</v>
       </c>
-      <c r="C370">
+      <c r="C370" s="1">
         <v>207.33</v>
       </c>
       <c r="D370">
@@ -8973,7 +8973,7 @@
       <c r="B371">
         <v>1166.3900000000001</v>
       </c>
-      <c r="C371">
+      <c r="C371" s="1">
         <v>680.03</v>
       </c>
       <c r="D371">
@@ -8996,7 +8996,7 @@
       <c r="B372">
         <v>605.36</v>
       </c>
-      <c r="C372">
+      <c r="C372" s="1">
         <v>297.18</v>
       </c>
       <c r="D372">
@@ -9019,7 +9019,7 @@
       <c r="B373">
         <v>975.97</v>
       </c>
-      <c r="C373">
+      <c r="C373" s="1">
         <v>151.75</v>
       </c>
       <c r="D373">
@@ -9042,7 +9042,7 @@
       <c r="B374">
         <v>686.02</v>
       </c>
-      <c r="C374">
+      <c r="C374" s="1">
         <v>257.97000000000003</v>
       </c>
       <c r="D374">
@@ -9065,7 +9065,7 @@
       <c r="B375">
         <v>1296.24</v>
       </c>
-      <c r="C375">
+      <c r="C375" s="1">
         <v>618.32000000000005</v>
       </c>
       <c r="D375">
@@ -9088,7 +9088,7 @@
       <c r="B376">
         <v>1238.5999999999999</v>
       </c>
-      <c r="C376">
+      <c r="C376" s="1">
         <v>319.33</v>
       </c>
       <c r="D376">
@@ -9111,7 +9111,7 @@
       <c r="B377">
         <v>543.01</v>
       </c>
-      <c r="C377">
+      <c r="C377" s="1">
         <v>235.36</v>
       </c>
       <c r="D377">
@@ -9134,7 +9134,7 @@
       <c r="B378">
         <v>1188.04</v>
       </c>
-      <c r="C378">
+      <c r="C378" s="1">
         <v>262.49</v>
       </c>
       <c r="D378">
@@ -9157,7 +9157,7 @@
       <c r="B379">
         <v>1095.1300000000001</v>
       </c>
-      <c r="C379">
+      <c r="C379" s="1">
         <v>114.95</v>
       </c>
       <c r="D379">
@@ -9180,7 +9180,7 @@
       <c r="B380">
         <v>811.86</v>
       </c>
-      <c r="C380">
+      <c r="C380" s="1">
         <v>395.37</v>
       </c>
       <c r="D380">
@@ -9203,7 +9203,7 @@
       <c r="B381">
         <v>681.74</v>
       </c>
-      <c r="C381">
+      <c r="C381" s="1">
         <v>216.63</v>
       </c>
       <c r="D381">
@@ -9226,7 +9226,7 @@
       <c r="B382">
         <v>1141.8599999999999</v>
       </c>
-      <c r="C382">
+      <c r="C382" s="1">
         <v>439.99</v>
       </c>
       <c r="D382">
@@ -9249,7 +9249,7 @@
       <c r="B383">
         <v>1329.76</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="1">
         <v>535.99</v>
       </c>
       <c r="D383">
@@ -9272,7 +9272,7 @@
       <c r="B384">
         <v>1210.1400000000001</v>
       </c>
-      <c r="C384">
+      <c r="C384" s="1">
         <v>688.19</v>
       </c>
       <c r="D384">
@@ -9295,7 +9295,7 @@
       <c r="B385">
         <v>739.16</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="1">
         <v>270.07</v>
       </c>
       <c r="D385">
@@ -9318,7 +9318,7 @@
       <c r="B386">
         <v>704.98</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="1">
         <v>326.27</v>
       </c>
       <c r="D386">
@@ -9341,7 +9341,7 @@
       <c r="B387">
         <v>1311.12</v>
       </c>
-      <c r="C387">
+      <c r="C387" s="1">
         <v>548.02</v>
       </c>
       <c r="D387">
@@ -9364,7 +9364,7 @@
       <c r="B388">
         <v>1447.4</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="1">
         <v>388.87</v>
       </c>
       <c r="D388">
@@ -9387,7 +9387,7 @@
       <c r="B389">
         <v>507.84</v>
       </c>
-      <c r="C389">
+      <c r="C389" s="1">
         <v>210.99</v>
       </c>
       <c r="D389">
@@ -9410,7 +9410,7 @@
       <c r="B390">
         <v>1261.0899999999999</v>
       </c>
-      <c r="C390">
+      <c r="C390" s="1">
         <v>349.49</v>
       </c>
       <c r="D390">
@@ -9433,7 +9433,7 @@
       <c r="B391">
         <v>665.75</v>
       </c>
-      <c r="C391">
+      <c r="C391" s="1">
         <v>214.88</v>
       </c>
       <c r="D391">
@@ -9456,7 +9456,7 @@
       <c r="B392">
         <v>1293.1400000000001</v>
       </c>
-      <c r="C392">
+      <c r="C392" s="1">
         <v>681.35</v>
       </c>
       <c r="D392">
@@ -9479,7 +9479,7 @@
       <c r="B393">
         <v>1419.39</v>
       </c>
-      <c r="C393">
+      <c r="C393" s="1">
         <v>266.91000000000003</v>
       </c>
       <c r="D393">
@@ -9502,7 +9502,7 @@
       <c r="B394">
         <v>1292.5999999999999</v>
       </c>
-      <c r="C394">
+      <c r="C394" s="1">
         <v>716.03</v>
       </c>
       <c r="D394">
@@ -9525,7 +9525,7 @@
       <c r="B395">
         <v>747.34</v>
       </c>
-      <c r="C395">
+      <c r="C395" s="1">
         <v>314.11</v>
       </c>
       <c r="D395">
@@ -9548,7 +9548,7 @@
       <c r="B396">
         <v>998.9</v>
       </c>
-      <c r="C396">
+      <c r="C396" s="1">
         <v>105.93</v>
       </c>
       <c r="D396">
@@ -9571,7 +9571,7 @@
       <c r="B397">
         <v>821.67</v>
       </c>
-      <c r="C397">
+      <c r="C397" s="1">
         <v>430.57</v>
       </c>
       <c r="D397">
@@ -9594,7 +9594,7 @@
       <c r="B398">
         <v>902.76</v>
       </c>
-      <c r="C398">
+      <c r="C398" s="1">
         <v>494.1</v>
       </c>
       <c r="D398">
@@ -9617,7 +9617,7 @@
       <c r="B399">
         <v>1135.44</v>
       </c>
-      <c r="C399">
+      <c r="C399" s="1">
         <v>165.05</v>
       </c>
       <c r="D399">
@@ -9640,7 +9640,7 @@
       <c r="B400">
         <v>857.12</v>
       </c>
-      <c r="C400">
+      <c r="C400" s="1">
         <v>423.22</v>
       </c>
       <c r="D400">
@@ -9663,7 +9663,7 @@
       <c r="B401">
         <v>1377.36</v>
       </c>
-      <c r="C401">
+      <c r="C401" s="1">
         <v>808.76</v>
       </c>
       <c r="D401">
@@ -9686,7 +9686,7 @@
       <c r="B402">
         <v>536.02</v>
       </c>
-      <c r="C402">
+      <c r="C402" s="1">
         <v>100.56</v>
       </c>
       <c r="D402">
@@ -9709,7 +9709,7 @@
       <c r="B403">
         <v>927.5</v>
       </c>
-      <c r="C403">
+      <c r="C403" s="1">
         <v>244.09</v>
       </c>
       <c r="D403">
@@ -9732,7 +9732,7 @@
       <c r="B404">
         <v>1392.56</v>
       </c>
-      <c r="C404">
+      <c r="C404" s="1">
         <v>431.31</v>
       </c>
       <c r="D404">
@@ -9755,7 +9755,7 @@
       <c r="B405">
         <v>795.69</v>
       </c>
-      <c r="C405">
+      <c r="C405" s="1">
         <v>315.81</v>
       </c>
       <c r="D405">
@@ -9778,7 +9778,7 @@
       <c r="B406">
         <v>1440.78</v>
       </c>
-      <c r="C406">
+      <c r="C406" s="1">
         <v>509.26</v>
       </c>
       <c r="D406">
@@ -9801,7 +9801,7 @@
       <c r="B407">
         <v>1324.79</v>
       </c>
-      <c r="C407">
+      <c r="C407" s="1">
         <v>474.05</v>
       </c>
       <c r="D407">
@@ -9824,7 +9824,7 @@
       <c r="B408">
         <v>537.57000000000005</v>
       </c>
-      <c r="C408">
+      <c r="C408" s="1">
         <v>88.13</v>
       </c>
       <c r="D408">
@@ -9847,7 +9847,7 @@
       <c r="B409">
         <v>700.56</v>
       </c>
-      <c r="C409">
+      <c r="C409" s="1">
         <v>141.37</v>
       </c>
       <c r="D409">
@@ -9870,7 +9870,7 @@
       <c r="B410">
         <v>1466.85</v>
       </c>
-      <c r="C410">
+      <c r="C410" s="1">
         <v>311.19</v>
       </c>
       <c r="D410">
@@ -9893,7 +9893,7 @@
       <c r="B411">
         <v>1212.6199999999999</v>
       </c>
-      <c r="C411">
+      <c r="C411" s="1">
         <v>616.48</v>
       </c>
       <c r="D411">
@@ -9916,7 +9916,7 @@
       <c r="B412">
         <v>1484.86</v>
       </c>
-      <c r="C412">
+      <c r="C412" s="1">
         <v>708.46</v>
       </c>
       <c r="D412">
@@ -9939,7 +9939,7 @@
       <c r="B413">
         <v>520.66999999999996</v>
       </c>
-      <c r="C413">
+      <c r="C413" s="1">
         <v>122.1</v>
       </c>
       <c r="D413">
@@ -9962,7 +9962,7 @@
       <c r="B414">
         <v>861.71</v>
       </c>
-      <c r="C414">
+      <c r="C414" s="1">
         <v>495.14</v>
       </c>
       <c r="D414">
@@ -9985,7 +9985,7 @@
       <c r="B415">
         <v>869.28</v>
       </c>
-      <c r="C415">
+      <c r="C415" s="1">
         <v>492.41</v>
       </c>
       <c r="D415">
@@ -10008,7 +10008,7 @@
       <c r="B416">
         <v>1303.52</v>
       </c>
-      <c r="C416">
+      <c r="C416" s="1">
         <v>209.89</v>
       </c>
       <c r="D416">
@@ -10031,7 +10031,7 @@
       <c r="B417">
         <v>1478.53</v>
       </c>
-      <c r="C417">
+      <c r="C417" s="1">
         <v>781.06</v>
       </c>
       <c r="D417">
@@ -10054,7 +10054,7 @@
       <c r="B418">
         <v>811.98</v>
       </c>
-      <c r="C418">
+      <c r="C418" s="1">
         <v>277.08999999999997</v>
       </c>
       <c r="D418">
@@ -10077,7 +10077,7 @@
       <c r="B419">
         <v>1470.26</v>
       </c>
-      <c r="C419">
+      <c r="C419" s="1">
         <v>468.76</v>
       </c>
       <c r="D419">
@@ -10100,7 +10100,7 @@
       <c r="B420">
         <v>1034.29</v>
       </c>
-      <c r="C420">
+      <c r="C420" s="1">
         <v>383.07</v>
       </c>
       <c r="D420">
@@ -10123,7 +10123,7 @@
       <c r="B421">
         <v>657.27</v>
       </c>
-      <c r="C421">
+      <c r="C421" s="1">
         <v>167.53</v>
       </c>
       <c r="D421">
@@ -10146,7 +10146,7 @@
       <c r="B422">
         <v>570.89</v>
       </c>
-      <c r="C422">
+      <c r="C422" s="1">
         <v>146.38999999999999</v>
       </c>
       <c r="D422">
@@ -10169,7 +10169,7 @@
       <c r="B423">
         <v>686.91</v>
       </c>
-      <c r="C423">
+      <c r="C423" s="1">
         <v>75.489999999999995</v>
       </c>
       <c r="D423">
@@ -10192,7 +10192,7 @@
       <c r="B424">
         <v>930.54</v>
       </c>
-      <c r="C424">
+      <c r="C424" s="1">
         <v>501.55</v>
       </c>
       <c r="D424">
@@ -10215,7 +10215,7 @@
       <c r="B425">
         <v>572.11</v>
       </c>
-      <c r="C425">
+      <c r="C425" s="1">
         <v>115.97</v>
       </c>
       <c r="D425">
@@ -10238,7 +10238,7 @@
       <c r="B426">
         <v>1285.27</v>
       </c>
-      <c r="C426">
+      <c r="C426" s="1">
         <v>514.82000000000005</v>
       </c>
       <c r="D426">
@@ -10261,7 +10261,7 @@
       <c r="B427">
         <v>1470.68</v>
       </c>
-      <c r="C427">
+      <c r="C427" s="1">
         <v>230.38</v>
       </c>
       <c r="D427">
@@ -10284,7 +10284,7 @@
       <c r="B428">
         <v>704.44</v>
       </c>
-      <c r="C428">
+      <c r="C428" s="1">
         <v>253.49</v>
       </c>
       <c r="D428">
@@ -10307,7 +10307,7 @@
       <c r="B429">
         <v>1189.78</v>
       </c>
-      <c r="C429">
+      <c r="C429" s="1">
         <v>204.61</v>
       </c>
       <c r="D429">
@@ -10330,7 +10330,7 @@
       <c r="B430">
         <v>797.29</v>
       </c>
-      <c r="C430">
+      <c r="C430" s="1">
         <v>116.43</v>
       </c>
       <c r="D430">
@@ -10353,7 +10353,7 @@
       <c r="B431">
         <v>1025.76</v>
       </c>
-      <c r="C431">
+      <c r="C431" s="1">
         <v>230.55</v>
       </c>
       <c r="D431">
@@ -10376,7 +10376,7 @@
       <c r="B432">
         <v>654.83000000000004</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="1">
         <v>374.8</v>
       </c>
       <c r="D432">
@@ -10399,7 +10399,7 @@
       <c r="B433">
         <v>550.49</v>
       </c>
-      <c r="C433">
+      <c r="C433" s="1">
         <v>227.76</v>
       </c>
       <c r="D433">
@@ -10422,7 +10422,7 @@
       <c r="B434">
         <v>1457.58</v>
       </c>
-      <c r="C434">
+      <c r="C434" s="1">
         <v>436.57</v>
       </c>
       <c r="D434">
@@ -10445,7 +10445,7 @@
       <c r="B435">
         <v>1390.06</v>
       </c>
-      <c r="C435">
+      <c r="C435" s="1">
         <v>197.6</v>
       </c>
       <c r="D435">
@@ -10468,7 +10468,7 @@
       <c r="B436">
         <v>1223.45</v>
       </c>
-      <c r="C436">
+      <c r="C436" s="1">
         <v>127.88</v>
       </c>
       <c r="D436">
@@ -10491,7 +10491,7 @@
       <c r="B437">
         <v>1318.37</v>
       </c>
-      <c r="C437">
+      <c r="C437" s="1">
         <v>164.81</v>
       </c>
       <c r="D437">
@@ -10514,7 +10514,7 @@
       <c r="B438">
         <v>577.15</v>
       </c>
-      <c r="C438">
+      <c r="C438" s="1">
         <v>320.64999999999998</v>
       </c>
       <c r="D438">
@@ -10537,7 +10537,7 @@
       <c r="B439">
         <v>1384.96</v>
       </c>
-      <c r="C439">
+      <c r="C439" s="1">
         <v>403.91</v>
       </c>
       <c r="D439">
@@ -10560,7 +10560,7 @@
       <c r="B440">
         <v>1116.78</v>
       </c>
-      <c r="C440">
+      <c r="C440" s="1">
         <v>526.5</v>
       </c>
       <c r="D440">
@@ -10583,7 +10583,7 @@
       <c r="B441">
         <v>1038.33</v>
       </c>
-      <c r="C441">
+      <c r="C441" s="1">
         <v>243.41</v>
       </c>
       <c r="D441">
@@ -10606,7 +10606,7 @@
       <c r="B442">
         <v>954.35</v>
       </c>
-      <c r="C442">
+      <c r="C442" s="1">
         <v>396.17</v>
       </c>
       <c r="D442">
@@ -10629,7 +10629,7 @@
       <c r="B443">
         <v>1283.99</v>
       </c>
-      <c r="C443">
+      <c r="C443" s="1">
         <v>397.64</v>
       </c>
       <c r="D443">
@@ -10652,7 +10652,7 @@
       <c r="B444">
         <v>801.05</v>
       </c>
-      <c r="C444">
+      <c r="C444" s="1">
         <v>281.42</v>
       </c>
       <c r="D444">
@@ -10675,7 +10675,7 @@
       <c r="B445">
         <v>908.78</v>
       </c>
-      <c r="C445">
+      <c r="C445" s="1">
         <v>510.75</v>
       </c>
       <c r="D445">
@@ -10698,7 +10698,7 @@
       <c r="B446">
         <v>1164.22</v>
       </c>
-      <c r="C446">
+      <c r="C446" s="1">
         <v>629.66</v>
       </c>
       <c r="D446">
@@ -10721,7 +10721,7 @@
       <c r="B447">
         <v>943.31</v>
       </c>
-      <c r="C447">
+      <c r="C447" s="1">
         <v>355.33</v>
       </c>
       <c r="D447">
@@ -10744,7 +10744,7 @@
       <c r="B448">
         <v>1328.12</v>
       </c>
-      <c r="C448">
+      <c r="C448" s="1">
         <v>276.29000000000002</v>
       </c>
       <c r="D448">
@@ -10767,7 +10767,7 @@
       <c r="B449">
         <v>818.61</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="1">
         <v>451.69</v>
       </c>
       <c r="D449">
@@ -10790,7 +10790,7 @@
       <c r="B450">
         <v>1358.82</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="1">
         <v>595.79999999999995</v>
       </c>
       <c r="D450">
@@ -10813,7 +10813,7 @@
       <c r="B451">
         <v>959.19</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="1">
         <v>293.08</v>
       </c>
       <c r="D451">
@@ -10836,7 +10836,7 @@
       <c r="B452">
         <v>665.28</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="1">
         <v>67.19</v>
       </c>
       <c r="D452">
@@ -10859,7 +10859,7 @@
       <c r="B453">
         <v>1134.6400000000001</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="1">
         <v>443.73</v>
       </c>
       <c r="D453">
@@ -10882,7 +10882,7 @@
       <c r="B454">
         <v>835.67</v>
       </c>
-      <c r="C454">
+      <c r="C454" s="1">
         <v>396.69</v>
       </c>
       <c r="D454">
@@ -10905,7 +10905,7 @@
       <c r="B455">
         <v>1196.43</v>
       </c>
-      <c r="C455">
+      <c r="C455" s="1">
         <v>539.67999999999995</v>
       </c>
       <c r="D455">
@@ -10928,7 +10928,7 @@
       <c r="B456">
         <v>1131.42</v>
       </c>
-      <c r="C456">
+      <c r="C456" s="1">
         <v>414.38</v>
       </c>
       <c r="D456">
@@ -10951,7 +10951,7 @@
       <c r="B457">
         <v>1012.28</v>
       </c>
-      <c r="C457">
+      <c r="C457" s="1">
         <v>159.07</v>
       </c>
       <c r="D457">
@@ -10974,7 +10974,7 @@
       <c r="B458">
         <v>1276.49</v>
       </c>
-      <c r="C458">
+      <c r="C458" s="1">
         <v>517.83000000000004</v>
       </c>
       <c r="D458">
@@ -10997,7 +10997,7 @@
       <c r="B459">
         <v>753.27</v>
       </c>
-      <c r="C459">
+      <c r="C459" s="1">
         <v>79.09</v>
       </c>
       <c r="D459">
@@ -11020,7 +11020,7 @@
       <c r="B460">
         <v>1374.17</v>
       </c>
-      <c r="C460">
+      <c r="C460" s="1">
         <v>277.2</v>
       </c>
       <c r="D460">
@@ -11043,7 +11043,7 @@
       <c r="B461">
         <v>1382.56</v>
       </c>
-      <c r="C461">
+      <c r="C461" s="1">
         <v>460.61</v>
       </c>
       <c r="D461">
@@ -11066,7 +11066,7 @@
       <c r="B462">
         <v>780.88</v>
       </c>
-      <c r="C462">
+      <c r="C462" s="1">
         <v>159.28</v>
       </c>
       <c r="D462">
@@ -11089,7 +11089,7 @@
       <c r="B463">
         <v>1148.32</v>
       </c>
-      <c r="C463">
+      <c r="C463" s="1">
         <v>157.38</v>
       </c>
       <c r="D463">
@@ -11112,7 +11112,7 @@
       <c r="B464">
         <v>1059.06</v>
       </c>
-      <c r="C464">
+      <c r="C464" s="1">
         <v>275.97000000000003</v>
       </c>
       <c r="D464">
@@ -11135,7 +11135,7 @@
       <c r="B465">
         <v>869.48</v>
       </c>
-      <c r="C465">
+      <c r="C465" s="1">
         <v>106.65</v>
       </c>
       <c r="D465">
@@ -11158,7 +11158,7 @@
       <c r="B466">
         <v>1161.68</v>
       </c>
-      <c r="C466">
+      <c r="C466" s="1">
         <v>397.29</v>
       </c>
       <c r="D466">
@@ -11181,7 +11181,7 @@
       <c r="B467">
         <v>1083.71</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="1">
         <v>532.08000000000004</v>
       </c>
       <c r="D467">
@@ -11204,7 +11204,7 @@
       <c r="B468">
         <v>514.63</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="1">
         <v>104.79</v>
       </c>
       <c r="D468">
@@ -11227,7 +11227,7 @@
       <c r="B469">
         <v>1408.23</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="1">
         <v>675.05</v>
       </c>
       <c r="D469">
@@ -11250,7 +11250,7 @@
       <c r="B470">
         <v>1041.6500000000001</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="1">
         <v>499.09</v>
       </c>
       <c r="D470">
@@ -11273,7 +11273,7 @@
       <c r="B471">
         <v>741.5</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="1">
         <v>153.83000000000001</v>
       </c>
       <c r="D471">
@@ -11296,7 +11296,7 @@
       <c r="B472">
         <v>1084.67</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="1">
         <v>180.95</v>
       </c>
       <c r="D472">
@@ -11319,7 +11319,7 @@
       <c r="B473">
         <v>764.06</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="1">
         <v>435.16</v>
       </c>
       <c r="D473">
@@ -11342,7 +11342,7 @@
       <c r="B474">
         <v>963.11</v>
       </c>
-      <c r="C474">
+      <c r="C474" s="1">
         <v>230.4</v>
       </c>
       <c r="D474">
@@ -11365,7 +11365,7 @@
       <c r="B475">
         <v>1273.6600000000001</v>
       </c>
-      <c r="C475">
+      <c r="C475" s="1">
         <v>603.61</v>
       </c>
       <c r="D475">
@@ -11388,7 +11388,7 @@
       <c r="B476">
         <v>1379.19</v>
       </c>
-      <c r="C476">
+      <c r="C476" s="1">
         <v>305.76</v>
       </c>
       <c r="D476">
@@ -11411,7 +11411,7 @@
       <c r="B477">
         <v>1014.2</v>
       </c>
-      <c r="C477">
+      <c r="C477" s="1">
         <v>474.76</v>
       </c>
       <c r="D477">
@@ -11434,7 +11434,7 @@
       <c r="B478">
         <v>1312.71</v>
       </c>
-      <c r="C478">
+      <c r="C478" s="1">
         <v>595.21</v>
       </c>
       <c r="D478">
@@ -11457,7 +11457,7 @@
       <c r="B479">
         <v>818.1</v>
       </c>
-      <c r="C479">
+      <c r="C479" s="1">
         <v>474.97</v>
       </c>
       <c r="D479">
@@ -11480,7 +11480,7 @@
       <c r="B480">
         <v>1154.3399999999999</v>
       </c>
-      <c r="C480">
+      <c r="C480" s="1">
         <v>249.35</v>
       </c>
       <c r="D480">
@@ -11503,7 +11503,7 @@
       <c r="B481">
         <v>1438.41</v>
       </c>
-      <c r="C481">
+      <c r="C481" s="1">
         <v>442.18</v>
       </c>
       <c r="D481">
@@ -11526,7 +11526,7 @@
       <c r="B482">
         <v>1256.73</v>
       </c>
-      <c r="C482">
+      <c r="C482" s="1">
         <v>403.6</v>
       </c>
       <c r="D482">
@@ -11549,7 +11549,7 @@
       <c r="B483">
         <v>841.91</v>
       </c>
-      <c r="C483">
+      <c r="C483" s="1">
         <v>306.32</v>
       </c>
       <c r="D483">
@@ -11572,7 +11572,7 @@
       <c r="B484">
         <v>1361.05</v>
       </c>
-      <c r="C484">
+      <c r="C484" s="1">
         <v>449.94</v>
       </c>
       <c r="D484">
@@ -11595,7 +11595,7 @@
       <c r="B485">
         <v>610.05999999999995</v>
       </c>
-      <c r="C485">
+      <c r="C485" s="1">
         <v>343.17</v>
       </c>
       <c r="D485">
@@ -11618,7 +11618,7 @@
       <c r="B486">
         <v>1148.6400000000001</v>
       </c>
-      <c r="C486">
+      <c r="C486" s="1">
         <v>272.97000000000003</v>
       </c>
       <c r="D486">
@@ -11641,7 +11641,7 @@
       <c r="B487">
         <v>1167.76</v>
       </c>
-      <c r="C487">
+      <c r="C487" s="1">
         <v>605.70000000000005</v>
       </c>
       <c r="D487">
@@ -11664,7 +11664,7 @@
       <c r="B488">
         <v>1199.6400000000001</v>
       </c>
-      <c r="C488">
+      <c r="C488" s="1">
         <v>622.71</v>
       </c>
       <c r="D488">
@@ -11687,7 +11687,7 @@
       <c r="B489">
         <v>1084.5</v>
       </c>
-      <c r="C489">
+      <c r="C489" s="1">
         <v>560.57000000000005</v>
       </c>
       <c r="D489">
@@ -11710,7 +11710,7 @@
       <c r="B490">
         <v>854.92</v>
       </c>
-      <c r="C490">
+      <c r="C490" s="1">
         <v>107.72</v>
       </c>
       <c r="D490">
@@ -11733,7 +11733,7 @@
       <c r="B491">
         <v>711.23</v>
       </c>
-      <c r="C491">
+      <c r="C491" s="1">
         <v>378.02</v>
       </c>
       <c r="D491">
@@ -11756,7 +11756,7 @@
       <c r="B492">
         <v>1497.24</v>
       </c>
-      <c r="C492">
+      <c r="C492" s="1">
         <v>172.2</v>
       </c>
       <c r="D492">
@@ -11779,7 +11779,7 @@
       <c r="B493">
         <v>847.51</v>
       </c>
-      <c r="C493">
+      <c r="C493" s="1">
         <v>269.25</v>
       </c>
       <c r="D493">
@@ -11802,7 +11802,7 @@
       <c r="B494">
         <v>585.1</v>
       </c>
-      <c r="C494">
+      <c r="C494" s="1">
         <v>171.32</v>
       </c>
       <c r="D494">
@@ -11825,7 +11825,7 @@
       <c r="B495">
         <v>574.82000000000005</v>
       </c>
-      <c r="C495">
+      <c r="C495" s="1">
         <v>183.5</v>
       </c>
       <c r="D495">
@@ -11848,7 +11848,7 @@
       <c r="B496">
         <v>778.37</v>
       </c>
-      <c r="C496">
+      <c r="C496" s="1">
         <v>388.52</v>
       </c>
       <c r="D496">
@@ -11871,7 +11871,7 @@
       <c r="B497">
         <v>853.7</v>
       </c>
-      <c r="C497">
+      <c r="C497" s="1">
         <v>214.48</v>
       </c>
       <c r="D497">
@@ -11894,7 +11894,7 @@
       <c r="B498">
         <v>842.65</v>
       </c>
-      <c r="C498">
+      <c r="C498" s="1">
         <v>448.56</v>
       </c>
       <c r="D498">
@@ -11917,7 +11917,7 @@
       <c r="B499">
         <v>978.5</v>
       </c>
-      <c r="C499">
+      <c r="C499" s="1">
         <v>479.74</v>
       </c>
       <c r="D499">
@@ -11940,7 +11940,7 @@
       <c r="B500">
         <v>987.83</v>
       </c>
-      <c r="C500">
+      <c r="C500" s="1">
         <v>139.41999999999999</v>
       </c>
       <c r="D500">
@@ -11963,7 +11963,7 @@
       <c r="B501">
         <v>690.73</v>
       </c>
-      <c r="C501">
+      <c r="C501" s="1">
         <v>188.94</v>
       </c>
       <c r="D501">
@@ -11986,7 +11986,7 @@
       <c r="B502">
         <v>813.88</v>
       </c>
-      <c r="C502">
+      <c r="C502" s="1">
         <v>300.33</v>
       </c>
       <c r="D502">
@@ -12009,7 +12009,7 @@
       <c r="B503">
         <v>970.87</v>
       </c>
-      <c r="C503">
+      <c r="C503" s="1">
         <v>415.56</v>
       </c>
       <c r="D503">
@@ -12032,7 +12032,7 @@
       <c r="B504">
         <v>1359.79</v>
       </c>
-      <c r="C504">
+      <c r="C504" s="1">
         <v>412.56</v>
       </c>
       <c r="D504">
@@ -12055,7 +12055,7 @@
       <c r="B505">
         <v>1317.86</v>
       </c>
-      <c r="C505">
+      <c r="C505" s="1">
         <v>467.94</v>
       </c>
       <c r="D505">
@@ -12078,7 +12078,7 @@
       <c r="B506">
         <v>1470.24</v>
       </c>
-      <c r="C506">
+      <c r="C506" s="1">
         <v>832.39</v>
       </c>
       <c r="D506">
@@ -12101,7 +12101,7 @@
       <c r="B507">
         <v>718.71</v>
       </c>
-      <c r="C507">
+      <c r="C507" s="1">
         <v>137.57</v>
       </c>
       <c r="D507">
@@ -12124,7 +12124,7 @@
       <c r="B508">
         <v>1285.6400000000001</v>
       </c>
-      <c r="C508">
+      <c r="C508" s="1">
         <v>291.07</v>
       </c>
       <c r="D508">
@@ -12147,7 +12147,7 @@
       <c r="B509">
         <v>675.12</v>
       </c>
-      <c r="C509">
+      <c r="C509" s="1">
         <v>294.61</v>
       </c>
       <c r="D509">
@@ -12170,7 +12170,7 @@
       <c r="B510">
         <v>500.65</v>
       </c>
-      <c r="C510">
+      <c r="C510" s="1">
         <v>268.02</v>
       </c>
       <c r="D510">
@@ -12193,7 +12193,7 @@
       <c r="B511">
         <v>593.78</v>
       </c>
-      <c r="C511">
+      <c r="C511" s="1">
         <v>203.7</v>
       </c>
       <c r="D511">
@@ -12216,7 +12216,7 @@
       <c r="B512">
         <v>738.15</v>
       </c>
-      <c r="C512">
+      <c r="C512" s="1">
         <v>409.09</v>
       </c>
       <c r="D512">
@@ -12239,7 +12239,7 @@
       <c r="B513">
         <v>1012.92</v>
       </c>
-      <c r="C513">
+      <c r="C513" s="1">
         <v>457.88</v>
       </c>
       <c r="D513">
@@ -12262,7 +12262,7 @@
       <c r="B514">
         <v>670.71</v>
       </c>
-      <c r="C514">
+      <c r="C514" s="1">
         <v>77.290000000000006</v>
       </c>
       <c r="D514">
@@ -12285,7 +12285,7 @@
       <c r="B515">
         <v>1273.55</v>
       </c>
-      <c r="C515">
+      <c r="C515" s="1">
         <v>205.93</v>
       </c>
       <c r="D515">
@@ -12308,7 +12308,7 @@
       <c r="B516">
         <v>1339.18</v>
       </c>
-      <c r="C516">
+      <c r="C516" s="1">
         <v>241.51</v>
       </c>
       <c r="D516">
@@ -12331,7 +12331,7 @@
       <c r="B517">
         <v>673.5</v>
       </c>
-      <c r="C517">
+      <c r="C517" s="1">
         <v>195.23</v>
       </c>
       <c r="D517">
@@ -12354,7 +12354,7 @@
       <c r="B518">
         <v>1151.52</v>
       </c>
-      <c r="C518">
+      <c r="C518" s="1">
         <v>236.51</v>
       </c>
       <c r="D518">
@@ -12377,7 +12377,7 @@
       <c r="B519">
         <v>1249.43</v>
       </c>
-      <c r="C519">
+      <c r="C519" s="1">
         <v>394.26</v>
       </c>
       <c r="D519">
@@ -12400,7 +12400,7 @@
       <c r="B520">
         <v>832.21</v>
       </c>
-      <c r="C520">
+      <c r="C520" s="1">
         <v>205.46</v>
       </c>
       <c r="D520">
@@ -12423,7 +12423,7 @@
       <c r="B521">
         <v>1348.11</v>
       </c>
-      <c r="C521">
+      <c r="C521" s="1">
         <v>773.25</v>
       </c>
       <c r="D521">
@@ -12446,7 +12446,7 @@
       <c r="B522">
         <v>839.77</v>
       </c>
-      <c r="C522">
+      <c r="C522" s="1">
         <v>275.27999999999997</v>
       </c>
       <c r="D522">
@@ -12469,7 +12469,7 @@
       <c r="B523">
         <v>839.97</v>
       </c>
-      <c r="C523">
+      <c r="C523" s="1">
         <v>117.15</v>
       </c>
       <c r="D523">
@@ -12492,7 +12492,7 @@
       <c r="B524">
         <v>1435.48</v>
       </c>
-      <c r="C524">
+      <c r="C524" s="1">
         <v>276.86</v>
       </c>
       <c r="D524">
@@ -12515,7 +12515,7 @@
       <c r="B525">
         <v>946.71</v>
       </c>
-      <c r="C525">
+      <c r="C525" s="1">
         <v>332.07</v>
       </c>
       <c r="D525">
@@ -12538,7 +12538,7 @@
       <c r="B526">
         <v>1147.52</v>
       </c>
-      <c r="C526">
+      <c r="C526" s="1">
         <v>271.41000000000003</v>
       </c>
       <c r="D526">
@@ -12561,7 +12561,7 @@
       <c r="B527">
         <v>911.2</v>
       </c>
-      <c r="C527">
+      <c r="C527" s="1">
         <v>274.45999999999998</v>
       </c>
       <c r="D527">
@@ -12584,7 +12584,7 @@
       <c r="B528">
         <v>940.06</v>
       </c>
-      <c r="C528">
+      <c r="C528" s="1">
         <v>436.99</v>
       </c>
       <c r="D528">
@@ -12607,7 +12607,7 @@
       <c r="B529">
         <v>1031.45</v>
       </c>
-      <c r="C529">
+      <c r="C529" s="1">
         <v>251.65</v>
       </c>
       <c r="D529">
@@ -12630,7 +12630,7 @@
       <c r="B530">
         <v>664.41</v>
       </c>
-      <c r="C530">
+      <c r="C530" s="1">
         <v>105.17</v>
       </c>
       <c r="D530">
@@ -12653,7 +12653,7 @@
       <c r="B531">
         <v>605.85</v>
       </c>
-      <c r="C531">
+      <c r="C531" s="1">
         <v>325.05</v>
       </c>
       <c r="D531">
@@ -12676,7 +12676,7 @@
       <c r="B532">
         <v>826.79</v>
       </c>
-      <c r="C532">
+      <c r="C532" s="1">
         <v>87.15</v>
       </c>
       <c r="D532">
@@ -12699,7 +12699,7 @@
       <c r="B533">
         <v>1480.57</v>
       </c>
-      <c r="C533">
+      <c r="C533" s="1">
         <v>306.99</v>
       </c>
       <c r="D533">
@@ -12722,7 +12722,7 @@
       <c r="B534">
         <v>1116.94</v>
       </c>
-      <c r="C534">
+      <c r="C534" s="1">
         <v>593.91999999999996</v>
       </c>
       <c r="D534">
@@ -12745,7 +12745,7 @@
       <c r="B535">
         <v>1318.74</v>
       </c>
-      <c r="C535">
+      <c r="C535" s="1">
         <v>780.41</v>
       </c>
       <c r="D535">
@@ -12768,7 +12768,7 @@
       <c r="B536">
         <v>550.35</v>
       </c>
-      <c r="C536">
+      <c r="C536" s="1">
         <v>69.55</v>
       </c>
       <c r="D536">
@@ -12791,7 +12791,7 @@
       <c r="B537">
         <v>859.21</v>
       </c>
-      <c r="C537">
+      <c r="C537" s="1">
         <v>439.72</v>
       </c>
       <c r="D537">
@@ -12814,7 +12814,7 @@
       <c r="B538">
         <v>828.18</v>
       </c>
-      <c r="C538">
+      <c r="C538" s="1">
         <v>169.39</v>
       </c>
       <c r="D538">
@@ -12837,7 +12837,7 @@
       <c r="B539">
         <v>1076.47</v>
       </c>
-      <c r="C539">
+      <c r="C539" s="1">
         <v>517.72</v>
       </c>
       <c r="D539">
@@ -12860,7 +12860,7 @@
       <c r="B540">
         <v>618.64</v>
       </c>
-      <c r="C540">
+      <c r="C540" s="1">
         <v>350.69</v>
       </c>
       <c r="D540">
@@ -12883,7 +12883,7 @@
       <c r="B541">
         <v>1156.4100000000001</v>
       </c>
-      <c r="C541">
+      <c r="C541" s="1">
         <v>677.17</v>
       </c>
       <c r="D541">
@@ -12906,7 +12906,7 @@
       <c r="B542">
         <v>616.36</v>
       </c>
-      <c r="C542">
+      <c r="C542" s="1">
         <v>250.49</v>
       </c>
       <c r="D542">
@@ -12929,7 +12929,7 @@
       <c r="B543">
         <v>1333.64</v>
       </c>
-      <c r="C543">
+      <c r="C543" s="1">
         <v>676.6</v>
       </c>
       <c r="D543">
@@ -12952,7 +12952,7 @@
       <c r="B544">
         <v>944.12</v>
       </c>
-      <c r="C544">
+      <c r="C544" s="1">
         <v>448.47</v>
       </c>
       <c r="D544">
@@ -12975,7 +12975,7 @@
       <c r="B545">
         <v>529.16</v>
       </c>
-      <c r="C545">
+      <c r="C545" s="1">
         <v>292.95</v>
       </c>
       <c r="D545">
@@ -12998,7 +12998,7 @@
       <c r="B546">
         <v>1057.04</v>
       </c>
-      <c r="C546">
+      <c r="C546" s="1">
         <v>227.99</v>
       </c>
       <c r="D546">
@@ -13021,7 +13021,7 @@
       <c r="B547">
         <v>1416.42</v>
       </c>
-      <c r="C547">
+      <c r="C547" s="1">
         <v>591.65</v>
       </c>
       <c r="D547">
@@ -13044,7 +13044,7 @@
       <c r="B548">
         <v>543.04999999999995</v>
       </c>
-      <c r="C548">
+      <c r="C548" s="1">
         <v>266.36</v>
       </c>
       <c r="D548">
@@ -13067,7 +13067,7 @@
       <c r="B549">
         <v>1344.21</v>
       </c>
-      <c r="C549">
+      <c r="C549" s="1">
         <v>459.73</v>
       </c>
       <c r="D549">
@@ -13090,7 +13090,7 @@
       <c r="B550">
         <v>1059.4100000000001</v>
       </c>
-      <c r="C550">
+      <c r="C550" s="1">
         <v>544.79</v>
       </c>
       <c r="D550">
@@ -13113,7 +13113,7 @@
       <c r="B551">
         <v>1446.76</v>
       </c>
-      <c r="C551">
+      <c r="C551" s="1">
         <v>434.18</v>
       </c>
       <c r="D551">
@@ -13136,7 +13136,7 @@
       <c r="B552">
         <v>1497.62</v>
       </c>
-      <c r="C552">
+      <c r="C552" s="1">
         <v>292.88</v>
       </c>
       <c r="D552">
@@ -13159,7 +13159,7 @@
       <c r="B553">
         <v>1046.46</v>
       </c>
-      <c r="C553">
+      <c r="C553" s="1">
         <v>322.93</v>
       </c>
       <c r="D553">
@@ -13182,7 +13182,7 @@
       <c r="B554">
         <v>1297.21</v>
       </c>
-      <c r="C554">
+      <c r="C554" s="1">
         <v>599.46</v>
       </c>
       <c r="D554">
@@ -13205,7 +13205,7 @@
       <c r="B555">
         <v>523.71</v>
       </c>
-      <c r="C555">
+      <c r="C555" s="1">
         <v>271</v>
       </c>
       <c r="D555">
@@ -13228,7 +13228,7 @@
       <c r="B556">
         <v>1426.46</v>
       </c>
-      <c r="C556">
+      <c r="C556" s="1">
         <v>441.94</v>
       </c>
       <c r="D556">
@@ -13251,7 +13251,7 @@
       <c r="B557">
         <v>1446.76</v>
       </c>
-      <c r="C557">
+      <c r="C557" s="1">
         <v>710.08</v>
       </c>
       <c r="D557">
@@ -13274,7 +13274,7 @@
       <c r="B558">
         <v>897.68</v>
       </c>
-      <c r="C558">
+      <c r="C558" s="1">
         <v>526.85</v>
       </c>
       <c r="D558">
@@ -13297,7 +13297,7 @@
       <c r="B559">
         <v>926.12</v>
       </c>
-      <c r="C559">
+      <c r="C559" s="1">
         <v>478.05</v>
       </c>
       <c r="D559">
@@ -13320,7 +13320,7 @@
       <c r="B560">
         <v>587.59</v>
       </c>
-      <c r="C560">
+      <c r="C560" s="1">
         <v>85.18</v>
       </c>
       <c r="D560">
@@ -13343,7 +13343,7 @@
       <c r="B561">
         <v>1162.8</v>
       </c>
-      <c r="C561">
+      <c r="C561" s="1">
         <v>622.46</v>
       </c>
       <c r="D561">
@@ -13366,7 +13366,7 @@
       <c r="B562">
         <v>661.37</v>
       </c>
-      <c r="C562">
+      <c r="C562" s="1">
         <v>255.29</v>
       </c>
       <c r="D562">
@@ -13389,7 +13389,7 @@
       <c r="B563">
         <v>907.72</v>
       </c>
-      <c r="C563">
+      <c r="C563" s="1">
         <v>147.76</v>
       </c>
       <c r="D563">
@@ -13412,7 +13412,7 @@
       <c r="B564">
         <v>1197.1600000000001</v>
       </c>
-      <c r="C564">
+      <c r="C564" s="1">
         <v>235.5</v>
       </c>
       <c r="D564">
@@ -13435,7 +13435,7 @@
       <c r="B565">
         <v>911.3</v>
       </c>
-      <c r="C565">
+      <c r="C565" s="1">
         <v>200.73</v>
       </c>
       <c r="D565">
@@ -13458,7 +13458,7 @@
       <c r="B566">
         <v>605.59</v>
       </c>
-      <c r="C566">
+      <c r="C566" s="1">
         <v>74.27</v>
       </c>
       <c r="D566">
@@ -13481,7 +13481,7 @@
       <c r="B567">
         <v>1477.28</v>
       </c>
-      <c r="C567">
+      <c r="C567" s="1">
         <v>734.07</v>
       </c>
       <c r="D567">
@@ -13504,7 +13504,7 @@
       <c r="B568">
         <v>1485.17</v>
       </c>
-      <c r="C568">
+      <c r="C568" s="1">
         <v>718.83</v>
       </c>
       <c r="D568">
@@ -13527,7 +13527,7 @@
       <c r="B569">
         <v>929.62</v>
       </c>
-      <c r="C569">
+      <c r="C569" s="1">
         <v>222.62</v>
       </c>
       <c r="D569">
@@ -13550,7 +13550,7 @@
       <c r="B570">
         <v>753.58</v>
       </c>
-      <c r="C570">
+      <c r="C570" s="1">
         <v>252.81</v>
       </c>
       <c r="D570">
@@ -13573,7 +13573,7 @@
       <c r="B571">
         <v>1365.56</v>
       </c>
-      <c r="C571">
+      <c r="C571" s="1">
         <v>206.78</v>
       </c>
       <c r="D571">
@@ -13596,7 +13596,7 @@
       <c r="B572">
         <v>635.08000000000004</v>
       </c>
-      <c r="C572">
+      <c r="C572" s="1">
         <v>111.7</v>
       </c>
       <c r="D572">
@@ -13619,7 +13619,7 @@
       <c r="B573">
         <v>964.07</v>
       </c>
-      <c r="C573">
+      <c r="C573" s="1">
         <v>550.99</v>
       </c>
       <c r="D573">
@@ -13642,7 +13642,7 @@
       <c r="B574">
         <v>1150.43</v>
       </c>
-      <c r="C574">
+      <c r="C574" s="1">
         <v>237.18</v>
       </c>
       <c r="D574">
@@ -13665,7 +13665,7 @@
       <c r="B575">
         <v>965.34</v>
       </c>
-      <c r="C575">
+      <c r="C575" s="1">
         <v>103.14</v>
       </c>
       <c r="D575">
@@ -13688,7 +13688,7 @@
       <c r="B576">
         <v>1277.46</v>
       </c>
-      <c r="C576">
+      <c r="C576" s="1">
         <v>557.51</v>
       </c>
       <c r="D576">
@@ -13711,7 +13711,7 @@
       <c r="B577">
         <v>1092.02</v>
       </c>
-      <c r="C577">
+      <c r="C577" s="1">
         <v>199.79</v>
       </c>
       <c r="D577">
@@ -13734,7 +13734,7 @@
       <c r="B578">
         <v>1100.9100000000001</v>
       </c>
-      <c r="C578">
+      <c r="C578" s="1">
         <v>297.77</v>
       </c>
       <c r="D578">
@@ -13757,7 +13757,7 @@
       <c r="B579">
         <v>1400.26</v>
       </c>
-      <c r="C579">
+      <c r="C579" s="1">
         <v>694.66</v>
       </c>
       <c r="D579">
@@ -13780,7 +13780,7 @@
       <c r="B580">
         <v>753.64</v>
       </c>
-      <c r="C580">
+      <c r="C580" s="1">
         <v>360.36</v>
       </c>
       <c r="D580">
@@ -13803,7 +13803,7 @@
       <c r="B581">
         <v>823.53</v>
       </c>
-      <c r="C581">
+      <c r="C581" s="1">
         <v>356.2</v>
       </c>
       <c r="D581">
@@ -13826,7 +13826,7 @@
       <c r="B582">
         <v>1424.25</v>
       </c>
-      <c r="C582">
+      <c r="C582" s="1">
         <v>470.48</v>
       </c>
       <c r="D582">
@@ -13849,7 +13849,7 @@
       <c r="B583">
         <v>500.03</v>
       </c>
-      <c r="C583">
+      <c r="C583" s="1">
         <v>228.05</v>
       </c>
       <c r="D583">
@@ -13872,7 +13872,7 @@
       <c r="B584">
         <v>1457.63</v>
       </c>
-      <c r="C584">
+      <c r="C584" s="1">
         <v>558.09</v>
       </c>
       <c r="D584">
@@ -13895,7 +13895,7 @@
       <c r="B585">
         <v>725.73</v>
       </c>
-      <c r="C585">
+      <c r="C585" s="1">
         <v>214.05</v>
       </c>
       <c r="D585">
@@ -13918,7 +13918,7 @@
       <c r="B586">
         <v>1031.8699999999999</v>
       </c>
-      <c r="C586">
+      <c r="C586" s="1">
         <v>553.91999999999996</v>
       </c>
       <c r="D586">
@@ -13941,7 +13941,7 @@
       <c r="B587">
         <v>989.04</v>
       </c>
-      <c r="C587">
+      <c r="C587" s="1">
         <v>523.97</v>
       </c>
       <c r="D587">
@@ -13964,7 +13964,7 @@
       <c r="B588">
         <v>628.33000000000004</v>
       </c>
-      <c r="C588">
+      <c r="C588" s="1">
         <v>244.57</v>
       </c>
       <c r="D588">
@@ -13987,7 +13987,7 @@
       <c r="B589">
         <v>1119.17</v>
       </c>
-      <c r="C589">
+      <c r="C589" s="1">
         <v>216.36</v>
       </c>
       <c r="D589">
@@ -14010,7 +14010,7 @@
       <c r="B590">
         <v>1296.51</v>
       </c>
-      <c r="C590">
+      <c r="C590" s="1">
         <v>280.39999999999998</v>
       </c>
       <c r="D590">
@@ -14033,7 +14033,7 @@
       <c r="B591">
         <v>1041.3699999999999</v>
       </c>
-      <c r="C591">
+      <c r="C591" s="1">
         <v>148.93</v>
       </c>
       <c r="D591">
@@ -14056,7 +14056,7 @@
       <c r="B592">
         <v>1137.77</v>
       </c>
-      <c r="C592">
+      <c r="C592" s="1">
         <v>580.29999999999995</v>
       </c>
       <c r="D592">
@@ -14079,7 +14079,7 @@
       <c r="B593">
         <v>653.91999999999996</v>
       </c>
-      <c r="C593">
+      <c r="C593" s="1">
         <v>384.84</v>
       </c>
       <c r="D593">
@@ -14102,7 +14102,7 @@
       <c r="B594">
         <v>1407.74</v>
       </c>
-      <c r="C594">
+      <c r="C594" s="1">
         <v>842.22</v>
       </c>
       <c r="D594">
@@ -14125,7 +14125,7 @@
       <c r="B595">
         <v>815.77</v>
       </c>
-      <c r="C595">
+      <c r="C595" s="1">
         <v>104.78</v>
       </c>
       <c r="D595">
@@ -14148,7 +14148,7 @@
       <c r="B596">
         <v>895.94</v>
       </c>
-      <c r="C596">
+      <c r="C596" s="1">
         <v>428.37</v>
       </c>
       <c r="D596">
@@ -14171,7 +14171,7 @@
       <c r="B597">
         <v>1079.73</v>
       </c>
-      <c r="C597">
+      <c r="C597" s="1">
         <v>294.56</v>
       </c>
       <c r="D597">
@@ -14194,7 +14194,7 @@
       <c r="B598">
         <v>1158.0999999999999</v>
       </c>
-      <c r="C598">
+      <c r="C598" s="1">
         <v>693.56</v>
       </c>
       <c r="D598">
@@ -14217,7 +14217,7 @@
       <c r="B599">
         <v>942.03</v>
       </c>
-      <c r="C599">
+      <c r="C599" s="1">
         <v>399.53</v>
       </c>
       <c r="D599">
@@ -14240,7 +14240,7 @@
       <c r="B600">
         <v>1454.57</v>
       </c>
-      <c r="C600">
+      <c r="C600" s="1">
         <v>255.59</v>
       </c>
       <c r="D600">
@@ -14263,7 +14263,7 @@
       <c r="B601">
         <v>662.54</v>
       </c>
-      <c r="C601">
+      <c r="C601" s="1">
         <v>290.07</v>
       </c>
       <c r="D601">
@@ -14286,7 +14286,7 @@
       <c r="B602">
         <v>1052.3699999999999</v>
       </c>
-      <c r="C602">
+      <c r="C602" s="1">
         <v>418.44</v>
       </c>
       <c r="D602">
@@ -14309,7 +14309,7 @@
       <c r="B603">
         <v>1178.3900000000001</v>
       </c>
-      <c r="C603">
+      <c r="C603" s="1">
         <v>467.1</v>
       </c>
       <c r="D603">
@@ -14332,7 +14332,7 @@
       <c r="B604">
         <v>651.45000000000005</v>
       </c>
-      <c r="C604">
+      <c r="C604" s="1">
         <v>206.11</v>
       </c>
       <c r="D604">
@@ -14355,7 +14355,7 @@
       <c r="B605">
         <v>700.77</v>
       </c>
-      <c r="C605">
+      <c r="C605" s="1">
         <v>180.45</v>
       </c>
       <c r="D605">
@@ -14378,7 +14378,7 @@
       <c r="B606">
         <v>777.07</v>
       </c>
-      <c r="C606">
+      <c r="C606" s="1">
         <v>443.27</v>
       </c>
       <c r="D606">
@@ -14401,7 +14401,7 @@
       <c r="B607">
         <v>1016.28</v>
       </c>
-      <c r="C607">
+      <c r="C607" s="1">
         <v>396.68</v>
       </c>
       <c r="D607">
@@ -14424,7 +14424,7 @@
       <c r="B608">
         <v>1285.93</v>
       </c>
-      <c r="C608">
+      <c r="C608" s="1">
         <v>525.9</v>
       </c>
       <c r="D608">
@@ -14447,7 +14447,7 @@
       <c r="B609">
         <v>939.86</v>
       </c>
-      <c r="C609">
+      <c r="C609" s="1">
         <v>396.6</v>
       </c>
       <c r="D609">
@@ -14470,7 +14470,7 @@
       <c r="B610">
         <v>959.33</v>
       </c>
-      <c r="C610">
+      <c r="C610" s="1">
         <v>456.7</v>
       </c>
       <c r="D610">
@@ -14493,7 +14493,7 @@
       <c r="B611">
         <v>853.1</v>
       </c>
-      <c r="C611">
+      <c r="C611" s="1">
         <v>426.46</v>
       </c>
       <c r="D611">
@@ -14516,7 +14516,7 @@
       <c r="B612">
         <v>945.39</v>
       </c>
-      <c r="C612">
+      <c r="C612" s="1">
         <v>101.42</v>
       </c>
       <c r="D612">
@@ -14539,7 +14539,7 @@
       <c r="B613">
         <v>1071.6099999999999</v>
       </c>
-      <c r="C613">
+      <c r="C613" s="1">
         <v>206.2</v>
       </c>
       <c r="D613">
@@ -14562,7 +14562,7 @@
       <c r="B614">
         <v>726.77</v>
       </c>
-      <c r="C614">
+      <c r="C614" s="1">
         <v>314.88</v>
       </c>
       <c r="D614">
@@ -14585,7 +14585,7 @@
       <c r="B615">
         <v>551.15</v>
       </c>
-      <c r="C615">
+      <c r="C615" s="1">
         <v>164.74</v>
       </c>
       <c r="D615">
@@ -14608,7 +14608,7 @@
       <c r="B616">
         <v>645.33000000000004</v>
       </c>
-      <c r="C616">
+      <c r="C616" s="1">
         <v>227.7</v>
       </c>
       <c r="D616">
@@ -14631,7 +14631,7 @@
       <c r="B617">
         <v>758.1</v>
       </c>
-      <c r="C617">
+      <c r="C617" s="1">
         <v>118.85</v>
       </c>
       <c r="D617">
@@ -14654,7 +14654,7 @@
       <c r="B618">
         <v>1145.57</v>
       </c>
-      <c r="C618">
+      <c r="C618" s="1">
         <v>140.66999999999999</v>
       </c>
       <c r="D618">
@@ -14677,7 +14677,7 @@
       <c r="B619">
         <v>559.11</v>
       </c>
-      <c r="C619">
+      <c r="C619" s="1">
         <v>249.01</v>
       </c>
       <c r="D619">
@@ -14700,7 +14700,7 @@
       <c r="B620">
         <v>1054.73</v>
       </c>
-      <c r="C620">
+      <c r="C620" s="1">
         <v>145.94999999999999</v>
       </c>
       <c r="D620">
@@ -14723,7 +14723,7 @@
       <c r="B621">
         <v>1079.6199999999999</v>
       </c>
-      <c r="C621">
+      <c r="C621" s="1">
         <v>119.96</v>
       </c>
       <c r="D621">
@@ -14746,7 +14746,7 @@
       <c r="B622">
         <v>736.92</v>
       </c>
-      <c r="C622">
+      <c r="C622" s="1">
         <v>109.42</v>
       </c>
       <c r="D622">
@@ -14769,7 +14769,7 @@
       <c r="B623">
         <v>572.73</v>
       </c>
-      <c r="C623">
+      <c r="C623" s="1">
         <v>137.63</v>
       </c>
       <c r="D623">
@@ -14792,7 +14792,7 @@
       <c r="B624">
         <v>1187.3</v>
       </c>
-      <c r="C624">
+      <c r="C624" s="1">
         <v>689.59</v>
       </c>
       <c r="D624">
@@ -14815,7 +14815,7 @@
       <c r="B625">
         <v>834.19</v>
       </c>
-      <c r="C625">
+      <c r="C625" s="1">
         <v>388.26</v>
       </c>
       <c r="D625">
@@ -14838,7 +14838,7 @@
       <c r="B626">
         <v>567.97</v>
       </c>
-      <c r="C626">
+      <c r="C626" s="1">
         <v>108.26</v>
       </c>
       <c r="D626">
@@ -14861,7 +14861,7 @@
       <c r="B627">
         <v>1496.53</v>
       </c>
-      <c r="C627">
+      <c r="C627" s="1">
         <v>250.83</v>
       </c>
       <c r="D627">
@@ -14884,7 +14884,7 @@
       <c r="B628">
         <v>1230.17</v>
       </c>
-      <c r="C628">
+      <c r="C628" s="1">
         <v>474.72</v>
       </c>
       <c r="D628">
@@ -14907,7 +14907,7 @@
       <c r="B629">
         <v>1200.73</v>
       </c>
-      <c r="C629">
+      <c r="C629" s="1">
         <v>473.7</v>
       </c>
       <c r="D629">
@@ -14930,7 +14930,7 @@
       <c r="B630">
         <v>971.74</v>
       </c>
-      <c r="C630">
+      <c r="C630" s="1">
         <v>366.09</v>
       </c>
       <c r="D630">
@@ -14953,7 +14953,7 @@
       <c r="B631">
         <v>543.32000000000005</v>
       </c>
-      <c r="C631">
+      <c r="C631" s="1">
         <v>244.31</v>
       </c>
       <c r="D631">
@@ -14976,7 +14976,7 @@
       <c r="B632">
         <v>1235.03</v>
       </c>
-      <c r="C632">
+      <c r="C632" s="1">
         <v>500.25</v>
       </c>
       <c r="D632">
@@ -14999,7 +14999,7 @@
       <c r="B633">
         <v>682.75</v>
       </c>
-      <c r="C633">
+      <c r="C633" s="1">
         <v>177.19</v>
       </c>
       <c r="D633">
@@ -15022,7 +15022,7 @@
       <c r="B634">
         <v>818.69</v>
       </c>
-      <c r="C634">
+      <c r="C634" s="1">
         <v>124.72</v>
       </c>
       <c r="D634">
@@ -15045,7 +15045,7 @@
       <c r="B635">
         <v>1396.57</v>
       </c>
-      <c r="C635">
+      <c r="C635" s="1">
         <v>276.73</v>
       </c>
       <c r="D635">
@@ -15068,7 +15068,7 @@
       <c r="B636">
         <v>816.08</v>
       </c>
-      <c r="C636">
+      <c r="C636" s="1">
         <v>337.44</v>
       </c>
       <c r="D636">
@@ -15091,7 +15091,7 @@
       <c r="B637">
         <v>768.8</v>
       </c>
-      <c r="C637">
+      <c r="C637" s="1">
         <v>153.24</v>
       </c>
       <c r="D637">
@@ -15114,7 +15114,7 @@
       <c r="B638">
         <v>926.5</v>
       </c>
-      <c r="C638">
+      <c r="C638" s="1">
         <v>377.74</v>
       </c>
       <c r="D638">
@@ -15137,7 +15137,7 @@
       <c r="B639">
         <v>514.61</v>
       </c>
-      <c r="C639">
+      <c r="C639" s="1">
         <v>144.19</v>
       </c>
       <c r="D639">
@@ -15160,7 +15160,7 @@
       <c r="B640">
         <v>1298.6600000000001</v>
       </c>
-      <c r="C640">
+      <c r="C640" s="1">
         <v>735.53</v>
       </c>
       <c r="D640">
@@ -15183,7 +15183,7 @@
       <c r="B641">
         <v>1385.91</v>
       </c>
-      <c r="C641">
+      <c r="C641" s="1">
         <v>704.1</v>
       </c>
       <c r="D641">
@@ -15206,7 +15206,7 @@
       <c r="B642">
         <v>1379.75</v>
       </c>
-      <c r="C642">
+      <c r="C642" s="1">
         <v>171.93</v>
       </c>
       <c r="D642">
@@ -15229,7 +15229,7 @@
       <c r="B643">
         <v>709.46</v>
       </c>
-      <c r="C643">
+      <c r="C643" s="1">
         <v>218.61</v>
       </c>
       <c r="D643">
@@ -15252,7 +15252,7 @@
       <c r="B644">
         <v>1180.48</v>
       </c>
-      <c r="C644">
+      <c r="C644" s="1">
         <v>667.97</v>
       </c>
       <c r="D644">
@@ -15275,7 +15275,7 @@
       <c r="B645">
         <v>1265.8599999999999</v>
       </c>
-      <c r="C645">
+      <c r="C645" s="1">
         <v>564.36</v>
       </c>
       <c r="D645">
@@ -15298,7 +15298,7 @@
       <c r="B646">
         <v>1465.21</v>
       </c>
-      <c r="C646">
+      <c r="C646" s="1">
         <v>460.21</v>
       </c>
       <c r="D646">
@@ -15321,7 +15321,7 @@
       <c r="B647">
         <v>1245.21</v>
       </c>
-      <c r="C647">
+      <c r="C647" s="1">
         <v>269.11</v>
       </c>
       <c r="D647">
@@ -15344,7 +15344,7 @@
       <c r="B648">
         <v>870.23</v>
       </c>
-      <c r="C648">
+      <c r="C648" s="1">
         <v>413.92</v>
       </c>
       <c r="D648">
@@ -15367,7 +15367,7 @@
       <c r="B649">
         <v>1287.97</v>
       </c>
-      <c r="C649">
+      <c r="C649" s="1">
         <v>710.48</v>
       </c>
       <c r="D649">
@@ -15390,7 +15390,7 @@
       <c r="B650">
         <v>985.65</v>
       </c>
-      <c r="C650">
+      <c r="C650" s="1">
         <v>367.61</v>
       </c>
       <c r="D650">
@@ -15413,7 +15413,7 @@
       <c r="B651">
         <v>1445.02</v>
       </c>
-      <c r="C651">
+      <c r="C651" s="1">
         <v>637.65</v>
       </c>
       <c r="D651">
@@ -15436,7 +15436,7 @@
       <c r="B652">
         <v>743.57</v>
       </c>
-      <c r="C652">
+      <c r="C652" s="1">
         <v>188.14</v>
       </c>
       <c r="D652">
@@ -15459,7 +15459,7 @@
       <c r="B653">
         <v>1311.95</v>
       </c>
-      <c r="C653">
+      <c r="C653" s="1">
         <v>751.58</v>
       </c>
       <c r="D653">
@@ -15482,7 +15482,7 @@
       <c r="B654">
         <v>1097.8399999999999</v>
       </c>
-      <c r="C654">
+      <c r="C654" s="1">
         <v>154.78</v>
       </c>
       <c r="D654">
@@ -15505,7 +15505,7 @@
       <c r="B655">
         <v>975.48</v>
       </c>
-      <c r="C655">
+      <c r="C655" s="1">
         <v>511.68</v>
       </c>
       <c r="D655">
@@ -15528,7 +15528,7 @@
       <c r="B656">
         <v>1136.05</v>
       </c>
-      <c r="C656">
+      <c r="C656" s="1">
         <v>341.83</v>
       </c>
       <c r="D656">
@@ -15551,7 +15551,7 @@
       <c r="B657">
         <v>1422.19</v>
       </c>
-      <c r="C657">
+      <c r="C657" s="1">
         <v>243.19</v>
       </c>
       <c r="D657">
@@ -15574,7 +15574,7 @@
       <c r="B658">
         <v>547.20000000000005</v>
       </c>
-      <c r="C658">
+      <c r="C658" s="1">
         <v>317.76</v>
       </c>
       <c r="D658">
@@ -15597,7 +15597,7 @@
       <c r="B659">
         <v>639.25</v>
       </c>
-      <c r="C659">
+      <c r="C659" s="1">
         <v>67.349999999999994</v>
       </c>
       <c r="D659">
@@ -15620,7 +15620,7 @@
       <c r="B660">
         <v>1027.56</v>
       </c>
-      <c r="C660">
+      <c r="C660" s="1">
         <v>190.92</v>
       </c>
       <c r="D660">
@@ -15643,7 +15643,7 @@
       <c r="B661">
         <v>749.97</v>
       </c>
-      <c r="C661">
+      <c r="C661" s="1">
         <v>102.51</v>
       </c>
       <c r="D661">
@@ -15666,7 +15666,7 @@
       <c r="B662">
         <v>910.71</v>
       </c>
-      <c r="C662">
+      <c r="C662" s="1">
         <v>463.38</v>
       </c>
       <c r="D662">
@@ -15689,7 +15689,7 @@
       <c r="B663">
         <v>1430.82</v>
       </c>
-      <c r="C663">
+      <c r="C663" s="1">
         <v>615.83000000000004</v>
       </c>
       <c r="D663">
@@ -15712,7 +15712,7 @@
       <c r="B664">
         <v>1420.69</v>
       </c>
-      <c r="C664">
+      <c r="C664" s="1">
         <v>387.15</v>
       </c>
       <c r="D664">
@@ -15735,7 +15735,7 @@
       <c r="B665">
         <v>567.6</v>
       </c>
-      <c r="C665">
+      <c r="C665" s="1">
         <v>262.24</v>
       </c>
       <c r="D665">
@@ -15758,7 +15758,7 @@
       <c r="B666">
         <v>742.17</v>
       </c>
-      <c r="C666">
+      <c r="C666" s="1">
         <v>101.31</v>
       </c>
       <c r="D666">
@@ -15781,7 +15781,7 @@
       <c r="B667">
         <v>553.83000000000004</v>
       </c>
-      <c r="C667">
+      <c r="C667" s="1">
         <v>107.96</v>
       </c>
       <c r="D667">
@@ -15804,7 +15804,7 @@
       <c r="B668">
         <v>1239.0899999999999</v>
       </c>
-      <c r="C668">
+      <c r="C668" s="1">
         <v>549.24</v>
       </c>
       <c r="D668">
@@ -15827,7 +15827,7 @@
       <c r="B669">
         <v>960.73</v>
       </c>
-      <c r="C669">
+      <c r="C669" s="1">
         <v>571.08000000000004</v>
       </c>
       <c r="D669">
@@ -15850,7 +15850,7 @@
       <c r="B670">
         <v>1038.3900000000001</v>
       </c>
-      <c r="C670">
+      <c r="C670" s="1">
         <v>618.95000000000005</v>
       </c>
       <c r="D670">
@@ -15873,7 +15873,7 @@
       <c r="B671">
         <v>518.28</v>
       </c>
-      <c r="C671">
+      <c r="C671" s="1">
         <v>286.12</v>
       </c>
       <c r="D671">
@@ -15896,7 +15896,7 @@
       <c r="B672">
         <v>733.57</v>
       </c>
-      <c r="C672">
+      <c r="C672" s="1">
         <v>98.37</v>
       </c>
       <c r="D672">
@@ -15919,7 +15919,7 @@
       <c r="B673">
         <v>1405.3</v>
       </c>
-      <c r="C673">
+      <c r="C673" s="1">
         <v>486.91</v>
       </c>
       <c r="D673">
@@ -15942,7 +15942,7 @@
       <c r="B674">
         <v>797.65</v>
       </c>
-      <c r="C674">
+      <c r="C674" s="1">
         <v>198.64</v>
       </c>
       <c r="D674">
@@ -15965,7 +15965,7 @@
       <c r="B675">
         <v>826.28</v>
       </c>
-      <c r="C675">
+      <c r="C675" s="1">
         <v>91.2</v>
       </c>
       <c r="D675">
@@ -15988,7 +15988,7 @@
       <c r="B676">
         <v>671.88</v>
       </c>
-      <c r="C676">
+      <c r="C676" s="1">
         <v>227.27</v>
       </c>
       <c r="D676">
@@ -16011,7 +16011,7 @@
       <c r="B677">
         <v>1269.44</v>
       </c>
-      <c r="C677">
+      <c r="C677" s="1">
         <v>720.28</v>
       </c>
       <c r="D677">
@@ -16034,7 +16034,7 @@
       <c r="B678">
         <v>1105.93</v>
       </c>
-      <c r="C678">
+      <c r="C678" s="1">
         <v>389.12</v>
       </c>
       <c r="D678">
@@ -16057,7 +16057,7 @@
       <c r="B679">
         <v>667.57</v>
       </c>
-      <c r="C679">
+      <c r="C679" s="1">
         <v>170.33</v>
       </c>
       <c r="D679">
@@ -16080,7 +16080,7 @@
       <c r="B680">
         <v>1163.3599999999999</v>
       </c>
-      <c r="C680">
+      <c r="C680" s="1">
         <v>185.1</v>
       </c>
       <c r="D680">
@@ -16103,7 +16103,7 @@
       <c r="B681">
         <v>852.33</v>
       </c>
-      <c r="C681">
+      <c r="C681" s="1">
         <v>103.6</v>
       </c>
       <c r="D681">
@@ -16126,7 +16126,7 @@
       <c r="B682">
         <v>1003.69</v>
       </c>
-      <c r="C682">
+      <c r="C682" s="1">
         <v>516.47</v>
       </c>
       <c r="D682">
@@ -16149,7 +16149,7 @@
       <c r="B683">
         <v>692.02</v>
       </c>
-      <c r="C683">
+      <c r="C683" s="1">
         <v>119.73</v>
       </c>
       <c r="D683">
@@ -16172,7 +16172,7 @@
       <c r="B684">
         <v>1424.07</v>
       </c>
-      <c r="C684">
+      <c r="C684" s="1">
         <v>726.51</v>
       </c>
       <c r="D684">
@@ -16195,7 +16195,7 @@
       <c r="B685">
         <v>1051.94</v>
       </c>
-      <c r="C685">
+      <c r="C685" s="1">
         <v>232.39</v>
       </c>
       <c r="D685">
@@ -16218,7 +16218,7 @@
       <c r="B686">
         <v>1142.8</v>
       </c>
-      <c r="C686">
+      <c r="C686" s="1">
         <v>457.66</v>
       </c>
       <c r="D686">
@@ -16241,7 +16241,7 @@
       <c r="B687">
         <v>972.52</v>
       </c>
-      <c r="C687">
+      <c r="C687" s="1">
         <v>281.17</v>
       </c>
       <c r="D687">
@@ -16264,7 +16264,7 @@
       <c r="B688">
         <v>525.35</v>
       </c>
-      <c r="C688">
+      <c r="C688" s="1">
         <v>233.79</v>
       </c>
       <c r="D688">
@@ -16287,7 +16287,7 @@
       <c r="B689">
         <v>1045.49</v>
       </c>
-      <c r="C689">
+      <c r="C689" s="1">
         <v>212.79</v>
       </c>
       <c r="D689">
@@ -16310,7 +16310,7 @@
       <c r="B690">
         <v>745.55</v>
       </c>
-      <c r="C690">
+      <c r="C690" s="1">
         <v>377.37</v>
       </c>
       <c r="D690">
@@ -16333,7 +16333,7 @@
       <c r="B691">
         <v>1046.68</v>
       </c>
-      <c r="C691">
+      <c r="C691" s="1">
         <v>567.54999999999995</v>
       </c>
       <c r="D691">
@@ -16356,7 +16356,7 @@
       <c r="B692">
         <v>1416.49</v>
       </c>
-      <c r="C692">
+      <c r="C692" s="1">
         <v>373.84</v>
       </c>
       <c r="D692">
@@ -16379,7 +16379,7 @@
       <c r="B693">
         <v>814.04</v>
       </c>
-      <c r="C693">
+      <c r="C693" s="1">
         <v>284.58999999999997</v>
       </c>
       <c r="D693">
@@ -16402,7 +16402,7 @@
       <c r="B694">
         <v>923.77</v>
       </c>
-      <c r="C694">
+      <c r="C694" s="1">
         <v>250.4</v>
       </c>
       <c r="D694">
@@ -16425,7 +16425,7 @@
       <c r="B695">
         <v>799.23</v>
       </c>
-      <c r="C695">
+      <c r="C695" s="1">
         <v>252.1</v>
       </c>
       <c r="D695">
@@ -16448,7 +16448,7 @@
       <c r="B696">
         <v>863.26</v>
       </c>
-      <c r="C696">
+      <c r="C696" s="1">
         <v>429.01</v>
       </c>
       <c r="D696">
@@ -16471,7 +16471,7 @@
       <c r="B697">
         <v>551.26</v>
       </c>
-      <c r="C697">
+      <c r="C697" s="1">
         <v>165.9</v>
       </c>
       <c r="D697">
@@ -16494,7 +16494,7 @@
       <c r="B698">
         <v>1119.2</v>
       </c>
-      <c r="C698">
+      <c r="C698" s="1">
         <v>380.69</v>
       </c>
       <c r="D698">
@@ -16517,7 +16517,7 @@
       <c r="B699">
         <v>982.6</v>
       </c>
-      <c r="C699">
+      <c r="C699" s="1">
         <v>204.4</v>
       </c>
       <c r="D699">
@@ -16540,7 +16540,7 @@
       <c r="B700">
         <v>975.1</v>
       </c>
-      <c r="C700">
+      <c r="C700" s="1">
         <v>535.30999999999995</v>
       </c>
       <c r="D700">
@@ -16563,7 +16563,7 @@
       <c r="B701">
         <v>928.76</v>
       </c>
-      <c r="C701">
+      <c r="C701" s="1">
         <v>117.85</v>
       </c>
       <c r="D701">
@@ -16586,7 +16586,7 @@
       <c r="B702">
         <v>1339.1</v>
       </c>
-      <c r="C702">
+      <c r="C702" s="1">
         <v>502.6</v>
       </c>
       <c r="D702">
@@ -16609,7 +16609,7 @@
       <c r="B703">
         <v>918.29</v>
       </c>
-      <c r="C703">
+      <c r="C703" s="1">
         <v>233.89</v>
       </c>
       <c r="D703">
@@ -16632,7 +16632,7 @@
       <c r="B704">
         <v>619.38</v>
       </c>
-      <c r="C704">
+      <c r="C704" s="1">
         <v>163.47</v>
       </c>
       <c r="D704">
@@ -16655,7 +16655,7 @@
       <c r="B705">
         <v>1369.65</v>
       </c>
-      <c r="C705">
+      <c r="C705" s="1">
         <v>197.32</v>
       </c>
       <c r="D705">
@@ -16678,7 +16678,7 @@
       <c r="B706">
         <v>665.5</v>
       </c>
-      <c r="C706">
+      <c r="C706" s="1">
         <v>301.67</v>
       </c>
       <c r="D706">
@@ -16701,7 +16701,7 @@
       <c r="B707">
         <v>1166.93</v>
       </c>
-      <c r="C707">
+      <c r="C707" s="1">
         <v>370.73</v>
       </c>
       <c r="D707">
@@ -16724,7 +16724,7 @@
       <c r="B708">
         <v>592.71</v>
       </c>
-      <c r="C708">
+      <c r="C708" s="1">
         <v>217</v>
       </c>
       <c r="D708">
@@ -16747,7 +16747,7 @@
       <c r="B709">
         <v>674.59</v>
       </c>
-      <c r="C709">
+      <c r="C709" s="1">
         <v>306.07</v>
       </c>
       <c r="D709">
@@ -16770,7 +16770,7 @@
       <c r="B710">
         <v>1422.6</v>
       </c>
-      <c r="C710">
+      <c r="C710" s="1">
         <v>684.42</v>
       </c>
       <c r="D710">
@@ -16793,7 +16793,7 @@
       <c r="B711">
         <v>907.89</v>
       </c>
-      <c r="C711">
+      <c r="C711" s="1">
         <v>217.73</v>
       </c>
       <c r="D711">
@@ -16816,7 +16816,7 @@
       <c r="B712">
         <v>584.97</v>
       </c>
-      <c r="C712">
+      <c r="C712" s="1">
         <v>186.09</v>
       </c>
       <c r="D712">
@@ -16839,7 +16839,7 @@
       <c r="B713">
         <v>1422.65</v>
       </c>
-      <c r="C713">
+      <c r="C713" s="1">
         <v>499.61</v>
       </c>
       <c r="D713">
@@ -16862,7 +16862,7 @@
       <c r="B714">
         <v>816</v>
       </c>
-      <c r="C714">
+      <c r="C714" s="1">
         <v>429.3</v>
       </c>
       <c r="D714">
@@ -16885,7 +16885,7 @@
       <c r="B715">
         <v>1018.01</v>
       </c>
-      <c r="C715">
+      <c r="C715" s="1">
         <v>414.43</v>
       </c>
       <c r="D715">
@@ -16908,7 +16908,7 @@
       <c r="B716">
         <v>606.16</v>
       </c>
-      <c r="C716">
+      <c r="C716" s="1">
         <v>314.44</v>
       </c>
       <c r="D716">
@@ -16931,7 +16931,7 @@
       <c r="B717">
         <v>902.31</v>
       </c>
-      <c r="C717">
+      <c r="C717" s="1">
         <v>281.95</v>
       </c>
       <c r="D717">
@@ -16954,7 +16954,7 @@
       <c r="B718">
         <v>1343.99</v>
       </c>
-      <c r="C718">
+      <c r="C718" s="1">
         <v>310.74</v>
       </c>
       <c r="D718">
@@ -16977,7 +16977,7 @@
       <c r="B719">
         <v>1384.81</v>
       </c>
-      <c r="C719">
+      <c r="C719" s="1">
         <v>298.67</v>
       </c>
       <c r="D719">
@@ -17000,7 +17000,7 @@
       <c r="B720">
         <v>1365.07</v>
       </c>
-      <c r="C720">
+      <c r="C720" s="1">
         <v>546.57000000000005</v>
       </c>
       <c r="D720">
@@ -17023,7 +17023,7 @@
       <c r="B721">
         <v>781.92</v>
       </c>
-      <c r="C721">
+      <c r="C721" s="1">
         <v>202.53</v>
       </c>
       <c r="D721">
@@ -17046,7 +17046,7 @@
       <c r="B722">
         <v>1047.32</v>
       </c>
-      <c r="C722">
+      <c r="C722" s="1">
         <v>190.93</v>
       </c>
       <c r="D722">
@@ -17069,7 +17069,7 @@
       <c r="B723">
         <v>1406.23</v>
       </c>
-      <c r="C723">
+      <c r="C723" s="1">
         <v>663.35</v>
       </c>
       <c r="D723">
@@ -17092,7 +17092,7 @@
       <c r="B724">
         <v>894.09</v>
       </c>
-      <c r="C724">
+      <c r="C724" s="1">
         <v>469.82</v>
       </c>
       <c r="D724">
@@ -17115,7 +17115,7 @@
       <c r="B725">
         <v>1148.68</v>
       </c>
-      <c r="C725">
+      <c r="C725" s="1">
         <v>631.34</v>
       </c>
       <c r="D725">
@@ -17138,7 +17138,7 @@
       <c r="B726">
         <v>976.32</v>
       </c>
-      <c r="C726">
+      <c r="C726" s="1">
         <v>424.58</v>
       </c>
       <c r="D726">
@@ -17161,7 +17161,7 @@
       <c r="B727">
         <v>725.79</v>
       </c>
-      <c r="C727">
+      <c r="C727" s="1">
         <v>296.35000000000002</v>
       </c>
       <c r="D727">
@@ -17184,7 +17184,7 @@
       <c r="B728">
         <v>942.83</v>
       </c>
-      <c r="C728">
+      <c r="C728" s="1">
         <v>493.7</v>
       </c>
       <c r="D728">
@@ -17207,7 +17207,7 @@
       <c r="B729">
         <v>945.83</v>
       </c>
-      <c r="C729">
+      <c r="C729" s="1">
         <v>480.79</v>
       </c>
       <c r="D729">
@@ -17230,7 +17230,7 @@
       <c r="B730">
         <v>887.97</v>
       </c>
-      <c r="C730">
+      <c r="C730" s="1">
         <v>457.11</v>
       </c>
       <c r="D730">
@@ -17253,7 +17253,7 @@
       <c r="B731">
         <v>1438.18</v>
       </c>
-      <c r="C731">
+      <c r="C731" s="1">
         <v>341.98</v>
       </c>
       <c r="D731">
@@ -17276,7 +17276,7 @@
       <c r="B732">
         <v>704.8</v>
       </c>
-      <c r="C732">
+      <c r="C732" s="1">
         <v>351.7</v>
       </c>
       <c r="D732">
@@ -17299,7 +17299,7 @@
       <c r="B733">
         <v>1418.52</v>
       </c>
-      <c r="C733">
+      <c r="C733" s="1">
         <v>175.18</v>
       </c>
       <c r="D733">
@@ -17322,7 +17322,7 @@
       <c r="B734">
         <v>934.53</v>
       </c>
-      <c r="C734">
+      <c r="C734" s="1">
         <v>499.76</v>
       </c>
       <c r="D734">
@@ -17345,7 +17345,7 @@
       <c r="B735">
         <v>989.23</v>
       </c>
-      <c r="C735">
+      <c r="C735" s="1">
         <v>164.88</v>
       </c>
       <c r="D735">
@@ -17368,7 +17368,7 @@
       <c r="B736">
         <v>799.93</v>
       </c>
-      <c r="C736">
+      <c r="C736" s="1">
         <v>269.7</v>
       </c>
       <c r="D736">
@@ -17391,7 +17391,7 @@
       <c r="B737">
         <v>1174.04</v>
       </c>
-      <c r="C737">
+      <c r="C737" s="1">
         <v>127.18</v>
       </c>
       <c r="D737">
@@ -17414,7 +17414,7 @@
       <c r="B738">
         <v>910.73</v>
       </c>
-      <c r="C738">
+      <c r="C738" s="1">
         <v>320.87</v>
       </c>
       <c r="D738">
@@ -17437,7 +17437,7 @@
       <c r="B739">
         <v>1014.49</v>
       </c>
-      <c r="C739">
+      <c r="C739" s="1">
         <v>536.07000000000005</v>
       </c>
       <c r="D739">
@@ -17460,7 +17460,7 @@
       <c r="B740">
         <v>1364.37</v>
       </c>
-      <c r="C740">
+      <c r="C740" s="1">
         <v>448.12</v>
       </c>
       <c r="D740">
@@ -17483,7 +17483,7 @@
       <c r="B741">
         <v>1496.81</v>
       </c>
-      <c r="C741">
+      <c r="C741" s="1">
         <v>469.14</v>
       </c>
       <c r="D741">
@@ -17506,7 +17506,7 @@
       <c r="B742">
         <v>703.99</v>
       </c>
-      <c r="C742">
+      <c r="C742" s="1">
         <v>361.31</v>
       </c>
       <c r="D742">
@@ -17529,7 +17529,7 @@
       <c r="B743">
         <v>1339.45</v>
       </c>
-      <c r="C743">
+      <c r="C743" s="1">
         <v>569.83000000000004</v>
       </c>
       <c r="D743">
@@ -17552,7 +17552,7 @@
       <c r="B744">
         <v>1280.05</v>
       </c>
-      <c r="C744">
+      <c r="C744" s="1">
         <v>429.86</v>
       </c>
       <c r="D744">
@@ -17575,7 +17575,7 @@
       <c r="B745">
         <v>956.73</v>
       </c>
-      <c r="C745">
+      <c r="C745" s="1">
         <v>253.17</v>
       </c>
       <c r="D745">
@@ -17598,7 +17598,7 @@
       <c r="B746">
         <v>1483.71</v>
       </c>
-      <c r="C746">
+      <c r="C746" s="1">
         <v>185.59</v>
       </c>
       <c r="D746">
@@ -17621,7 +17621,7 @@
       <c r="B747">
         <v>1435.83</v>
       </c>
-      <c r="C747">
+      <c r="C747" s="1">
         <v>471.71</v>
       </c>
       <c r="D747">
@@ -17644,7 +17644,7 @@
       <c r="B748">
         <v>1068.43</v>
       </c>
-      <c r="C748">
+      <c r="C748" s="1">
         <v>529.94000000000005</v>
       </c>
       <c r="D748">
@@ -17667,7 +17667,7 @@
       <c r="B749">
         <v>1115.07</v>
       </c>
-      <c r="C749">
+      <c r="C749" s="1">
         <v>628.29</v>
       </c>
       <c r="D749">
@@ -17690,7 +17690,7 @@
       <c r="B750">
         <v>1458.87</v>
       </c>
-      <c r="C750">
+      <c r="C750" s="1">
         <v>250.06</v>
       </c>
       <c r="D750">
@@ -17713,7 +17713,7 @@
       <c r="B751">
         <v>947.55</v>
       </c>
-      <c r="C751">
+      <c r="C751" s="1">
         <v>440.61</v>
       </c>
       <c r="D751">
@@ -17736,7 +17736,7 @@
       <c r="B752">
         <v>586.97</v>
       </c>
-      <c r="C752">
+      <c r="C752" s="1">
         <v>147.69</v>
       </c>
       <c r="D752">
@@ -17759,7 +17759,7 @@
       <c r="B753">
         <v>1125.22</v>
       </c>
-      <c r="C753">
+      <c r="C753" s="1">
         <v>640.04999999999995</v>
       </c>
       <c r="D753">
@@ -17782,7 +17782,7 @@
       <c r="B754">
         <v>1037.54</v>
       </c>
-      <c r="C754">
+      <c r="C754" s="1">
         <v>111.12</v>
       </c>
       <c r="D754">
@@ -17805,7 +17805,7 @@
       <c r="B755">
         <v>1382.62</v>
       </c>
-      <c r="C755">
+      <c r="C755" s="1">
         <v>205.3</v>
       </c>
       <c r="D755">
@@ -17828,7 +17828,7 @@
       <c r="B756">
         <v>1103.25</v>
       </c>
-      <c r="C756">
+      <c r="C756" s="1">
         <v>235.69</v>
       </c>
       <c r="D756">
@@ -17851,7 +17851,7 @@
       <c r="B757">
         <v>513.66</v>
       </c>
-      <c r="C757">
+      <c r="C757" s="1">
         <v>281.42</v>
       </c>
       <c r="D757">
@@ -17874,7 +17874,7 @@
       <c r="B758">
         <v>1294.01</v>
       </c>
-      <c r="C758">
+      <c r="C758" s="1">
         <v>502.39</v>
       </c>
       <c r="D758">
@@ -17897,7 +17897,7 @@
       <c r="B759">
         <v>509.09</v>
       </c>
-      <c r="C759">
+      <c r="C759" s="1">
         <v>215.93</v>
       </c>
       <c r="D759">
@@ -17920,7 +17920,7 @@
       <c r="B760">
         <v>1206.96</v>
       </c>
-      <c r="C760">
+      <c r="C760" s="1">
         <v>515.58000000000004</v>
       </c>
       <c r="D760">
@@ -17943,7 +17943,7 @@
       <c r="B761">
         <v>592.45000000000005</v>
       </c>
-      <c r="C761">
+      <c r="C761" s="1">
         <v>194.89</v>
       </c>
       <c r="D761">
@@ -17966,7 +17966,7 @@
       <c r="B762">
         <v>1458.14</v>
       </c>
-      <c r="C762">
+      <c r="C762" s="1">
         <v>326.35000000000002</v>
       </c>
       <c r="D762">
@@ -17989,7 +17989,7 @@
       <c r="B763">
         <v>673.02</v>
       </c>
-      <c r="C763">
+      <c r="C763" s="1">
         <v>157.07</v>
       </c>
       <c r="D763">
@@ -18012,7 +18012,7 @@
       <c r="B764">
         <v>853.47</v>
       </c>
-      <c r="C764">
+      <c r="C764" s="1">
         <v>220.04</v>
       </c>
       <c r="D764">
@@ -18035,7 +18035,7 @@
       <c r="B765">
         <v>1483.34</v>
       </c>
-      <c r="C765">
+      <c r="C765" s="1">
         <v>327.52</v>
       </c>
       <c r="D765">
@@ -18058,7 +18058,7 @@
       <c r="B766">
         <v>564.09</v>
       </c>
-      <c r="C766">
+      <c r="C766" s="1">
         <v>224.55</v>
       </c>
       <c r="D766">
@@ -18081,7 +18081,7 @@
       <c r="B767">
         <v>619.02</v>
       </c>
-      <c r="C767">
+      <c r="C767" s="1">
         <v>83.24</v>
       </c>
       <c r="D767">
@@ -18104,7 +18104,7 @@
       <c r="B768">
         <v>625.64</v>
       </c>
-      <c r="C768">
+      <c r="C768" s="1">
         <v>153.19999999999999</v>
       </c>
       <c r="D768">
@@ -18127,7 +18127,7 @@
       <c r="B769">
         <v>639.32000000000005</v>
       </c>
-      <c r="C769">
+      <c r="C769" s="1">
         <v>340.83</v>
       </c>
       <c r="D769">
@@ -18150,7 +18150,7 @@
       <c r="B770">
         <v>568.04</v>
       </c>
-      <c r="C770">
+      <c r="C770" s="1">
         <v>146.81</v>
       </c>
       <c r="D770">
@@ -18173,7 +18173,7 @@
       <c r="B771">
         <v>1144.49</v>
       </c>
-      <c r="C771">
+      <c r="C771" s="1">
         <v>219.09</v>
       </c>
       <c r="D771">
@@ -18196,7 +18196,7 @@
       <c r="B772">
         <v>909.18</v>
       </c>
-      <c r="C772">
+      <c r="C772" s="1">
         <v>240.65</v>
       </c>
       <c r="D772">
@@ -18219,7 +18219,7 @@
       <c r="B773">
         <v>1483.91</v>
       </c>
-      <c r="C773">
+      <c r="C773" s="1">
         <v>823.38</v>
       </c>
       <c r="D773">
@@ -18242,7 +18242,7 @@
       <c r="B774">
         <v>1109.68</v>
       </c>
-      <c r="C774">
+      <c r="C774" s="1">
         <v>618.70000000000005</v>
       </c>
       <c r="D774">
@@ -18265,7 +18265,7 @@
       <c r="B775">
         <v>1018.28</v>
       </c>
-      <c r="C775">
+      <c r="C775" s="1">
         <v>469.54</v>
       </c>
       <c r="D775">
@@ -18288,7 +18288,7 @@
       <c r="B776">
         <v>551.16999999999996</v>
       </c>
-      <c r="C776">
+      <c r="C776" s="1">
         <v>119.29</v>
       </c>
       <c r="D776">
@@ -18311,7 +18311,7 @@
       <c r="B777">
         <v>946.17</v>
       </c>
-      <c r="C777">
+      <c r="C777" s="1">
         <v>356.7</v>
       </c>
       <c r="D777">
@@ -18334,7 +18334,7 @@
       <c r="B778">
         <v>1121.1099999999999</v>
       </c>
-      <c r="C778">
+      <c r="C778" s="1">
         <v>281.29000000000002</v>
       </c>
       <c r="D778">
@@ -18357,7 +18357,7 @@
       <c r="B779">
         <v>1146.4100000000001</v>
       </c>
-      <c r="C779">
+      <c r="C779" s="1">
         <v>377.38</v>
       </c>
       <c r="D779">
@@ -18380,7 +18380,7 @@
       <c r="B780">
         <v>1366.18</v>
       </c>
-      <c r="C780">
+      <c r="C780" s="1">
         <v>477.61</v>
       </c>
       <c r="D780">
@@ -18403,7 +18403,7 @@
       <c r="B781">
         <v>1377.13</v>
       </c>
-      <c r="C781">
+      <c r="C781" s="1">
         <v>501.4</v>
       </c>
       <c r="D781">
@@ -18426,7 +18426,7 @@
       <c r="B782">
         <v>629.09</v>
       </c>
-      <c r="C782">
+      <c r="C782" s="1">
         <v>296.39</v>
       </c>
       <c r="D782">
@@ -18449,7 +18449,7 @@
       <c r="B783">
         <v>633.53</v>
       </c>
-      <c r="C783">
+      <c r="C783" s="1">
         <v>185.85</v>
       </c>
       <c r="D783">
@@ -18472,7 +18472,7 @@
       <c r="B784">
         <v>1235.92</v>
       </c>
-      <c r="C784">
+      <c r="C784" s="1">
         <v>293.58999999999997</v>
       </c>
       <c r="D784">
@@ -18495,7 +18495,7 @@
       <c r="B785">
         <v>1154.22</v>
       </c>
-      <c r="C785">
+      <c r="C785" s="1">
         <v>691.49</v>
       </c>
       <c r="D785">
@@ -18518,7 +18518,7 @@
       <c r="B786">
         <v>565.28</v>
       </c>
-      <c r="C786">
+      <c r="C786" s="1">
         <v>288.81</v>
       </c>
       <c r="D786">
@@ -18541,7 +18541,7 @@
       <c r="B787">
         <v>712.66</v>
       </c>
-      <c r="C787">
+      <c r="C787" s="1">
         <v>105.84</v>
       </c>
       <c r="D787">
@@ -18564,7 +18564,7 @@
       <c r="B788">
         <v>926.89</v>
       </c>
-      <c r="C788">
+      <c r="C788" s="1">
         <v>310.06</v>
       </c>
       <c r="D788">
@@ -18587,7 +18587,7 @@
       <c r="B789">
         <v>1481.04</v>
       </c>
-      <c r="C789">
+      <c r="C789" s="1">
         <v>638.19000000000005</v>
       </c>
       <c r="D789">
@@ -18610,7 +18610,7 @@
       <c r="B790">
         <v>557.09</v>
       </c>
-      <c r="C790">
+      <c r="C790" s="1">
         <v>151.27000000000001</v>
       </c>
       <c r="D790">
@@ -18633,7 +18633,7 @@
       <c r="B791">
         <v>949.04</v>
       </c>
-      <c r="C791">
+      <c r="C791" s="1">
         <v>312.85000000000002</v>
       </c>
       <c r="D791">
@@ -18656,7 +18656,7 @@
       <c r="B792">
         <v>1072.76</v>
       </c>
-      <c r="C792">
+      <c r="C792" s="1">
         <v>180.88</v>
       </c>
       <c r="D792">
@@ -18679,7 +18679,7 @@
       <c r="B793">
         <v>1131.05</v>
       </c>
-      <c r="C793">
+      <c r="C793" s="1">
         <v>127.23</v>
       </c>
       <c r="D793">
@@ -18702,7 +18702,7 @@
       <c r="B794">
         <v>842.4</v>
       </c>
-      <c r="C794">
+      <c r="C794" s="1">
         <v>314.41000000000003</v>
       </c>
       <c r="D794">
@@ -18725,7 +18725,7 @@
       <c r="B795">
         <v>557</v>
       </c>
-      <c r="C795">
+      <c r="C795" s="1">
         <v>219.4</v>
       </c>
       <c r="D795">
@@ -18748,7 +18748,7 @@
       <c r="B796">
         <v>826.74</v>
       </c>
-      <c r="C796">
+      <c r="C796" s="1">
         <v>227.19</v>
       </c>
       <c r="D796">
@@ -18771,7 +18771,7 @@
       <c r="B797">
         <v>1215.6199999999999</v>
       </c>
-      <c r="C797">
+      <c r="C797" s="1">
         <v>539.09</v>
       </c>
       <c r="D797">
@@ -18794,7 +18794,7 @@
       <c r="B798">
         <v>629.86</v>
       </c>
-      <c r="C798">
+      <c r="C798" s="1">
         <v>275.94</v>
       </c>
       <c r="D798">
@@ -18817,7 +18817,7 @@
       <c r="B799">
         <v>1281.46</v>
       </c>
-      <c r="C799">
+      <c r="C799" s="1">
         <v>578.76</v>
       </c>
       <c r="D799">
@@ -18840,7 +18840,7 @@
       <c r="B800">
         <v>1140.45</v>
       </c>
-      <c r="C800">
+      <c r="C800" s="1">
         <v>293.19</v>
       </c>
       <c r="D800">
@@ -18863,7 +18863,7 @@
       <c r="B801">
         <v>717.73</v>
       </c>
-      <c r="C801">
+      <c r="C801" s="1">
         <v>294.70999999999998</v>
       </c>
       <c r="D801">
@@ -18886,7 +18886,7 @@
       <c r="B802">
         <v>1258.98</v>
       </c>
-      <c r="C802">
+      <c r="C802" s="1">
         <v>441.03</v>
       </c>
       <c r="D802">
@@ -18909,7 +18909,7 @@
       <c r="B803">
         <v>850.78</v>
       </c>
-      <c r="C803">
+      <c r="C803" s="1">
         <v>439.3</v>
       </c>
       <c r="D803">
@@ -18932,7 +18932,7 @@
       <c r="B804">
         <v>1484.09</v>
       </c>
-      <c r="C804">
+      <c r="C804" s="1">
         <v>365.27</v>
       </c>
       <c r="D804">
@@ -18955,7 +18955,7 @@
       <c r="B805">
         <v>1395.82</v>
       </c>
-      <c r="C805">
+      <c r="C805" s="1">
         <v>211.8</v>
       </c>
       <c r="D805">
@@ -18978,7 +18978,7 @@
       <c r="B806">
         <v>1045.67</v>
       </c>
-      <c r="C806">
+      <c r="C806" s="1">
         <v>462.17</v>
       </c>
       <c r="D806">
@@ -19001,7 +19001,7 @@
       <c r="B807">
         <v>1013.26</v>
       </c>
-      <c r="C807">
+      <c r="C807" s="1">
         <v>155.65</v>
       </c>
       <c r="D807">
@@ -19024,7 +19024,7 @@
       <c r="B808">
         <v>597.61</v>
       </c>
-      <c r="C808">
+      <c r="C808" s="1">
         <v>109.62</v>
       </c>
       <c r="D808">
@@ -19047,7 +19047,7 @@
       <c r="B809">
         <v>718.3</v>
       </c>
-      <c r="C809">
+      <c r="C809" s="1">
         <v>91.47</v>
       </c>
       <c r="D809">
@@ -19070,7 +19070,7 @@
       <c r="B810">
         <v>1390.97</v>
       </c>
-      <c r="C810">
+      <c r="C810" s="1">
         <v>535.17999999999995</v>
       </c>
       <c r="D810">
@@ -19093,7 +19093,7 @@
       <c r="B811">
         <v>1185.6500000000001</v>
       </c>
-      <c r="C811">
+      <c r="C811" s="1">
         <v>252.71</v>
       </c>
       <c r="D811">
@@ -19116,7 +19116,7 @@
       <c r="B812">
         <v>1280.7</v>
       </c>
-      <c r="C812">
+      <c r="C812" s="1">
         <v>710.91</v>
       </c>
       <c r="D812">
@@ -19139,7 +19139,7 @@
       <c r="B813">
         <v>598.34</v>
       </c>
-      <c r="C813">
+      <c r="C813" s="1">
         <v>194.25</v>
       </c>
       <c r="D813">
@@ -19162,7 +19162,7 @@
       <c r="B814">
         <v>752.84</v>
       </c>
-      <c r="C814">
+      <c r="C814" s="1">
         <v>100.61</v>
       </c>
       <c r="D814">
@@ -19185,7 +19185,7 @@
       <c r="B815">
         <v>528.12</v>
       </c>
-      <c r="C815">
+      <c r="C815" s="1">
         <v>151.91999999999999</v>
       </c>
       <c r="D815">
@@ -19208,7 +19208,7 @@
       <c r="B816">
         <v>1152.28</v>
       </c>
-      <c r="C816">
+      <c r="C816" s="1">
         <v>348.68</v>
       </c>
       <c r="D816">
@@ -19231,7 +19231,7 @@
       <c r="B817">
         <v>507.04</v>
       </c>
-      <c r="C817">
+      <c r="C817" s="1">
         <v>254.91</v>
       </c>
       <c r="D817">
@@ -19254,7 +19254,7 @@
       <c r="B818">
         <v>1415.81</v>
       </c>
-      <c r="C818">
+      <c r="C818" s="1">
         <v>497.57</v>
       </c>
       <c r="D818">
@@ -19277,7 +19277,7 @@
       <c r="B819">
         <v>1281.73</v>
       </c>
-      <c r="C819">
+      <c r="C819" s="1">
         <v>258.75</v>
       </c>
       <c r="D819">
@@ -19300,7 +19300,7 @@
       <c r="B820">
         <v>1129.68</v>
       </c>
-      <c r="C820">
+      <c r="C820" s="1">
         <v>348.03</v>
       </c>
       <c r="D820">
@@ -19323,7 +19323,7 @@
       <c r="B821">
         <v>1157.95</v>
       </c>
-      <c r="C821">
+      <c r="C821" s="1">
         <v>536.99</v>
       </c>
       <c r="D821">
@@ -19346,7 +19346,7 @@
       <c r="B822">
         <v>945.89</v>
       </c>
-      <c r="C822">
+      <c r="C822" s="1">
         <v>429.71</v>
       </c>
       <c r="D822">
@@ -19369,7 +19369,7 @@
       <c r="B823">
         <v>1496.22</v>
       </c>
-      <c r="C823">
+      <c r="C823" s="1">
         <v>504.63</v>
       </c>
       <c r="D823">
@@ -19392,7 +19392,7 @@
       <c r="B824">
         <v>1391.02</v>
       </c>
-      <c r="C824">
+      <c r="C824" s="1">
         <v>704.98</v>
       </c>
       <c r="D824">
@@ -19415,7 +19415,7 @@
       <c r="B825">
         <v>516.66999999999996</v>
       </c>
-      <c r="C825">
+      <c r="C825" s="1">
         <v>277.33</v>
       </c>
       <c r="D825">
@@ -19438,7 +19438,7 @@
       <c r="B826">
         <v>1121.98</v>
       </c>
-      <c r="C826">
+      <c r="C826" s="1">
         <v>606.98</v>
       </c>
       <c r="D826">
@@ -19461,7 +19461,7 @@
       <c r="B827">
         <v>508.62</v>
       </c>
-      <c r="C827">
+      <c r="C827" s="1">
         <v>55.94</v>
       </c>
       <c r="D827">
@@ -19484,7 +19484,7 @@
       <c r="B828">
         <v>1250.54</v>
       </c>
-      <c r="C828">
+      <c r="C828" s="1">
         <v>591.77</v>
       </c>
       <c r="D828">
@@ -19507,7 +19507,7 @@
       <c r="B829">
         <v>851.72</v>
       </c>
-      <c r="C829">
+      <c r="C829" s="1">
         <v>272.63</v>
       </c>
       <c r="D829">
@@ -19530,7 +19530,7 @@
       <c r="B830">
         <v>529.16999999999996</v>
       </c>
-      <c r="C830">
+      <c r="C830" s="1">
         <v>196.12</v>
       </c>
       <c r="D830">
@@ -19553,7 +19553,7 @@
       <c r="B831">
         <v>980.18</v>
       </c>
-      <c r="C831">
+      <c r="C831" s="1">
         <v>336.15</v>
       </c>
       <c r="D831">
@@ -19576,7 +19576,7 @@
       <c r="B832">
         <v>1218.7</v>
       </c>
-      <c r="C832">
+      <c r="C832" s="1">
         <v>479.09</v>
       </c>
       <c r="D832">
@@ -19599,7 +19599,7 @@
       <c r="B833">
         <v>1033.06</v>
       </c>
-      <c r="C833">
+      <c r="C833" s="1">
         <v>429.52</v>
       </c>
       <c r="D833">
@@ -19622,7 +19622,7 @@
       <c r="B834">
         <v>1429.94</v>
       </c>
-      <c r="C834">
+      <c r="C834" s="1">
         <v>470.95</v>
       </c>
       <c r="D834">
@@ -19645,7 +19645,7 @@
       <c r="B835">
         <v>1210.42</v>
       </c>
-      <c r="C835">
+      <c r="C835" s="1">
         <v>374.58</v>
       </c>
       <c r="D835">
@@ -19668,7 +19668,7 @@
       <c r="B836">
         <v>1214.9000000000001</v>
       </c>
-      <c r="C836">
+      <c r="C836" s="1">
         <v>382.6</v>
       </c>
       <c r="D836">
@@ -19691,7 +19691,7 @@
       <c r="B837">
         <v>1173.42</v>
       </c>
-      <c r="C837">
+      <c r="C837" s="1">
         <v>477.87</v>
       </c>
       <c r="D837">
@@ -19714,7 +19714,7 @@
       <c r="B838">
         <v>906.9</v>
       </c>
-      <c r="C838">
+      <c r="C838" s="1">
         <v>190.77</v>
       </c>
       <c r="D838">
@@ -19737,7 +19737,7 @@
       <c r="B839">
         <v>706.8</v>
       </c>
-      <c r="C839">
+      <c r="C839" s="1">
         <v>397.6</v>
       </c>
       <c r="D839">
@@ -19760,7 +19760,7 @@
       <c r="B840">
         <v>838.51</v>
       </c>
-      <c r="C840">
+      <c r="C840" s="1">
         <v>86.82</v>
       </c>
       <c r="D840">
@@ -19783,7 +19783,7 @@
       <c r="B841">
         <v>531.51</v>
       </c>
-      <c r="C841">
+      <c r="C841" s="1">
         <v>85.47</v>
       </c>
       <c r="D841">
@@ -19806,7 +19806,7 @@
       <c r="B842">
         <v>1310.94</v>
       </c>
-      <c r="C842">
+      <c r="C842" s="1">
         <v>393.51</v>
       </c>
       <c r="D842">
@@ -19829,7 +19829,7 @@
       <c r="B843">
         <v>587.41999999999996</v>
       </c>
-      <c r="C843">
+      <c r="C843" s="1">
         <v>333.8</v>
       </c>
       <c r="D843">
@@ -19852,7 +19852,7 @@
       <c r="B844">
         <v>789.15</v>
       </c>
-      <c r="C844">
+      <c r="C844" s="1">
         <v>454.65</v>
       </c>
       <c r="D844">
@@ -19875,7 +19875,7 @@
       <c r="B845">
         <v>1482.86</v>
       </c>
-      <c r="C845">
+      <c r="C845" s="1">
         <v>546.04</v>
       </c>
       <c r="D845">
@@ -19898,7 +19898,7 @@
       <c r="B846">
         <v>1432.27</v>
       </c>
-      <c r="C846">
+      <c r="C846" s="1">
         <v>620.13</v>
       </c>
       <c r="D846">
@@ -19921,7 +19921,7 @@
       <c r="B847">
         <v>1184.44</v>
       </c>
-      <c r="C847">
+      <c r="C847" s="1">
         <v>416.46</v>
       </c>
       <c r="D847">
@@ -19944,7 +19944,7 @@
       <c r="B848">
         <v>1036.53</v>
       </c>
-      <c r="C848">
+      <c r="C848" s="1">
         <v>549.33000000000004</v>
       </c>
       <c r="D848">
@@ -19967,7 +19967,7 @@
       <c r="B849">
         <v>1126.83</v>
       </c>
-      <c r="C849">
+      <c r="C849" s="1">
         <v>255.34</v>
       </c>
       <c r="D849">
@@ -19990,7 +19990,7 @@
       <c r="B850">
         <v>954.96</v>
       </c>
-      <c r="C850">
+      <c r="C850" s="1">
         <v>455.26</v>
       </c>
       <c r="D850">
@@ -20013,7 +20013,7 @@
       <c r="B851">
         <v>500.63</v>
       </c>
-      <c r="C851">
+      <c r="C851" s="1">
         <v>291.14</v>
       </c>
       <c r="D851">
@@ -20036,7 +20036,7 @@
       <c r="B852">
         <v>628.9</v>
       </c>
-      <c r="C852">
+      <c r="C852" s="1">
         <v>289.29000000000002</v>
       </c>
       <c r="D852">
@@ -20059,7 +20059,7 @@
       <c r="B853">
         <v>735.68</v>
       </c>
-      <c r="C853">
+      <c r="C853" s="1">
         <v>336.08</v>
       </c>
       <c r="D853">
@@ -20082,7 +20082,7 @@
       <c r="B854">
         <v>544.51</v>
       </c>
-      <c r="C854">
+      <c r="C854" s="1">
         <v>133.16999999999999</v>
       </c>
       <c r="D854">
@@ -20105,7 +20105,7 @@
       <c r="B855">
         <v>1314.63</v>
       </c>
-      <c r="C855">
+      <c r="C855" s="1">
         <v>746.81</v>
       </c>
       <c r="D855">
@@ -20128,7 +20128,7 @@
       <c r="B856">
         <v>1084.4000000000001</v>
       </c>
-      <c r="C856">
+      <c r="C856" s="1">
         <v>540.5</v>
       </c>
       <c r="D856">
@@ -20151,7 +20151,7 @@
       <c r="B857">
         <v>833.3</v>
       </c>
-      <c r="C857">
+      <c r="C857" s="1">
         <v>288.29000000000002</v>
       </c>
       <c r="D857">
@@ -20174,7 +20174,7 @@
       <c r="B858">
         <v>1027.76</v>
       </c>
-      <c r="C858">
+      <c r="C858" s="1">
         <v>389.23</v>
       </c>
       <c r="D858">
@@ -20197,7 +20197,7 @@
       <c r="B859">
         <v>535.16</v>
       </c>
-      <c r="C859">
+      <c r="C859" s="1">
         <v>139.97999999999999</v>
       </c>
       <c r="D859">
@@ -20220,7 +20220,7 @@
       <c r="B860">
         <v>1172.3599999999999</v>
       </c>
-      <c r="C860">
+      <c r="C860" s="1">
         <v>309.95</v>
       </c>
       <c r="D860">
@@ -20243,7 +20243,7 @@
       <c r="B861">
         <v>1209.3</v>
       </c>
-      <c r="C861">
+      <c r="C861" s="1">
         <v>133.72</v>
       </c>
       <c r="D861">
@@ -20266,7 +20266,7 @@
       <c r="B862">
         <v>1445.31</v>
       </c>
-      <c r="C862">
+      <c r="C862" s="1">
         <v>807.26</v>
       </c>
       <c r="D862">
@@ -20289,7 +20289,7 @@
       <c r="B863">
         <v>928.88</v>
       </c>
-      <c r="C863">
+      <c r="C863" s="1">
         <v>180.66</v>
       </c>
       <c r="D863">
@@ -20312,7 +20312,7 @@
       <c r="B864">
         <v>581.94000000000005</v>
       </c>
-      <c r="C864">
+      <c r="C864" s="1">
         <v>115.22</v>
       </c>
       <c r="D864">
@@ -20335,7 +20335,7 @@
       <c r="B865">
         <v>1414.69</v>
       </c>
-      <c r="C865">
+      <c r="C865" s="1">
         <v>490.58</v>
       </c>
       <c r="D865">
@@ -20358,7 +20358,7 @@
       <c r="B866">
         <v>702.08</v>
       </c>
-      <c r="C866">
+      <c r="C866" s="1">
         <v>108.85</v>
       </c>
       <c r="D866">
@@ -20381,7 +20381,7 @@
       <c r="B867">
         <v>651.26</v>
       </c>
-      <c r="C867">
+      <c r="C867" s="1">
         <v>157.83000000000001</v>
       </c>
       <c r="D867">
@@ -20404,7 +20404,7 @@
       <c r="B868">
         <v>813.48</v>
       </c>
-      <c r="C868">
+      <c r="C868" s="1">
         <v>333.75</v>
       </c>
       <c r="D868">
@@ -20427,7 +20427,7 @@
       <c r="B869">
         <v>861.67</v>
       </c>
-      <c r="C869">
+      <c r="C869" s="1">
         <v>132.87</v>
       </c>
       <c r="D869">
@@ -20450,7 +20450,7 @@
       <c r="B870">
         <v>527.47</v>
       </c>
-      <c r="C870">
+      <c r="C870" s="1">
         <v>159.19999999999999</v>
       </c>
       <c r="D870">
@@ -20473,7 +20473,7 @@
       <c r="B871">
         <v>1179.97</v>
       </c>
-      <c r="C871">
+      <c r="C871" s="1">
         <v>237.69</v>
       </c>
       <c r="D871">
@@ -20496,7 +20496,7 @@
       <c r="B872">
         <v>654.79</v>
       </c>
-      <c r="C872">
+      <c r="C872" s="1">
         <v>164.08</v>
       </c>
       <c r="D872">
@@ -20519,7 +20519,7 @@
       <c r="B873">
         <v>1066.52</v>
       </c>
-      <c r="C873">
+      <c r="C873" s="1">
         <v>453.03</v>
       </c>
       <c r="D873">
@@ -20542,7 +20542,7 @@
       <c r="B874">
         <v>1336.44</v>
       </c>
-      <c r="C874">
+      <c r="C874" s="1">
         <v>475.73</v>
       </c>
       <c r="D874">
@@ -20565,7 +20565,7 @@
       <c r="B875">
         <v>710.12</v>
       </c>
-      <c r="C875">
+      <c r="C875" s="1">
         <v>112.32</v>
       </c>
       <c r="D875">
@@ -20588,7 +20588,7 @@
       <c r="B876">
         <v>589.82000000000005</v>
       </c>
-      <c r="C876">
+      <c r="C876" s="1">
         <v>134.72</v>
       </c>
       <c r="D876">
@@ -20611,7 +20611,7 @@
       <c r="B877">
         <v>1342.19</v>
       </c>
-      <c r="C877">
+      <c r="C877" s="1">
         <v>274.68</v>
       </c>
       <c r="D877">
@@ -20634,7 +20634,7 @@
       <c r="B878">
         <v>1021.71</v>
       </c>
-      <c r="C878">
+      <c r="C878" s="1">
         <v>236.36</v>
       </c>
       <c r="D878">
@@ -20657,7 +20657,7 @@
       <c r="B879">
         <v>1388.75</v>
       </c>
-      <c r="C879">
+      <c r="C879" s="1">
         <v>619.74</v>
       </c>
       <c r="D879">
@@ -20680,7 +20680,7 @@
       <c r="B880">
         <v>653.41</v>
       </c>
-      <c r="C880">
+      <c r="C880" s="1">
         <v>185.1</v>
       </c>
       <c r="D880">
@@ -20703,7 +20703,7 @@
       <c r="B881">
         <v>547.22</v>
       </c>
-      <c r="C881">
+      <c r="C881" s="1">
         <v>103</v>
       </c>
       <c r="D881">
@@ -20726,7 +20726,7 @@
       <c r="B882">
         <v>1078.56</v>
       </c>
-      <c r="C882">
+      <c r="C882" s="1">
         <v>599.33000000000004</v>
       </c>
       <c r="D882">
@@ -20749,7 +20749,7 @@
       <c r="B883">
         <v>919.48</v>
       </c>
-      <c r="C883">
+      <c r="C883" s="1">
         <v>271.57</v>
       </c>
       <c r="D883">
@@ -20772,7 +20772,7 @@
       <c r="B884">
         <v>1240.51</v>
       </c>
-      <c r="C884">
+      <c r="C884" s="1">
         <v>593.54</v>
       </c>
       <c r="D884">
@@ -20795,7 +20795,7 @@
       <c r="B885">
         <v>1391.87</v>
       </c>
-      <c r="C885">
+      <c r="C885" s="1">
         <v>339.04</v>
       </c>
       <c r="D885">
@@ -20818,7 +20818,7 @@
       <c r="B886">
         <v>1119.58</v>
       </c>
-      <c r="C886">
+      <c r="C886" s="1">
         <v>483.37</v>
       </c>
       <c r="D886">
@@ -20841,7 +20841,7 @@
       <c r="B887">
         <v>962.04</v>
       </c>
-      <c r="C887">
+      <c r="C887" s="1">
         <v>530.58000000000004</v>
       </c>
       <c r="D887">
@@ -20864,7 +20864,7 @@
       <c r="B888">
         <v>1138.22</v>
       </c>
-      <c r="C888">
+      <c r="C888" s="1">
         <v>313.02</v>
       </c>
       <c r="D888">
@@ -20887,7 +20887,7 @@
       <c r="B889">
         <v>1121.94</v>
       </c>
-      <c r="C889">
+      <c r="C889" s="1">
         <v>452.59</v>
       </c>
       <c r="D889">
@@ -20910,7 +20910,7 @@
       <c r="B890">
         <v>562.44000000000005</v>
       </c>
-      <c r="C890">
+      <c r="C890" s="1">
         <v>164.22</v>
       </c>
       <c r="D890">
@@ -20933,7 +20933,7 @@
       <c r="B891">
         <v>642.79</v>
       </c>
-      <c r="C891">
+      <c r="C891" s="1">
         <v>189.44</v>
       </c>
       <c r="D891">
@@ -20956,7 +20956,7 @@
       <c r="B892">
         <v>793.79</v>
       </c>
-      <c r="C892">
+      <c r="C892" s="1">
         <v>346.12</v>
       </c>
       <c r="D892">
@@ -20979,7 +20979,7 @@
       <c r="B893">
         <v>876.19</v>
       </c>
-      <c r="C893">
+      <c r="C893" s="1">
         <v>248.55</v>
       </c>
       <c r="D893">
@@ -21002,7 +21002,7 @@
       <c r="B894">
         <v>1228.42</v>
       </c>
-      <c r="C894">
+      <c r="C894" s="1">
         <v>317.20999999999998</v>
       </c>
       <c r="D894">
@@ -21025,7 +21025,7 @@
       <c r="B895">
         <v>1009.51</v>
       </c>
-      <c r="C895">
+      <c r="C895" s="1">
         <v>376.42</v>
       </c>
       <c r="D895">
@@ -21048,7 +21048,7 @@
       <c r="B896">
         <v>815.42</v>
       </c>
-      <c r="C896">
+      <c r="C896" s="1">
         <v>359.84</v>
       </c>
       <c r="D896">
@@ -21071,7 +21071,7 @@
       <c r="B897">
         <v>743.12</v>
       </c>
-      <c r="C897">
+      <c r="C897" s="1">
         <v>351.03</v>
       </c>
       <c r="D897">
@@ -21094,7 +21094,7 @@
       <c r="B898">
         <v>747.46</v>
       </c>
-      <c r="C898">
+      <c r="C898" s="1">
         <v>315.89</v>
       </c>
       <c r="D898">
@@ -21117,7 +21117,7 @@
       <c r="B899">
         <v>1197.8599999999999</v>
       </c>
-      <c r="C899">
+      <c r="C899" s="1">
         <v>280.45</v>
       </c>
       <c r="D899">
@@ -21140,7 +21140,7 @@
       <c r="B900">
         <v>1069.23</v>
       </c>
-      <c r="C900">
+      <c r="C900" s="1">
         <v>599.17999999999995</v>
       </c>
       <c r="D900">
@@ -21163,7 +21163,7 @@
       <c r="B901">
         <v>1348.48</v>
       </c>
-      <c r="C901">
+      <c r="C901" s="1">
         <v>745.72</v>
       </c>
       <c r="D901">
@@ -21186,7 +21186,7 @@
       <c r="B902">
         <v>856.77</v>
       </c>
-      <c r="C902">
+      <c r="C902" s="1">
         <v>156.05000000000001</v>
       </c>
       <c r="D902">
@@ -21209,7 +21209,7 @@
       <c r="B903">
         <v>1025.77</v>
       </c>
-      <c r="C903">
+      <c r="C903" s="1">
         <v>470.88</v>
       </c>
       <c r="D903">
@@ -21232,7 +21232,7 @@
       <c r="B904">
         <v>673.67</v>
       </c>
-      <c r="C904">
+      <c r="C904" s="1">
         <v>299.83999999999997</v>
       </c>
       <c r="D904">
@@ -21255,7 +21255,7 @@
       <c r="B905">
         <v>1333.19</v>
       </c>
-      <c r="C905">
+      <c r="C905" s="1">
         <v>417.82</v>
       </c>
       <c r="D905">
@@ -21278,7 +21278,7 @@
       <c r="B906">
         <v>1490.64</v>
       </c>
-      <c r="C906">
+      <c r="C906" s="1">
         <v>356.18</v>
       </c>
       <c r="D906">
@@ -21301,7 +21301,7 @@
       <c r="B907">
         <v>1296.29</v>
       </c>
-      <c r="C907">
+      <c r="C907" s="1">
         <v>507.54</v>
       </c>
       <c r="D907">
@@ -21324,7 +21324,7 @@
       <c r="B908">
         <v>799.25</v>
       </c>
-      <c r="C908">
+      <c r="C908" s="1">
         <v>378.89</v>
       </c>
       <c r="D908">
@@ -21347,7 +21347,7 @@
       <c r="B909">
         <v>1274.93</v>
       </c>
-      <c r="C909">
+      <c r="C909" s="1">
         <v>596.19000000000005</v>
       </c>
       <c r="D909">
@@ -21370,7 +21370,7 @@
       <c r="B910">
         <v>558.24</v>
       </c>
-      <c r="C910">
+      <c r="C910" s="1">
         <v>129.03</v>
       </c>
       <c r="D910">
@@ -21393,7 +21393,7 @@
       <c r="B911">
         <v>680.87</v>
       </c>
-      <c r="C911">
+      <c r="C911" s="1">
         <v>318.23</v>
       </c>
       <c r="D911">
@@ -21416,7 +21416,7 @@
       <c r="B912">
         <v>1165.8599999999999</v>
       </c>
-      <c r="C912">
+      <c r="C912" s="1">
         <v>337.33</v>
       </c>
       <c r="D912">
@@ -21439,7 +21439,7 @@
       <c r="B913">
         <v>532.49</v>
       </c>
-      <c r="C913">
+      <c r="C913" s="1">
         <v>211.74</v>
       </c>
       <c r="D913">
@@ -21462,7 +21462,7 @@
       <c r="B914">
         <v>1051.69</v>
       </c>
-      <c r="C914">
+      <c r="C914" s="1">
         <v>547.45000000000005</v>
       </c>
       <c r="D914">
@@ -21485,7 +21485,7 @@
       <c r="B915">
         <v>847.29</v>
       </c>
-      <c r="C915">
+      <c r="C915" s="1">
         <v>197.09</v>
       </c>
       <c r="D915">
@@ -21508,7 +21508,7 @@
       <c r="B916">
         <v>1202.32</v>
       </c>
-      <c r="C916">
+      <c r="C916" s="1">
         <v>632.4</v>
       </c>
       <c r="D916">
@@ -21531,7 +21531,7 @@
       <c r="B917">
         <v>1147.52</v>
       </c>
-      <c r="C917">
+      <c r="C917" s="1">
         <v>670.69</v>
       </c>
       <c r="D917">
@@ -21554,7 +21554,7 @@
       <c r="B918">
         <v>626.87</v>
       </c>
-      <c r="C918">
+      <c r="C918" s="1">
         <v>248.4</v>
       </c>
       <c r="D918">
@@ -21577,7 +21577,7 @@
       <c r="B919">
         <v>992.4</v>
       </c>
-      <c r="C919">
+      <c r="C919" s="1">
         <v>514.42999999999995</v>
       </c>
       <c r="D919">
@@ -21600,7 +21600,7 @@
       <c r="B920">
         <v>888.67</v>
       </c>
-      <c r="C920">
+      <c r="C920" s="1">
         <v>286.02</v>
       </c>
       <c r="D920">
@@ -21623,7 +21623,7 @@
       <c r="B921">
         <v>1483.39</v>
       </c>
-      <c r="C921">
+      <c r="C921" s="1">
         <v>772.18</v>
       </c>
       <c r="D921">
@@ -21646,7 +21646,7 @@
       <c r="B922">
         <v>1415.14</v>
       </c>
-      <c r="C922">
+      <c r="C922" s="1">
         <v>746.14</v>
       </c>
       <c r="D922">
@@ -21669,7 +21669,7 @@
       <c r="B923">
         <v>732.9</v>
       </c>
-      <c r="C923">
+      <c r="C923" s="1">
         <v>383.06</v>
       </c>
       <c r="D923">
@@ -21692,7 +21692,7 @@
       <c r="B924">
         <v>711.8</v>
       </c>
-      <c r="C924">
+      <c r="C924" s="1">
         <v>353.24</v>
       </c>
       <c r="D924">
@@ -21715,7 +21715,7 @@
       <c r="B925">
         <v>732.6</v>
       </c>
-      <c r="C925">
+      <c r="C925" s="1">
         <v>115.57</v>
       </c>
       <c r="D925">
@@ -21738,7 +21738,7 @@
       <c r="B926">
         <v>1169.32</v>
       </c>
-      <c r="C926">
+      <c r="C926" s="1">
         <v>636.27</v>
       </c>
       <c r="D926">
@@ -21761,7 +21761,7 @@
       <c r="B927">
         <v>1196.3599999999999</v>
       </c>
-      <c r="C927">
+      <c r="C927" s="1">
         <v>521.6</v>
       </c>
       <c r="D927">
@@ -21784,7 +21784,7 @@
       <c r="B928">
         <v>1021.83</v>
       </c>
-      <c r="C928">
+      <c r="C928" s="1">
         <v>401.4</v>
       </c>
       <c r="D928">
@@ -21807,7 +21807,7 @@
       <c r="B929">
         <v>783.22</v>
       </c>
-      <c r="C929">
+      <c r="C929" s="1">
         <v>423.49</v>
       </c>
       <c r="D929">
@@ -21830,7 +21830,7 @@
       <c r="B930">
         <v>689.93</v>
       </c>
-      <c r="C930">
+      <c r="C930" s="1">
         <v>351.43</v>
       </c>
       <c r="D930">
@@ -21853,7 +21853,7 @@
       <c r="B931">
         <v>578.51</v>
       </c>
-      <c r="C931">
+      <c r="C931" s="1">
         <v>312.76</v>
       </c>
       <c r="D931">
@@ -21876,7 +21876,7 @@
       <c r="B932">
         <v>876.23</v>
       </c>
-      <c r="C932">
+      <c r="C932" s="1">
         <v>493.13</v>
       </c>
       <c r="D932">
@@ -21899,7 +21899,7 @@
       <c r="B933">
         <v>970.7</v>
       </c>
-      <c r="C933">
+      <c r="C933" s="1">
         <v>120.92</v>
       </c>
       <c r="D933">
@@ -21922,7 +21922,7 @@
       <c r="B934">
         <v>884.02</v>
       </c>
-      <c r="C934">
+      <c r="C934" s="1">
         <v>466.05</v>
       </c>
       <c r="D934">
@@ -21945,7 +21945,7 @@
       <c r="B935">
         <v>946.35</v>
       </c>
-      <c r="C935">
+      <c r="C935" s="1">
         <v>355.21</v>
       </c>
       <c r="D935">
@@ -21968,7 +21968,7 @@
       <c r="B936">
         <v>616.75</v>
       </c>
-      <c r="C936">
+      <c r="C936" s="1">
         <v>101.48</v>
       </c>
       <c r="D936">
@@ -21991,7 +21991,7 @@
       <c r="B937">
         <v>557.09</v>
       </c>
-      <c r="C937">
+      <c r="C937" s="1">
         <v>243.12</v>
       </c>
       <c r="D937">
@@ -22014,7 +22014,7 @@
       <c r="B938">
         <v>700.88</v>
       </c>
-      <c r="C938">
+      <c r="C938" s="1">
         <v>177.22</v>
       </c>
       <c r="D938">
@@ -22037,7 +22037,7 @@
       <c r="B939">
         <v>1055.8699999999999</v>
       </c>
-      <c r="C939">
+      <c r="C939" s="1">
         <v>474.89</v>
       </c>
       <c r="D939">
@@ -22060,7 +22060,7 @@
       <c r="B940">
         <v>1447.86</v>
       </c>
-      <c r="C940">
+      <c r="C940" s="1">
         <v>194.96</v>
       </c>
       <c r="D940">
@@ -22083,7 +22083,7 @@
       <c r="B941">
         <v>1101.98</v>
       </c>
-      <c r="C941">
+      <c r="C941" s="1">
         <v>494.49</v>
       </c>
       <c r="D941">
@@ -22106,7 +22106,7 @@
       <c r="B942">
         <v>1396.26</v>
       </c>
-      <c r="C942">
+      <c r="C942" s="1">
         <v>618.34</v>
       </c>
       <c r="D942">
@@ -22129,7 +22129,7 @@
       <c r="B943">
         <v>917.97</v>
       </c>
-      <c r="C943">
+      <c r="C943" s="1">
         <v>207.09</v>
       </c>
       <c r="D943">
@@ -22152,7 +22152,7 @@
       <c r="B944">
         <v>859</v>
       </c>
-      <c r="C944">
+      <c r="C944" s="1">
         <v>433.09</v>
       </c>
       <c r="D944">
@@ -22175,7 +22175,7 @@
       <c r="B945">
         <v>1146.3699999999999</v>
       </c>
-      <c r="C945">
+      <c r="C945" s="1">
         <v>615.20000000000005</v>
       </c>
       <c r="D945">
@@ -22198,7 +22198,7 @@
       <c r="B946">
         <v>753.2</v>
       </c>
-      <c r="C946">
+      <c r="C946" s="1">
         <v>284.44</v>
       </c>
       <c r="D946">
@@ -22221,7 +22221,7 @@
       <c r="B947">
         <v>1029.57</v>
       </c>
-      <c r="C947">
+      <c r="C947" s="1">
         <v>309.33</v>
       </c>
       <c r="D947">
@@ -22244,7 +22244,7 @@
       <c r="B948">
         <v>1290.1300000000001</v>
       </c>
-      <c r="C948">
+      <c r="C948" s="1">
         <v>269.5</v>
       </c>
       <c r="D948">
@@ -22267,7 +22267,7 @@
       <c r="B949">
         <v>1308.8599999999999</v>
       </c>
-      <c r="C949">
+      <c r="C949" s="1">
         <v>323.75</v>
       </c>
       <c r="D949">
@@ -22290,7 +22290,7 @@
       <c r="B950">
         <v>906.41</v>
       </c>
-      <c r="C950">
+      <c r="C950" s="1">
         <v>476.43</v>
       </c>
       <c r="D950">
@@ -22313,7 +22313,7 @@
       <c r="B951">
         <v>732.08</v>
       </c>
-      <c r="C951">
+      <c r="C951" s="1">
         <v>332.69</v>
       </c>
       <c r="D951">
@@ -22336,7 +22336,7 @@
       <c r="B952">
         <v>1205.3599999999999</v>
       </c>
-      <c r="C952">
+      <c r="C952" s="1">
         <v>267.37</v>
       </c>
       <c r="D952">
@@ -22359,7 +22359,7 @@
       <c r="B953">
         <v>1096.06</v>
       </c>
-      <c r="C953">
+      <c r="C953" s="1">
         <v>158.74</v>
       </c>
       <c r="D953">
@@ -22382,7 +22382,7 @@
       <c r="B954">
         <v>504.11</v>
       </c>
-      <c r="C954">
+      <c r="C954" s="1">
         <v>53.19</v>
       </c>
       <c r="D954">
@@ -22405,7 +22405,7 @@
       <c r="B955">
         <v>738.12</v>
       </c>
-      <c r="C955">
+      <c r="C955" s="1">
         <v>420.16</v>
       </c>
       <c r="D955">
@@ -22428,7 +22428,7 @@
       <c r="B956">
         <v>1353.47</v>
       </c>
-      <c r="C956">
+      <c r="C956" s="1">
         <v>634.35</v>
       </c>
       <c r="D956">
@@ -22451,7 +22451,7 @@
       <c r="B957">
         <v>949.58</v>
       </c>
-      <c r="C957">
+      <c r="C957" s="1">
         <v>492.29</v>
       </c>
       <c r="D957">
@@ -22474,7 +22474,7 @@
       <c r="B958">
         <v>1098.19</v>
       </c>
-      <c r="C958">
+      <c r="C958" s="1">
         <v>440.28</v>
       </c>
       <c r="D958">
@@ -22497,7 +22497,7 @@
       <c r="B959">
         <v>1381.3</v>
       </c>
-      <c r="C959">
+      <c r="C959" s="1">
         <v>364.84</v>
       </c>
       <c r="D959">
@@ -22520,7 +22520,7 @@
       <c r="B960">
         <v>929.83</v>
       </c>
-      <c r="C960">
+      <c r="C960" s="1">
         <v>226.53</v>
       </c>
       <c r="D960">
@@ -22543,7 +22543,7 @@
       <c r="B961">
         <v>1003.13</v>
       </c>
-      <c r="C961">
+      <c r="C961" s="1">
         <v>258.77999999999997</v>
       </c>
       <c r="D961">
@@ -22566,7 +22566,7 @@
       <c r="B962">
         <v>1361.88</v>
       </c>
-      <c r="C962">
+      <c r="C962" s="1">
         <v>520.42999999999995</v>
       </c>
       <c r="D962">
@@ -22589,7 +22589,7 @@
       <c r="B963">
         <v>754.66</v>
       </c>
-      <c r="C963">
+      <c r="C963" s="1">
         <v>452.12</v>
       </c>
       <c r="D963">
@@ -22612,7 +22612,7 @@
       <c r="B964">
         <v>1127.8599999999999</v>
       </c>
-      <c r="C964">
+      <c r="C964" s="1">
         <v>318.75</v>
       </c>
       <c r="D964">
@@ -22635,7 +22635,7 @@
       <c r="B965">
         <v>1166.53</v>
       </c>
-      <c r="C965">
+      <c r="C965" s="1">
         <v>587.66</v>
       </c>
       <c r="D965">
@@ -22658,7 +22658,7 @@
       <c r="B966">
         <v>1359.5</v>
       </c>
-      <c r="C966">
+      <c r="C966" s="1">
         <v>618.42999999999995</v>
       </c>
       <c r="D966">
@@ -22681,7 +22681,7 @@
       <c r="B967">
         <v>624.42999999999995</v>
       </c>
-      <c r="C967">
+      <c r="C967" s="1">
         <v>362.86</v>
       </c>
       <c r="D967">
@@ -22704,7 +22704,7 @@
       <c r="B968">
         <v>1418.52</v>
       </c>
-      <c r="C968">
+      <c r="C968" s="1">
         <v>783.1</v>
       </c>
       <c r="D968">
@@ -22727,7 +22727,7 @@
       <c r="B969">
         <v>901.25</v>
       </c>
-      <c r="C969">
+      <c r="C969" s="1">
         <v>475.45</v>
       </c>
       <c r="D969">
@@ -22750,7 +22750,7 @@
       <c r="B970">
         <v>519.4</v>
       </c>
-      <c r="C970">
+      <c r="C970" s="1">
         <v>136.86000000000001</v>
       </c>
       <c r="D970">
@@ -22773,7 +22773,7 @@
       <c r="B971">
         <v>1457.77</v>
       </c>
-      <c r="C971">
+      <c r="C971" s="1">
         <v>202.42</v>
       </c>
       <c r="D971">
@@ -22796,7 +22796,7 @@
       <c r="B972">
         <v>806.4</v>
       </c>
-      <c r="C972">
+      <c r="C972" s="1">
         <v>142.04</v>
       </c>
       <c r="D972">
@@ -22819,7 +22819,7 @@
       <c r="B973">
         <v>934.68</v>
       </c>
-      <c r="C973">
+      <c r="C973" s="1">
         <v>183.59</v>
       </c>
       <c r="D973">
@@ -22842,7 +22842,7 @@
       <c r="B974">
         <v>509.78</v>
       </c>
-      <c r="C974">
+      <c r="C974" s="1">
         <v>70.13</v>
       </c>
       <c r="D974">
@@ -22865,7 +22865,7 @@
       <c r="B975">
         <v>960.58</v>
       </c>
-      <c r="C975">
+      <c r="C975" s="1">
         <v>528.69000000000005</v>
       </c>
       <c r="D975">
@@ -22888,7 +22888,7 @@
       <c r="B976">
         <v>615.4</v>
       </c>
-      <c r="C976">
+      <c r="C976" s="1">
         <v>308.18</v>
       </c>
       <c r="D976">
@@ -22911,7 +22911,7 @@
       <c r="B977">
         <v>762.51</v>
       </c>
-      <c r="C977">
+      <c r="C977" s="1">
         <v>96.21</v>
       </c>
       <c r="D977">
@@ -22934,7 +22934,7 @@
       <c r="B978">
         <v>569.69000000000005</v>
       </c>
-      <c r="C978">
+      <c r="C978" s="1">
         <v>73.55</v>
       </c>
       <c r="D978">
@@ -22957,7 +22957,7 @@
       <c r="B979">
         <v>1115.3499999999999</v>
       </c>
-      <c r="C979">
+      <c r="C979" s="1">
         <v>341.27</v>
       </c>
       <c r="D979">
@@ -22980,7 +22980,7 @@
       <c r="B980">
         <v>1377.85</v>
       </c>
-      <c r="C980">
+      <c r="C980" s="1">
         <v>516.29999999999995</v>
       </c>
       <c r="D980">
@@ -23003,7 +23003,7 @@
       <c r="B981">
         <v>593.52</v>
       </c>
-      <c r="C981">
+      <c r="C981" s="1">
         <v>186.1</v>
       </c>
       <c r="D981">
@@ -23026,7 +23026,7 @@
       <c r="B982">
         <v>1069.33</v>
       </c>
-      <c r="C982">
+      <c r="C982" s="1">
         <v>311.57</v>
       </c>
       <c r="D982">
@@ -23049,7 +23049,7 @@
       <c r="B983">
         <v>1263.29</v>
       </c>
-      <c r="C983">
+      <c r="C983" s="1">
         <v>212.55</v>
       </c>
       <c r="D983">
@@ -23072,7 +23072,7 @@
       <c r="B984">
         <v>742.95</v>
       </c>
-      <c r="C984">
+      <c r="C984" s="1">
         <v>411.73</v>
       </c>
       <c r="D984">
@@ -23095,7 +23095,7 @@
       <c r="B985">
         <v>1202.6300000000001</v>
       </c>
-      <c r="C985">
+      <c r="C985" s="1">
         <v>695.11</v>
       </c>
       <c r="D985">
@@ -23118,7 +23118,7 @@
       <c r="B986">
         <v>798.15</v>
       </c>
-      <c r="C986">
+      <c r="C986" s="1">
         <v>130.28</v>
       </c>
       <c r="D986">
@@ -23141,7 +23141,7 @@
       <c r="B987">
         <v>1046.6099999999999</v>
       </c>
-      <c r="C987">
+      <c r="C987" s="1">
         <v>332.85</v>
       </c>
       <c r="D987">
@@ -23164,7 +23164,7 @@
       <c r="B988">
         <v>1172.28</v>
       </c>
-      <c r="C988">
+      <c r="C988" s="1">
         <v>415.39</v>
       </c>
       <c r="D988">
@@ -23187,7 +23187,7 @@
       <c r="B989">
         <v>970.71</v>
       </c>
-      <c r="C989">
+      <c r="C989" s="1">
         <v>173.45</v>
       </c>
       <c r="D989">
@@ -23210,7 +23210,7 @@
       <c r="B990">
         <v>583.38</v>
       </c>
-      <c r="C990">
+      <c r="C990" s="1">
         <v>329.17</v>
       </c>
       <c r="D990">
@@ -23233,7 +23233,7 @@
       <c r="B991">
         <v>1161.3499999999999</v>
       </c>
-      <c r="C991">
+      <c r="C991" s="1">
         <v>343.76</v>
       </c>
       <c r="D991">
@@ -23256,7 +23256,7 @@
       <c r="B992">
         <v>1335.89</v>
       </c>
-      <c r="C992">
+      <c r="C992" s="1">
         <v>201.24</v>
       </c>
       <c r="D992">
@@ -23279,7 +23279,7 @@
       <c r="B993">
         <v>1365.65</v>
       </c>
-      <c r="C993">
+      <c r="C993" s="1">
         <v>301.36</v>
       </c>
       <c r="D993">
@@ -23302,7 +23302,7 @@
       <c r="B994">
         <v>1316.79</v>
       </c>
-      <c r="C994">
+      <c r="C994" s="1">
         <v>763.47</v>
       </c>
       <c r="D994">
@@ -23325,7 +23325,7 @@
       <c r="B995">
         <v>784.29</v>
       </c>
-      <c r="C995">
+      <c r="C995" s="1">
         <v>308.14</v>
       </c>
       <c r="D995">
@@ -23348,7 +23348,7 @@
       <c r="B996">
         <v>1496.81</v>
       </c>
-      <c r="C996">
+      <c r="C996" s="1">
         <v>264.7</v>
       </c>
       <c r="D996">
@@ -23371,7 +23371,7 @@
       <c r="B997">
         <v>1432.65</v>
       </c>
-      <c r="C997">
+      <c r="C997" s="1">
         <v>417.66</v>
       </c>
       <c r="D997">
@@ -23394,7 +23394,7 @@
       <c r="B998">
         <v>947.57</v>
       </c>
-      <c r="C998">
+      <c r="C998" s="1">
         <v>487.73</v>
       </c>
       <c r="D998">
@@ -23417,7 +23417,7 @@
       <c r="B999">
         <v>746.97</v>
       </c>
-      <c r="C999">
+      <c r="C999" s="1">
         <v>410.69</v>
       </c>
       <c r="D999">
@@ -23440,7 +23440,7 @@
       <c r="B1000">
         <v>936.58</v>
       </c>
-      <c r="C1000">
+      <c r="C1000" s="1">
         <v>390.46</v>
       </c>
       <c r="D1000">
@@ -23463,7 +23463,7 @@
       <c r="B1001">
         <v>513.41</v>
       </c>
-      <c r="C1001">
+      <c r="C1001" s="1">
         <v>56.33</v>
       </c>
       <c r="D1001">
